--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -1323,6 +1323,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -1771,6 +1772,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="19.4" customHeight="1" s="89">
       <c r="A32" s="94" t="inlineStr">
         <is>
@@ -1877,6 +1879,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -2273,6 +2276,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="89">
       <c r="A18" s="101" t="inlineStr">
         <is>
@@ -2301,6 +2305,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="17.15" customHeight="1" s="89">
       <c r="A20" s="104" t="inlineStr">
         <is>
@@ -2347,6 +2352,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="19.4" customHeight="1" s="89">
       <c r="A25" s="107" t="inlineStr">
         <is>
@@ -2394,6 +2400,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="89">
       <c r="A31" s="112" t="inlineStr">
         <is>
@@ -2427,8 +2434,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2462,6 +2469,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="32.8" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -7474,7 +7482,7 @@
       </c>
       <c r="H124" s="122" t="inlineStr">
         <is>
-          <t>신규, 외부마감 최우선</t>
+          <t>신규, 외부마감 최우선. 제출물은 문서+코드만 해당, 영상은 10/12 발표 시연용(제출물 아님, 혼동 주의)</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7566,7 @@
       </c>
       <c r="H126" s="122" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>신규. 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지, 10/11 리허설 때 반드시 함께 확인)</t>
         </is>
       </c>
     </row>
@@ -7712,6 +7720,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -7908,6 +7917,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="17.35" customHeight="1" s="89">
       <c r="A15" s="142" t="inlineStr">
         <is>
@@ -8885,6 +8896,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -15437,6 +15449,7 @@
         </is>
       </c>
     </row>
+    <row r="129"/>
     <row r="130" ht="15" customHeight="1" s="89">
       <c r="A130" s="160" t="inlineStr">
         <is>
@@ -15551,6 +15564,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="89">
       <c r="A4" s="168" t="inlineStr">
         <is>
@@ -15750,6 +15764,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="89">
       <c r="A13" s="168" t="inlineStr">
         <is>
@@ -16165,6 +16180,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="24" customHeight="1" s="89">
       <c r="A28" s="168" t="inlineStr">
         <is>
@@ -16688,6 +16704,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="24" customHeight="1" s="89">
       <c r="A46" s="168" t="inlineStr">
         <is>
@@ -16923,6 +16940,7 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
     <row r="56" ht="24" customHeight="1" s="89">
       <c r="A56" s="168" t="inlineStr">
         <is>
@@ -17050,6 +17068,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63" ht="24" customHeight="1" s="89">
       <c r="A63" s="168" t="inlineStr">
         <is>
@@ -17321,6 +17340,7 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
     <row r="74" ht="24" customHeight="1" s="89">
       <c r="A74" s="168" t="inlineStr">
         <is>
@@ -17520,6 +17540,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="89">
       <c r="A83" s="168" t="inlineStr">
         <is>
@@ -17647,6 +17668,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90" ht="24" customHeight="1" s="89">
       <c r="A90" s="168" t="inlineStr">
         <is>
@@ -17846,6 +17868,7 @@
         </is>
       </c>
     </row>
+    <row r="98"/>
     <row r="99" ht="24" customHeight="1" s="89">
       <c r="A99" s="168" t="inlineStr">
         <is>
@@ -17973,6 +17996,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106" ht="24" customHeight="1" s="89">
       <c r="A106" s="168" t="inlineStr">
         <is>
@@ -18100,6 +18124,7 @@
         </is>
       </c>
     </row>
+    <row r="112"/>
     <row r="113" ht="24" customHeight="1" s="89">
       <c r="A113" s="168" t="inlineStr">
         <is>
@@ -18263,6 +18288,7 @@
         </is>
       </c>
     </row>
+    <row r="120"/>
     <row r="121" ht="24" customHeight="1" s="89">
       <c r="A121" s="168" t="inlineStr">
         <is>
@@ -18462,6 +18488,7 @@
         </is>
       </c>
     </row>
+    <row r="129"/>
     <row r="130" ht="24" customHeight="1" s="89">
       <c r="A130" s="168" t="inlineStr">
         <is>
@@ -18625,6 +18652,7 @@
         </is>
       </c>
     </row>
+    <row r="137"/>
     <row r="138" ht="24" customHeight="1" s="89">
       <c r="A138" s="168" t="inlineStr">
         <is>
@@ -18788,6 +18816,7 @@
         </is>
       </c>
     </row>
+    <row r="145"/>
     <row r="146" ht="24" customHeight="1" s="89">
       <c r="A146" s="168" t="inlineStr">
         <is>
@@ -18951,6 +18980,7 @@
         </is>
       </c>
     </row>
+    <row r="153"/>
     <row r="154" ht="24" customHeight="1" s="89">
       <c r="A154" s="168" t="inlineStr">
         <is>
@@ -19114,6 +19144,7 @@
         </is>
       </c>
     </row>
+    <row r="161"/>
     <row r="162" ht="24" customHeight="1" s="89">
       <c r="A162" s="168" t="inlineStr">
         <is>
@@ -19277,6 +19308,7 @@
         </is>
       </c>
     </row>
+    <row r="169"/>
     <row r="170" ht="24" customHeight="1" s="89">
       <c r="A170" s="168" t="inlineStr">
         <is>
@@ -19440,6 +19472,7 @@
         </is>
       </c>
     </row>
+    <row r="177"/>
     <row r="178" ht="24" customHeight="1" s="89">
       <c r="A178" s="168" t="inlineStr">
         <is>
@@ -19675,6 +19708,7 @@
         </is>
       </c>
     </row>
+    <row r="187"/>
     <row r="188" ht="24" customHeight="1" s="89">
       <c r="A188" s="168" t="inlineStr">
         <is>
@@ -19838,6 +19872,7 @@
         </is>
       </c>
     </row>
+    <row r="195"/>
     <row r="196" ht="24" customHeight="1" s="89">
       <c r="A196" s="168" t="inlineStr">
         <is>
@@ -20001,6 +20036,7 @@
         </is>
       </c>
     </row>
+    <row r="203"/>
     <row r="204" ht="24" customHeight="1" s="89">
       <c r="A204" s="168" t="inlineStr">
         <is>
@@ -20164,6 +20200,7 @@
         </is>
       </c>
     </row>
+    <row r="211"/>
     <row r="212" ht="24" customHeight="1" s="89">
       <c r="A212" s="168" t="inlineStr">
         <is>
@@ -20291,6 +20328,7 @@
         </is>
       </c>
     </row>
+    <row r="218"/>
     <row r="219" ht="24" customHeight="1" s="89">
       <c r="A219" s="168" t="inlineStr">
         <is>
@@ -20526,6 +20564,7 @@
         </is>
       </c>
     </row>
+    <row r="228"/>
     <row r="229" ht="24" customHeight="1" s="89">
       <c r="A229" s="168" t="inlineStr">
         <is>
@@ -20761,6 +20800,7 @@
         </is>
       </c>
     </row>
+    <row r="238"/>
     <row r="239" ht="24" customHeight="1" s="89">
       <c r="A239" s="168" t="inlineStr">
         <is>
@@ -20996,6 +21036,7 @@
         </is>
       </c>
     </row>
+    <row r="248"/>
     <row r="249" ht="24" customHeight="1" s="89">
       <c r="A249" s="168" t="inlineStr">
         <is>
@@ -21339,6 +21380,7 @@
         </is>
       </c>
     </row>
+    <row r="261"/>
     <row r="262" ht="24" customHeight="1" s="89">
       <c r="A262" s="168" t="inlineStr">
         <is>
@@ -21682,6 +21724,7 @@
         </is>
       </c>
     </row>
+    <row r="274"/>
     <row r="275" ht="24" customHeight="1" s="89">
       <c r="A275" s="168" t="inlineStr">
         <is>
@@ -22061,6 +22104,7 @@
         </is>
       </c>
     </row>
+    <row r="288"/>
     <row r="289" ht="24" customHeight="1" s="89">
       <c r="A289" s="168" t="inlineStr">
         <is>
@@ -22404,6 +22448,7 @@
         </is>
       </c>
     </row>
+    <row r="301"/>
     <row r="302" ht="24" customHeight="1" s="89">
       <c r="A302" s="168" t="inlineStr">
         <is>
@@ -22675,6 +22720,7 @@
         </is>
       </c>
     </row>
+    <row r="312"/>
     <row r="313" ht="24" customHeight="1" s="89">
       <c r="A313" s="168" t="inlineStr">
         <is>
@@ -22910,6 +22956,7 @@
         </is>
       </c>
     </row>
+    <row r="322"/>
     <row r="323" ht="24" customHeight="1" s="89">
       <c r="A323" s="168" t="inlineStr">
         <is>
@@ -23162,9 +23209,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2434,9 +2434,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7913,7 +7913,8 @@
           <t>□ 시드데이터 재실행 후 데모 데이터가 깨끗한가
 □ E2E 시나리오(로그인→...→정산)가 끊김없이 진행되는가
 □ 발표 전 서버 웨이크업을 확인했는가
-□ 예상 Q&amp;A 답변이 준비됐는가</t>
+□ 예상 Q&amp;A 답변이 준비됐는가
+□ 발표영상 실제 재생 확인(음성·화면 끝까지 끊김없이 재생되는지)</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8850,8 @@
           <t>□ [신규] 데모 데이터 시드 재실행(DB 초기화+골든패스 데이터 재세팅)
 □ [신규] E2E 데모 시나리오 리허설(로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산 1회 실행)
 □ [신규] 예상 Q&amp;A 답변 준비(iCal 선택이유/DB전환이유/AI Agent vs 챗봇 차이 등)
-□ [검증] ✅ 6.5단계 검증: 배포본 재생·서버 웨이크업·발표 최종 리허설</t>
+□ [검증] ✅ 6.5단계 검증: 배포본 재생·서버 웨이크업·발표 최종 리허설
+□ 발표영상 실제 재생 확인(음성·화면 끝까지 끊김없이 재생되는지)</t>
         </is>
       </c>
       <c r="D50" s="145" t="inlineStr">
@@ -14905,7 +14907,7 @@
       </c>
       <c r="F118" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="G118" s="154" t="inlineStr">
@@ -14957,7 +14959,7 @@
       </c>
       <c r="F119" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="G119" s="154" t="inlineStr">
@@ -15061,7 +15063,7 @@
       </c>
       <c r="F121" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="G121" s="153" t="inlineStr">
@@ -15326,7 +15328,7 @@
       </c>
       <c r="G126" s="154" t="inlineStr">
         <is>
-          <t>backend/app/api/auth.py, frontend/src/pages/Login.jsx</t>
+          <t>docs/demo_scenario.md</t>
         </is>
       </c>
       <c r="H126" s="153" t="inlineStr">
@@ -15341,7 +15343,7 @@
       </c>
       <c r="J126" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산까지 끊김없이 1회 실행, 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지)</t>
         </is>
       </c>
     </row>
@@ -15373,7 +15375,7 @@
       </c>
       <c r="F127" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="G127" s="154" t="inlineStr">
@@ -15445,7 +15447,7 @@
       </c>
       <c r="J128" s="153" t="inlineStr">
         <is>
-          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인</t>
+          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인. 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지, 10/11 리허설 때 반드시 함께 확인)</t>
         </is>
       </c>
     </row>
@@ -22583,7 +22585,7 @@
       </c>
       <c r="C307" s="171" t="inlineStr">
         <is>
-          <t>Claude Code(직접실행)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="D307" s="144" t="inlineStr">
@@ -22619,7 +22621,7 @@
       </c>
       <c r="C308" s="171" t="inlineStr">
         <is>
-          <t>Claude Code(직접실행)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="D308" s="144" t="inlineStr">
@@ -22783,7 +22785,7 @@
       </c>
       <c r="C316" s="171" t="inlineStr">
         <is>
-          <t>Claude Code(직접실행)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="D316" s="149" t="inlineStr">
@@ -23060,7 +23062,7 @@
       </c>
       <c r="D327" s="144" t="inlineStr">
         <is>
-          <t>backend/app/api/auth.py, frontend/src/pages/Login.jsx</t>
+          <t>docs/demo_scenario.md</t>
         </is>
       </c>
       <c r="E327" s="149" t="inlineStr">
@@ -23071,7 +23073,7 @@
       </c>
       <c r="F327" s="149" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산까지 끊김없이 1회 실행, 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지)</t>
         </is>
       </c>
       <c r="G327" s="171" t="inlineStr">
@@ -23091,7 +23093,7 @@
       </c>
       <c r="C328" s="171" t="inlineStr">
         <is>
-          <t>Claude Code(직접실행)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="D328" s="144" t="inlineStr">
@@ -23143,7 +23145,7 @@
       </c>
       <c r="F329" s="149" t="inlineStr">
         <is>
-          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인</t>
+          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인. 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지, 10/11 리허설 때 반드시 함께 확인)</t>
         </is>
       </c>
       <c r="G329" s="171" t="inlineStr">
@@ -23209,9 +23211,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A230:G230"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
-    <mergeCell ref="A230:G230"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2434,9 +2434,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15333,12 +15333,12 @@
       </c>
       <c r="H126" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>발표 전 마지막 통관 테스트 — 로그인부터 정산까지 실제로 끊기는 지점이 있는지 확인하는 것이 유일한 목적</t>
         </is>
       </c>
       <c r="I126" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>로컬 개발환경이 아니라 실제 배포된(Supabase 연결) 환경에서 리허설해야 의미가 있다 — 로컬에서만 통과하고 배포환경에서 다르게 동작할 위험을 놓치면 발표 당일 사고로 이어진다</t>
         </is>
       </c>
       <c r="J126" s="153" t="inlineStr">
@@ -23067,8 +23067,8 @@
       </c>
       <c r="E327" s="149" t="inlineStr">
         <is>
-          <t>▶ 자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)
-⚠ iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>▶ 발표 전 마지막 통관 테스트 — 로그인부터 정산까지 실제로 끊기는 지점이 있는지 확인하는 것이 유일한 목적
+⚠ 로컬 개발환경이 아니라 실제 배포된(Supabase 연결) 환경에서 리허설해야 의미가 있다 — 로컬에서만 통과하고 배포환경에서 다르게 동작할 위험을 놓치면 발표 당일 사고로 이어진다</t>
         </is>
       </c>
       <c r="F327" s="149" t="inlineStr">
@@ -23211,9 +23211,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="C217:F217"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2434,8 +2434,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -10757,17 +10757,17 @@
       </c>
       <c r="H38" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>빠진 화면이 없는지가 핵심 — 로그인/빈상태 화면을 특히 놓치기 쉬움</t>
         </is>
       </c>
       <c r="I38" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>와이어프레임을 너무 디테일하게 만들지 않는다(시간 낭비, 저해상도로 충분)</t>
         </is>
       </c>
       <c r="J38" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>실제 사용 흐름 그대로 클릭 시뮬레이션 해보며 막히는 지점이 있는지 확인</t>
         </is>
       </c>
     </row>
@@ -10809,17 +10809,17 @@
       </c>
       <c r="H39" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>빠진 화면이 없는지가 핵심 — 로그인/빈상태 화면을 특히 놓치기 쉬움</t>
         </is>
       </c>
       <c r="I39" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>와이어프레임을 너무 디테일하게 만들지 않는다(시간 낭비, 저해상도로 충분)</t>
         </is>
       </c>
       <c r="J39" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>실제 사용 흐름 그대로 클릭 시뮬레이션 해보며 막히는 지점이 있는지 확인</t>
         </is>
       </c>
     </row>
@@ -17415,13 +17415,13 @@
       </c>
       <c r="E77" s="149" t="inlineStr">
         <is>
-          <t>▶ 자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)
-⚠ iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>▶ 빠진 화면이 없는지가 핵심 — 로그인/빈상태 화면을 특히 놓치기 쉬움
+⚠ 와이어프레임을 너무 디테일하게 만들지 않는다(시간 낭비, 저해상도로 충분)</t>
         </is>
       </c>
       <c r="F77" s="149" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>실제 사용 흐름 그대로 클릭 시뮬레이션 해보며 막히는 지점이 있는지 확인</t>
         </is>
       </c>
       <c r="G77" s="171" t="inlineStr">
@@ -17451,13 +17451,13 @@
       </c>
       <c r="E78" s="149" t="inlineStr">
         <is>
-          <t>▶ 자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)
-⚠ iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>▶ 빠진 화면이 없는지가 핵심 — 로그인/빈상태 화면을 특히 놓치기 쉬움
+⚠ 와이어프레임을 너무 디테일하게 만들지 않는다(시간 낭비, 저해상도로 충분)</t>
         </is>
       </c>
       <c r="F78" s="149" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>실제 사용 흐름 그대로 클릭 시뮬레이션 해보며 막히는 지점이 있는지 확인</t>
         </is>
       </c>
       <c r="G78" s="171" t="inlineStr">
@@ -23211,9 +23211,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2434,9 +2434,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E33" s="124" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F33" s="130" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E36" s="124" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F36" s="130" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="G77" s="171" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="G79" s="171" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>
@@ -23211,9 +23211,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A230:G230"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
-    <mergeCell ref="A230:G230"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2434,9 +2434,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C33" s="122" t="inlineStr">
         <is>
-          <t>전체 화면목록 확정(로그인·회원가입·대시보드·온보딩3단계·캘린더·AI인박스·체크인·청소·정산·가격·컴플라이언스·설정)</t>
+          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
         </is>
       </c>
       <c r="D33" s="124" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="C35" s="122" t="inlineStr">
         <is>
-          <t>핵심 화면 와이어프레임 제작(대시보드·AI인박스·정산·온보딩)</t>
+          <t>핵심 화면 와이어프레임 제작(대시보드·예약모달·AI인박스·정산·온보딩)</t>
         </is>
       </c>
       <c r="D35" s="124" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E35" s="124" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F35" s="130" t="inlineStr">
@@ -8133,8 +8133,8 @@
       </c>
       <c r="D23" s="145" t="inlineStr">
         <is>
-          <t>□ [신규] 전체 화면목록 확정(로그인·회원가입·대시보드·온보딩3단계·캘린더·AI인박스·체크인·청소·정산·가격·컴플라이언스·설정)
-□ [신규] 핵심 화면 와이어프레임 제작(대시보드·AI인박스·정산·온보딩)
+          <t>□ [신규] 전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)
+□ [신규] 핵심 화면 와이어프레임 제작(대시보드·예약모달·AI인박스·정산·온보딩)
 □ [신규] 디자인시스템 공통 컴포넌트 정의(Header/Sidebar/Card/Badge/Modal/Toast/Loading/EmptyState)</t>
         </is>
       </c>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="E38" s="153" t="inlineStr">
         <is>
-          <t>전체 화면목록 확정(로그인·회원가입·대시보드·온보딩3단계·캘린더·AI인박스·체크인·청소·정산·가격·컴플라이언스·설정)</t>
+          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
         </is>
       </c>
       <c r="F38" s="155" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="G38" s="154" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/ui_wireframe.md</t>
         </is>
       </c>
       <c r="H38" s="153" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E39" s="153" t="inlineStr">
         <is>
-          <t>핵심 화면 와이어프레임 제작(대시보드·AI인박스·정산·온보딩)</t>
+          <t>핵심 화면 와이어프레임 제작(대시보드·예약모달·AI인박스·정산·온보딩)</t>
         </is>
       </c>
       <c r="F39" s="155" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G39" s="154" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/ui_wireframe.md</t>
         </is>
       </c>
       <c r="H39" s="153" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G40" s="154" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/ui_wireframe.md</t>
         </is>
       </c>
       <c r="H40" s="153" t="inlineStr">
@@ -17353,7 +17353,7 @@
     <row r="75" ht="18" customHeight="1" s="89">
       <c r="A75" s="169" t="inlineStr">
         <is>
-          <t>🎯 오늘의 타이틀: 전체 화면목록 확정(로그인·회원가입·대시보드·온보딩3단계·캘린더·AI인박스·체크인·청소·정산·가격·컴플라이언스·설정)</t>
+          <t>🎯 오늘의 타이틀: 전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="B77" s="149" t="inlineStr">
         <is>
-          <t>전체 화면목록 확정(로그인·회원가입·대시보드·온보딩3단계·캘린더·AI인박스·체크인·청소·정산·가격·컴플라이언스·설정)</t>
+          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
         </is>
       </c>
       <c r="C77" s="171" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="D77" s="144" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/ui_wireframe.md</t>
         </is>
       </c>
       <c r="E77" s="149" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="B78" s="149" t="inlineStr">
         <is>
-          <t>핵심 화면 와이어프레임 제작(대시보드·AI인박스·정산·온보딩)</t>
+          <t>핵심 화면 와이어프레임 제작(대시보드·예약모달·AI인박스·정산·온보딩)</t>
         </is>
       </c>
       <c r="C78" s="171" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="D78" s="144" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/ui_wireframe.md</t>
         </is>
       </c>
       <c r="E78" s="149" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="G78" s="171" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>
@@ -17482,7 +17482,7 @@
       </c>
       <c r="D79" s="144" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/ui_wireframe.md</t>
         </is>
       </c>
       <c r="E79" s="149" t="inlineStr">
@@ -23211,9 +23211,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="C217:F217"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2434,8 +2434,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E45" s="128" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F45" s="126" t="inlineStr">
@@ -4266,7 +4266,11 @@
           <t>2026-09-08(화)</t>
         </is>
       </c>
-      <c r="H45" s="126" t="n"/>
+      <c r="H45" s="126" t="inlineStr">
+        <is>
+          <t>Vite+React+TS+Tailwind 초기 세팅 포함(선행 작업, 별도 태스크 미생성). TypeScript로 구현하여 파일위치 .jsx→.tsx 정정.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="33.75" customHeight="1" s="89">
       <c r="A46" s="125" t="inlineStr">
@@ -8157,7 +8161,7 @@
       </c>
       <c r="C24" s="149" t="inlineStr">
         <is>
-          <t>□ 통합 대시보드 뼈대(3~5개 숙소 한눈에 보기)</t>
+          <t>☑ 통합 대시보드 뼈대(3~5개 숙소 한눈에 보기)</t>
         </is>
       </c>
       <c r="D24" s="145" t="inlineStr">
@@ -10908,7 +10912,7 @@
       </c>
       <c r="G41" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.jsx</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="H41" s="153" t="inlineStr">
@@ -12624,7 +12628,7 @@
       </c>
       <c r="G74" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.jsx</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="H74" s="154" t="inlineStr">
@@ -13872,7 +13876,7 @@
       </c>
       <c r="G98" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.jsx</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="H98" s="154" t="inlineStr">
@@ -17610,7 +17614,7 @@
       </c>
       <c r="D86" s="144" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.jsx</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="E86" s="149" t="inlineStr">
@@ -17626,7 +17630,7 @@
       </c>
       <c r="G86" s="171" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>
@@ -20270,7 +20274,7 @@
       </c>
       <c r="D215" s="144" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.jsx</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="E215" s="144" t="inlineStr">
@@ -21594,7 +21598,7 @@
       </c>
       <c r="D269" s="144" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.jsx</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="E269" s="144" t="inlineStr">
@@ -23211,9 +23215,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -1323,7 +1323,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -1772,7 +1771,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="19.4" customHeight="1" s="89">
       <c r="A32" s="94" t="inlineStr">
         <is>
@@ -1879,7 +1877,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -2276,7 +2273,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="89">
       <c r="A18" s="101" t="inlineStr">
         <is>
@@ -2305,7 +2301,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="17.15" customHeight="1" s="89">
       <c r="A20" s="104" t="inlineStr">
         <is>
@@ -2352,7 +2347,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="19.4" customHeight="1" s="89">
       <c r="A25" s="107" t="inlineStr">
         <is>
@@ -2400,7 +2394,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="89">
       <c r="A31" s="112" t="inlineStr">
         <is>
@@ -2434,8 +2427,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2469,7 +2462,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="32.8" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -3743,7 +3735,7 @@
       </c>
       <c r="C33" s="122" t="inlineStr">
         <is>
-          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
+          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스(설정탭)·지식베이스·설정)</t>
         </is>
       </c>
       <c r="D33" s="124" t="inlineStr">
@@ -7724,7 +7716,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -7774,7 +7765,7 @@
       </c>
       <c r="C5" s="140" t="inlineStr">
         <is>
-          <t>□ 12개 화면 목록에 빠진 화면이 없는가
+          <t>□ 11개 화면 목록에 빠진 화면이 없는가
 □ 와이어프레임이 실제 사용흐름과 맞는가(클릭 시뮬레이션)
 □ 공통 컴포넌트(Loading/Empty/Error/Toast)가 정의됐는가
 □ 회원가입/로그인 플로우가 설계에 포함됐는가</t>
@@ -7922,8 +7913,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="17.35" customHeight="1" s="89">
       <c r="A15" s="142" t="inlineStr">
         <is>
@@ -8137,7 +8126,7 @@
       </c>
       <c r="D23" s="145" t="inlineStr">
         <is>
-          <t>□ [신규] 전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)
+          <t>□ [신규] 전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스(설정탭)·지식베이스·설정)
 □ [신규] 핵심 화면 와이어프레임 제작(대시보드·예약모달·AI인박스·정산·온보딩)
 □ [신규] 디자인시스템 공통 컴포넌트 정의(Header/Sidebar/Card/Badge/Modal/Toast/Loading/EmptyState)</t>
         </is>
@@ -8902,7 +8891,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -10746,7 +10734,7 @@
       </c>
       <c r="E38" s="153" t="inlineStr">
         <is>
-          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
+          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스(설정탭)·지식베이스·설정)</t>
         </is>
       </c>
       <c r="F38" s="155" t="inlineStr">
@@ -15455,7 +15443,6 @@
         </is>
       </c>
     </row>
-    <row r="129"/>
     <row r="130" ht="15" customHeight="1" s="89">
       <c r="A130" s="160" t="inlineStr">
         <is>
@@ -15570,7 +15557,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="89">
       <c r="A4" s="168" t="inlineStr">
         <is>
@@ -15770,7 +15756,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="89">
       <c r="A13" s="168" t="inlineStr">
         <is>
@@ -16186,7 +16171,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1" s="89">
       <c r="A28" s="168" t="inlineStr">
         <is>
@@ -16710,7 +16694,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46" ht="24" customHeight="1" s="89">
       <c r="A46" s="168" t="inlineStr">
         <is>
@@ -16946,7 +16929,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56" ht="24" customHeight="1" s="89">
       <c r="A56" s="168" t="inlineStr">
         <is>
@@ -17074,7 +17056,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63" ht="24" customHeight="1" s="89">
       <c r="A63" s="168" t="inlineStr">
         <is>
@@ -17346,7 +17327,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74" ht="24" customHeight="1" s="89">
       <c r="A74" s="168" t="inlineStr">
         <is>
@@ -17357,7 +17337,7 @@
     <row r="75" ht="18" customHeight="1" s="89">
       <c r="A75" s="169" t="inlineStr">
         <is>
-          <t>🎯 오늘의 타이틀: 전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
+          <t>🎯 오늘의 타이틀: 전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스(설정탭)·지식베이스·설정)</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17384,7 @@
       </c>
       <c r="B77" s="149" t="inlineStr">
         <is>
-          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스·지식베이스·설정)</t>
+          <t>전체 화면목록 확정(로그인·회원가입·온보딩2스텝·대시보드·캘린더·AI인박스·액션센터·청소·정산·컴플라이언스(설정탭)·지식베이스·설정)</t>
         </is>
       </c>
       <c r="C77" s="171" t="inlineStr">
@@ -17546,7 +17526,6 @@
         </is>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="89">
       <c r="A83" s="168" t="inlineStr">
         <is>
@@ -17674,7 +17653,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90" ht="24" customHeight="1" s="89">
       <c r="A90" s="168" t="inlineStr">
         <is>
@@ -17874,7 +17852,6 @@
         </is>
       </c>
     </row>
-    <row r="98"/>
     <row r="99" ht="24" customHeight="1" s="89">
       <c r="A99" s="168" t="inlineStr">
         <is>
@@ -18002,7 +17979,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106" ht="24" customHeight="1" s="89">
       <c r="A106" s="168" t="inlineStr">
         <is>
@@ -18130,7 +18106,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113" ht="24" customHeight="1" s="89">
       <c r="A113" s="168" t="inlineStr">
         <is>
@@ -18294,7 +18269,6 @@
         </is>
       </c>
     </row>
-    <row r="120"/>
     <row r="121" ht="24" customHeight="1" s="89">
       <c r="A121" s="168" t="inlineStr">
         <is>
@@ -18494,7 +18468,6 @@
         </is>
       </c>
     </row>
-    <row r="129"/>
     <row r="130" ht="24" customHeight="1" s="89">
       <c r="A130" s="168" t="inlineStr">
         <is>
@@ -18658,7 +18631,6 @@
         </is>
       </c>
     </row>
-    <row r="137"/>
     <row r="138" ht="24" customHeight="1" s="89">
       <c r="A138" s="168" t="inlineStr">
         <is>
@@ -18822,7 +18794,6 @@
         </is>
       </c>
     </row>
-    <row r="145"/>
     <row r="146" ht="24" customHeight="1" s="89">
       <c r="A146" s="168" t="inlineStr">
         <is>
@@ -18986,7 +18957,6 @@
         </is>
       </c>
     </row>
-    <row r="153"/>
     <row r="154" ht="24" customHeight="1" s="89">
       <c r="A154" s="168" t="inlineStr">
         <is>
@@ -19150,7 +19120,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162" ht="24" customHeight="1" s="89">
       <c r="A162" s="168" t="inlineStr">
         <is>
@@ -19314,7 +19283,6 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
     <row r="170" ht="24" customHeight="1" s="89">
       <c r="A170" s="168" t="inlineStr">
         <is>
@@ -19478,7 +19446,6 @@
         </is>
       </c>
     </row>
-    <row r="177"/>
     <row r="178" ht="24" customHeight="1" s="89">
       <c r="A178" s="168" t="inlineStr">
         <is>
@@ -19714,7 +19681,6 @@
         </is>
       </c>
     </row>
-    <row r="187"/>
     <row r="188" ht="24" customHeight="1" s="89">
       <c r="A188" s="168" t="inlineStr">
         <is>
@@ -19878,7 +19844,6 @@
         </is>
       </c>
     </row>
-    <row r="195"/>
     <row r="196" ht="24" customHeight="1" s="89">
       <c r="A196" s="168" t="inlineStr">
         <is>
@@ -20042,7 +20007,6 @@
         </is>
       </c>
     </row>
-    <row r="203"/>
     <row r="204" ht="24" customHeight="1" s="89">
       <c r="A204" s="168" t="inlineStr">
         <is>
@@ -20206,7 +20170,6 @@
         </is>
       </c>
     </row>
-    <row r="211"/>
     <row r="212" ht="24" customHeight="1" s="89">
       <c r="A212" s="168" t="inlineStr">
         <is>
@@ -20334,7 +20297,6 @@
         </is>
       </c>
     </row>
-    <row r="218"/>
     <row r="219" ht="24" customHeight="1" s="89">
       <c r="A219" s="168" t="inlineStr">
         <is>
@@ -20570,7 +20532,6 @@
         </is>
       </c>
     </row>
-    <row r="228"/>
     <row r="229" ht="24" customHeight="1" s="89">
       <c r="A229" s="168" t="inlineStr">
         <is>
@@ -20806,7 +20767,6 @@
         </is>
       </c>
     </row>
-    <row r="238"/>
     <row r="239" ht="24" customHeight="1" s="89">
       <c r="A239" s="168" t="inlineStr">
         <is>
@@ -21042,7 +21002,6 @@
         </is>
       </c>
     </row>
-    <row r="248"/>
     <row r="249" ht="24" customHeight="1" s="89">
       <c r="A249" s="168" t="inlineStr">
         <is>
@@ -21386,7 +21345,6 @@
         </is>
       </c>
     </row>
-    <row r="261"/>
     <row r="262" ht="24" customHeight="1" s="89">
       <c r="A262" s="168" t="inlineStr">
         <is>
@@ -21730,7 +21688,6 @@
         </is>
       </c>
     </row>
-    <row r="274"/>
     <row r="275" ht="24" customHeight="1" s="89">
       <c r="A275" s="168" t="inlineStr">
         <is>
@@ -22110,7 +22067,6 @@
         </is>
       </c>
     </row>
-    <row r="288"/>
     <row r="289" ht="24" customHeight="1" s="89">
       <c r="A289" s="168" t="inlineStr">
         <is>
@@ -22454,7 +22410,6 @@
         </is>
       </c>
     </row>
-    <row r="301"/>
     <row r="302" ht="24" customHeight="1" s="89">
       <c r="A302" s="168" t="inlineStr">
         <is>
@@ -22726,7 +22681,6 @@
         </is>
       </c>
     </row>
-    <row r="312"/>
     <row r="313" ht="24" customHeight="1" s="89">
       <c r="A313" s="168" t="inlineStr">
         <is>
@@ -22962,7 +22916,6 @@
         </is>
       </c>
     </row>
-    <row r="322"/>
     <row r="323" ht="24" customHeight="1" s="89">
       <c r="A323" s="168" t="inlineStr">
         <is>
@@ -23215,9 +23168,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2427,8 +2427,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="G42" s="154" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md</t>
         </is>
       </c>
       <c r="H42" s="153" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="G43" s="154" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/api_contract.md</t>
         </is>
       </c>
       <c r="H43" s="153" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="G44" s="154" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>체크리스트 '9단계 검증 체크리스트' 시트</t>
         </is>
       </c>
       <c r="H44" s="153" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="H76" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>JWT_SECRET_KEY를 실제 값으로 교체(기본값 change-me-in-production 방치 시 토큰 위조 가능). CORS_ORIGINS에 Vercel 배포 도메인 추가(현재 localhost:5173만 허용). SUPABASE_DATABASE_URL 설정.</t>
         </is>
       </c>
       <c r="I76" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>.env.production은 커밋하지 않는다(.gitignore 확인). 실제 값은 Vercel·Render 대시보드 환경변수로 주입한다.</t>
         </is>
       </c>
       <c r="J76" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>배포본에서 로그인 성공 여부와 프론트→백엔드 API 호출이 CORS 오류 없이 되는지 확인</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="D93" s="144" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md</t>
         </is>
       </c>
       <c r="E93" s="149" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="D94" s="144" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>docs/ui_design.md, docs/api_contract.md</t>
         </is>
       </c>
       <c r="E94" s="149" t="inlineStr">
@@ -17792,7 +17792,7 @@
       </c>
       <c r="D95" s="144" t="inlineStr">
         <is>
-          <t>docs/ui_design.md (신규) 또는 Figma/손그림</t>
+          <t>체크리스트 '9단계 검증 체크리스트' 시트</t>
         </is>
       </c>
       <c r="E95" s="149" t="inlineStr">
@@ -20405,13 +20405,13 @@
       </c>
       <c r="E223" s="144" t="inlineStr">
         <is>
-          <t>▶ Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정
-⚠ 제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>▶ JWT_SECRET_KEY를 실제 값으로 교체(기본값 change-me-in-production 방치 시 토큰 위조 가능). CORS_ORIGINS에 Vercel 배포 도메인 추가(현재 localhost:5173만 허용). SUPABASE_DATABASE_URL 설정.
+⚠ .env.production은 커밋하지 않는다(.gitignore 확인). 실제 값은 Vercel·Render 대시보드 환경변수로 주입한다.</t>
         </is>
       </c>
       <c r="F223" s="149" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>배포본에서 로그인 성공 여부와 프론트→백엔드 API 호출이 CORS 오류 없이 되는지 확인</t>
         </is>
       </c>
       <c r="G223" s="171" t="inlineStr">
@@ -23168,9 +23168,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
     <mergeCell ref="A230:G230"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2443,7 +2443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="88" min="1" max="1"/>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="G51" s="121" t="inlineStr">
         <is>
-          <t>2026-09-18(금)</t>
+          <t>2026-09-16(수)</t>
         </is>
       </c>
       <c r="H51" s="122" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G58" s="121" t="inlineStr">
         <is>
-          <t>2026-09-18(금)</t>
+          <t>2026-09-16(수)</t>
         </is>
       </c>
       <c r="H58" s="122" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="G60" s="125" t="inlineStr">
         <is>
-          <t>2026-09-19(토)</t>
+          <t>2026-09-18(금)</t>
         </is>
       </c>
       <c r="H60" s="126" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G62" s="121" t="inlineStr">
         <is>
-          <t>2026-09-19(토)</t>
+          <t>2026-09-18(금)</t>
         </is>
       </c>
       <c r="H62" s="122" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G63" s="121" t="inlineStr">
         <is>
-          <t>2026-09-21(월)</t>
+          <t>2026-09-19(토)</t>
         </is>
       </c>
       <c r="H63" s="122" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G64" s="121" t="inlineStr">
         <is>
-          <t>2026-09-22(화)</t>
+          <t>2026-09-21(월)</t>
         </is>
       </c>
       <c r="H64" s="122" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="G66" s="125" t="inlineStr">
         <is>
-          <t>2026-09-21(월)</t>
+          <t>2026-09-19(토)</t>
         </is>
       </c>
       <c r="H66" s="126" t="n"/>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G67" s="135" t="inlineStr">
         <is>
-          <t>2026-09-22(화)</t>
+          <t>2026-09-21(월)</t>
         </is>
       </c>
       <c r="H67" s="136" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="G69" s="125" t="inlineStr">
         <is>
-          <t>2026-09-26(토)</t>
+          <t>2026-09-22(화)</t>
         </is>
       </c>
       <c r="H69" s="126" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G70" s="125" t="inlineStr">
         <is>
-          <t>2026-09-26(토)</t>
+          <t>2026-09-22(화)</t>
         </is>
       </c>
       <c r="H70" s="126" t="n"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G73" s="131" t="inlineStr">
         <is>
-          <t>2026-09-28(월)</t>
+          <t>2026-09-24(목)</t>
         </is>
       </c>
       <c r="H73" s="132" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G74" s="125" t="inlineStr">
         <is>
-          <t>2026-09-29(화)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="H74" s="126" t="n"/>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="G75" s="125" t="inlineStr">
         <is>
-          <t>2026-09-29(화)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="H75" s="127" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G76" s="125" t="inlineStr">
         <is>
-          <t>2026-09-30(수)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="H76" s="127" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G77" s="121" t="inlineStr">
         <is>
-          <t>2026-10-01(목)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="H77" s="122" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G78" s="125" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-24(목)</t>
         </is>
       </c>
       <c r="H78" s="126" t="n"/>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G79" s="125" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="H79" s="126" t="n"/>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="G80" s="121" t="inlineStr">
         <is>
-          <t>2026-09-28(월)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="H80" s="122" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G81" s="125" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="H81" s="126" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G82" s="125" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="H82" s="126" t="n"/>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="G83" s="135" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="H83" s="136" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G84" s="131" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-29(화)</t>
         </is>
       </c>
       <c r="H84" s="132" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="G88" s="121" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="H88" s="122" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G89" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-09-29(화)</t>
         </is>
       </c>
       <c r="H89" s="126" t="n"/>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="G90" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-09-30(수)</t>
         </is>
       </c>
       <c r="H90" s="126" t="n"/>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="G91" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="H91" s="126" t="n"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="G92" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="H92" s="127" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G93" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-09-30(수)</t>
         </is>
       </c>
       <c r="H93" s="126" t="n"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G94" s="125" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="H94" s="126" t="n"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G95" s="125" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H95" s="126" t="n"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G96" s="125" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H96" s="126" t="n"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G97" s="121" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H97" s="122" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="G98" s="125" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="H98" s="127" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="G100" s="125" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H100" s="126" t="n"/>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="G101" s="125" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="H101" s="126" t="n"/>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="G102" s="125" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="H102" s="126" t="n"/>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="G103" s="135" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H103" s="136" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G104" s="125" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H104" s="126" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="G105" s="125" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H105" s="126" t="n"/>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G106" s="121" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H106" s="123" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="G107" s="131" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="H107" s="132" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="C124" s="122" t="inlineStr">
         <is>
-          <t>✅ 설명문서+소스코드 GitHub 최종 제출(외부마감 10/10)</t>
+          <t>✅ 설명문서 + 소스코드(ZIP) PBT 제출(외부마감 10/10)</t>
         </is>
       </c>
       <c r="D124" s="124" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H124" s="122" t="inlineStr">
         <is>
-          <t>신규, 외부마감 최우선. 제출물은 문서+코드만 해당, 영상은 10/12 발표 시연용(제출물 아님, 혼동 주의)</t>
+          <t>제출물 3종: 설명문서·소스코드(ZIP)·발표자료(PPT). 영상은 제출물이 아니며 10/12 발표 시연용. 파일명 3기_3차_신경주_○○○. 제출경로 PBT → 프로젝트 섹션 → [3차 최종 제출]</t>
         </is>
       </c>
     </row>
@@ -7647,6 +7647,132 @@
       <c r="H128" s="132" t="inlineStr">
         <is>
           <t>검증, 10/12는 발표당일 작업없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B129" s="132" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C129" s="133" t="inlineStr">
+        <is>
+          <t>발표 슬라이드 초안 작성(구성·화면 캡처·AI Agent Loop 다이어그램)</t>
+        </is>
+      </c>
+      <c r="D129" s="134" t="inlineStr">
+        <is>
+          <t>최상</t>
+        </is>
+      </c>
+      <c r="E129" s="134" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="F129" s="132" t="inlineStr">
+        <is>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+        </is>
+      </c>
+      <c r="G129" s="131" t="inlineStr">
+        <is>
+          <t>2026-10-06(화)</t>
+        </is>
+      </c>
+      <c r="H129" s="132" t="inlineStr">
+        <is>
+          <t>신규. 10/9 "슬라이드 최종본 확정"의 선행 작업 — 현재 제작 태스크가 없어 신설</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B130" s="132" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C130" s="133" t="inlineStr">
+        <is>
+          <t>소스코드 ZIP 생성(node_modules·.env·__pycache__ 제외 확인)</t>
+        </is>
+      </c>
+      <c r="D130" s="134" t="inlineStr">
+        <is>
+          <t>최상</t>
+        </is>
+      </c>
+      <c r="E130" s="134" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="F130" s="132" t="inlineStr">
+        <is>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+        </is>
+      </c>
+      <c r="G130" s="131" t="inlineStr">
+        <is>
+          <t>2026-10-10(토)</t>
+        </is>
+      </c>
+      <c r="H130" s="132" t="inlineStr">
+        <is>
+          <t>신규. 안내문 명시 — API Key·비밀번호·개인정보 포함 여부 반드시 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="131" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B131" s="132" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C131" s="133" t="inlineStr">
+        <is>
+          <t>✅ 발표자료(PPT) PBT 제출(외부마감 10/11)</t>
+        </is>
+      </c>
+      <c r="D131" s="134" t="inlineStr">
+        <is>
+          <t>최상</t>
+        </is>
+      </c>
+      <c r="E131" s="134" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="F131" s="132" t="inlineStr">
+        <is>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+        </is>
+      </c>
+      <c r="G131" s="131" t="inlineStr">
+        <is>
+          <t>2026-10-11(일)</t>
+        </is>
+      </c>
+      <c r="H131" s="132" t="inlineStr">
+        <is>
+          <t>신규, 외부제출마감(10/11). 파일명 3기_3차_신경주_발표자료. PDF 또는 PPTX. 영상은 제출물 아님</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7780,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E128">
+  <conditionalFormatting sqref="E4:E131">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -7665,25 +7791,25 @@
       <formula>"예정"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D128">
+  <conditionalFormatting sqref="D4:D131">
     <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
       <formula>"최상"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="E4:E128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E4:E131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"예정,진행중,완료,보류"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D4:D128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D4:D131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"최상,상,중,하"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B4:B128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="B4:B131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"데이터모델 설계(P0),UI/UX 설계,기반 인프라,고객 응대 자동화,비대면 체크인,청소·시설 관리,정산 리포트,동적 가격 책정,알림·액션센터,컴플라이언스,통합QA·보안,마무리,최종 데모검증"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="A4:A128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="A4:A131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"1,1.5,2,3,4,5,5.5,6,6.5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7700,7 +7826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="88" min="1" max="1"/>
@@ -8316,59 +8442,55 @@
     <row r="31" ht="31.5" customHeight="1" s="89">
       <c r="A31" s="143" t="inlineStr">
         <is>
+          <t>2026-09-16(수)</t>
+        </is>
+      </c>
+      <c r="B31" s="140" t="inlineStr">
+        <is>
+          <t>2단계</t>
+        </is>
+      </c>
+      <c r="C31" s="149" t="inlineStr">
+        <is>
+          <t>□ [신규] 채널연결(iCal URL) 실패시 에러 안내 UI(잘못된 URL/파싱실패 케이스)
+□ [신규] 로딩/에러/빈상태 공통 컴포넌트 적용 시작(캘린더 화면)</t>
+        </is>
+      </c>
+      <c r="D31" s="145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="146" t="n"/>
+    </row>
+    <row r="32" ht="31.5" customHeight="1" s="89">
+      <c r="A32" s="147" t="inlineStr">
+        <is>
           <t>2026-09-17(목)</t>
         </is>
       </c>
-      <c r="B31" s="140" t="inlineStr">
+      <c r="B32" s="140" t="inlineStr">
         <is>
           <t>3단계</t>
         </is>
       </c>
-      <c r="C31" s="149" t="inlineStr">
+      <c r="C32" s="144" t="inlineStr">
         <is>
           <t>□ 자체 통합 인박스(게스트 채팅 시뮬레이터 UI)
 □ [신규] Claude API 초기설정: $5 선충전 + 월 Spend Limit $10 설정 + Dev/Prod API키 분리</t>
         </is>
       </c>
-      <c r="D31" s="145" t="inlineStr">
+      <c r="D32" s="145" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E31" s="146" t="n"/>
-    </row>
-    <row r="32" ht="31.5" customHeight="1" s="89">
-      <c r="A32" s="147" t="inlineStr">
-        <is>
-          <t>2026-09-18(금)</t>
-        </is>
-      </c>
-      <c r="B32" s="140" t="inlineStr">
-        <is>
-          <t>2단계</t>
-        </is>
-      </c>
-      <c r="C32" s="144" t="inlineStr">
-        <is>
-          <t>□ [신규] 채널연결(iCal URL) 실패시 에러 안내 UI(잘못된 URL/파싱실패 케이스)
-□ [신규] 로딩/에러/빈상태 공통 컴포넌트 적용 시작(캘린더 화면)</t>
-        </is>
-      </c>
-      <c r="D32" s="145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="148" t="inlineStr">
-        <is>
-          <t>🌙 연장근무일(+3h)</t>
-        </is>
-      </c>
+      <c r="E32" s="148" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="89">
       <c r="A33" s="143" t="inlineStr">
         <is>
-          <t>2026-09-19(토)</t>
+          <t>2026-09-18(금)</t>
         </is>
       </c>
       <c r="B33" s="140" t="inlineStr">
@@ -8386,12 +8508,16 @@
           <t>□ 숙소별 RAG 지식베이스 구축(로컬 벡터검색, LLM비용無) + property_id 스코프 격리 + 개발용 응답캐시(동일질문 반복시 API 미호출)</t>
         </is>
       </c>
-      <c r="E33" s="146" t="n"/>
+      <c r="E33" s="146" t="inlineStr">
+        <is>
+          <t>🌙 연장근무일(+3h)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="31.5" customHeight="1" s="89">
       <c r="A34" s="147" t="inlineStr">
         <is>
-          <t>2026-09-21(월)</t>
+          <t>2026-09-19(토)</t>
         </is>
       </c>
       <c r="B34" s="140" t="inlineStr">
@@ -8410,16 +8536,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E34" s="148" t="inlineStr">
-        <is>
-          <t>🌙 연장근무일(+3h)</t>
-        </is>
-      </c>
+      <c r="E34" s="148" t="n"/>
     </row>
     <row r="35" ht="31.5" customHeight="1" s="89">
       <c r="A35" s="143" t="inlineStr">
         <is>
-          <t>2026-09-22(화)</t>
+          <t>2026-09-21(월)</t>
         </is>
       </c>
       <c r="B35" s="140" t="inlineStr">
@@ -8438,20 +8560,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E35" s="146" t="n"/>
+      <c r="E35" s="146" t="inlineStr">
+        <is>
+          <t>🌙 연장근무일(+3h)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="63.75" customHeight="1" s="89">
       <c r="A36" s="147" t="inlineStr">
         <is>
+          <t>2026-09-22(화)</t>
+        </is>
+      </c>
+      <c r="B36" s="140" t="inlineStr">
+        <is>
+          <t>3단계</t>
+        </is>
+      </c>
+      <c r="C36" s="144" t="inlineStr">
+        <is>
+          <t>□ 체크인/체크아웃 안내, 리뷰요청 자동화</t>
+        </is>
+      </c>
+      <c r="D36" s="145" t="inlineStr">
+        <is>
+          <t>□ 위험도 분류 적용(자동:와이파이/체크인시간/주차/비번 vs 승인필요:환불/변경/할인/보상/민원/고장/안전)</t>
+        </is>
+      </c>
+      <c r="E36" s="148" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1" s="89">
+      <c r="A37" s="143" t="inlineStr">
+        <is>
           <t>2026-09-23(수)</t>
         </is>
       </c>
-      <c r="B36" s="140" t="inlineStr">
+      <c r="B37" s="140" t="inlineStr">
         <is>
           <t>3단계</t>
         </is>
       </c>
-      <c r="C36" s="144" t="inlineStr">
+      <c r="C37" s="149" t="inlineStr">
         <is>
           <t>□ [신규] AI/iCal 실패시 에러 Toast·Fallback 안내 처리
 □ AI 답변 '근거' 표시 UI(참고 KB 나열) + 마크다운 렌더링 처리
@@ -8459,44 +8608,21 @@
 □ [신규] 중간 회귀체크포인트1: 1~3단계 기능 통합 재확인(예약→AI응대까지 흐름 재실행)</t>
         </is>
       </c>
-      <c r="D36" s="145" t="inlineStr">
+      <c r="D37" s="150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E36" s="148" t="inlineStr">
+      <c r="E37" s="146" t="inlineStr">
         <is>
           <t>🌙 연장근무일(+3h)</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="19.5" customHeight="1" s="89">
-      <c r="A37" s="143" t="inlineStr">
-        <is>
-          <t>2026-09-26(토)</t>
-        </is>
-      </c>
-      <c r="B37" s="140" t="inlineStr">
-        <is>
-          <t>3단계</t>
-        </is>
-      </c>
-      <c r="C37" s="149" t="inlineStr">
-        <is>
-          <t>□ 체크인/체크아웃 안내, 리뷰요청 자동화</t>
-        </is>
-      </c>
-      <c r="D37" s="150" t="inlineStr">
-        <is>
-          <t>□ 위험도 분류 적용(자동:와이파이/체크인시간/주차/비번 vs 승인필요:환불/변경/할인/보상/민원/고장/안전)</t>
-        </is>
-      </c>
-      <c r="E37" s="146" t="n"/>
     </row>
     <row r="38" ht="31.5" customHeight="1" s="89">
       <c r="A38" s="147" t="inlineStr">
         <is>
-          <t>2026-09-28(월)</t>
+          <t>2026-09-24(목)</t>
         </is>
       </c>
       <c r="B38" s="140" t="inlineStr">
@@ -8506,25 +8632,20 @@
       </c>
       <c r="C38" s="144" t="inlineStr">
         <is>
-          <t>□ [검증] ✅ 3단계 검증: 교차오답 테스트 + 의도적 API실패 유발후 에러UI 확인
-□ [신규] Empty State/에러처리 청소·체크인 화면 반영</t>
+          <t>□ [검증] ✅ 3단계 검증: 교차오답 테스트 + 의도적 API실패 유발후 에러UI 확인</t>
         </is>
       </c>
       <c r="D38" s="145" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="148" t="inlineStr">
-        <is>
-          <t>🌙 연장근무일(+3h)</t>
-        </is>
-      </c>
+          <t>□ 청소 상태머신 구현(PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED/ISSUE)</t>
+        </is>
+      </c>
+      <c r="E38" s="148" t="n"/>
     </row>
     <row r="39" ht="31.5" customHeight="1" s="89">
       <c r="A39" s="143" t="inlineStr">
         <is>
-          <t>2026-09-29(화)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="B39" s="140" t="inlineStr">
@@ -8535,7 +8656,8 @@
       <c r="C39" s="149" t="inlineStr">
         <is>
           <t>□ 예약확정시 임시 비밀번호 자동생성/만료 로직
-□ 스마트락 100% Mock 확정 + '시뮬레이션' 뱃지 표시</t>
+□ [신규] 예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)
+□ 예약변경시 청소시간 자동 재계산 로직</t>
         </is>
       </c>
       <c r="D39" s="145" t="inlineStr">
@@ -8548,7 +8670,7 @@
     <row r="40" ht="19.5" customHeight="1" s="89">
       <c r="A40" s="147" t="inlineStr">
         <is>
-          <t>2026-09-30(수)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="B40" s="140" t="inlineStr">
@@ -8558,7 +8680,9 @@
       </c>
       <c r="C40" s="144" t="inlineStr">
         <is>
-          <t>□ Mock 락 상태 대시보드(잠김/열림/배터리)</t>
+          <t>□ [신규] Empty State/에러처리 청소·체크인 화면 반영
+□ 스마트락 100% Mock 확정 + '시뮬레이션' 뱃지 표시
+□ Mock 락 상태 대시보드(잠김/열림/배터리)</t>
         </is>
       </c>
       <c r="D40" s="145" t="inlineStr">
@@ -8566,41 +8690,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E40" s="148" t="inlineStr">
-        <is>
-          <t>🌙 연장근무일(+3h)</t>
-        </is>
-      </c>
+      <c r="E40" s="148" t="n"/>
     </row>
     <row r="41" ht="48" customHeight="1" s="89">
       <c r="A41" s="143" t="inlineStr">
         <is>
-          <t>2026-10-01(목)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="B41" s="140" t="inlineStr">
         <is>
-          <t>4단계,5단계,6단계</t>
+          <t>4단계</t>
         </is>
       </c>
       <c r="C41" s="144" t="inlineStr">
         <is>
-          <t>□ Vercel+Render+Supabase 스테이징=프로덕션 서비스 생성(뼈대 프로젝트로 CORS/env 연결 테스트, 10/8에 그대로 정식승격)
-□ [검증] .env.production 환경변수 설정(Vercel/Render/Supabase 키 분리)
-□ [신규] 예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
+          <t>□ 문자API(알리고 등) 청소업체 알림 자동발송
+□ 체크리스트+사진업로드 완료확인(VERIFIED 단계)</t>
         </is>
       </c>
       <c r="D41" s="145" t="inlineStr">
         <is>
-          <t>□ [신규] 개인정보 최소수집 원칙 점검(게스트데이터-RAG데이터 분리 확인)</t>
-        </is>
-      </c>
-      <c r="E41" s="146" t="n"/>
+          <t>□ 호스텔 객실(Room)단위 정비 체크리스트 + 비품부족 체크박스</t>
+        </is>
+      </c>
+      <c r="E41" s="146" t="inlineStr">
+        <is>
+          <t>🌙 연장근무일(+3h)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="31.5" customHeight="1" s="89">
       <c r="A42" s="147" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-29(화)</t>
         </is>
       </c>
       <c r="B42" s="140" t="inlineStr">
@@ -8610,152 +8733,221 @@
       </c>
       <c r="C42" s="149" t="inlineStr">
         <is>
-          <t>□ 예약변경시 청소시간 자동 재계산 로직
-□ [신규] 시드 스크립트 실행 및 데이터 정상 반영 확인</t>
+          <t>□ [검증] ✅ 4단계 검증: 체크아웃→청소생성→상태전이 전체 흐름 1회 시뮬레이션</t>
         </is>
       </c>
       <c r="D42" s="150" t="inlineStr">
         <is>
-          <t>□ 청소 상태머신 구현(PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED/ISSUE)
-□ [신규] 데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
-        </is>
-      </c>
-      <c r="E42" s="148" t="inlineStr">
-        <is>
-          <t>🌙 연장근무일(+3h)</t>
-        </is>
-      </c>
+          <t>□ 채널별 수수료 템플릿 설계(Airbnb 15.5%, Booking.com 15~18% 등)</t>
+        </is>
+      </c>
+      <c r="E42" s="148" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1" s="89">
       <c r="A43" s="143" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-30(수)</t>
         </is>
       </c>
       <c r="B43" s="140" t="inlineStr">
         <is>
-          <t>4단계</t>
+          <t>5단계</t>
         </is>
       </c>
       <c r="C43" s="149" t="inlineStr">
         <is>
-          <t>□ 문자API(알리고 등) 청소업체 알림 자동발송
-□ 체크리스트+사진업로드 완료확인(VERIFIED 단계)
-□ [검증] ✅ 4단계 검증: 체크아웃→청소생성→상태전이 전체 흐름 1회 시뮬레이션</t>
+          <t>□ 1단계 자동추정 로직(Room 기본단가×박수-수수료)
+□ 취소/환불 반영 로직(refund_status 연동, 매출 자동제외)</t>
         </is>
       </c>
       <c r="D43" s="150" t="inlineStr">
         <is>
-          <t>□ 호스텔 객실(Room)단위 정비 체크리스트 + 비품부족 체크박스</t>
-        </is>
-      </c>
-      <c r="E43" s="146" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="146" t="inlineStr">
+        <is>
+          <t>🌙 연장근무일(+3h)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="96" customHeight="1" s="89">
       <c r="A44" s="147" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-01(목)</t>
         </is>
       </c>
       <c r="B44" s="140" t="inlineStr">
         <is>
+          <t>6단계,5단계</t>
+        </is>
+      </c>
+      <c r="C44" s="144" t="inlineStr">
+        <is>
+          <t>□ Vercel+Render+Supabase 스테이징=프로덕션 서비스 생성(뼈대 프로젝트로 CORS/env 연결 테스트, 10/8에 그대로 정식승격)
+□ [검증] .env.production 환경변수 설정(Vercel/Render/Supabase 키 분리)</t>
+        </is>
+      </c>
+      <c r="D44" s="150" t="inlineStr">
+        <is>
+          <t>□ [신규] 개인정보 최소수집 원칙 점검(게스트데이터-RAG데이터 분리 확인)</t>
+        </is>
+      </c>
+      <c r="E44" s="148" t="n"/>
+    </row>
+    <row r="45" ht="79.5" customHeight="1" s="89">
+      <c r="A45" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-02(금)</t>
+        </is>
+      </c>
+      <c r="B45" s="140" t="inlineStr">
+        <is>
           <t>5단계</t>
         </is>
       </c>
-      <c r="C44" s="144" t="inlineStr">
-        <is>
-          <t>□ [신규] Mock UI '시뮬레이션' 뱃지 통일 적용(가격반영/OTA메시징)
-□ 1단계 자동추정 로직(Room 기본단가×박수-수수료)
+      <c r="C45" s="149" t="inlineStr">
+        <is>
+          <t>□ [신규] 시드 스크립트 실행 및 데이터 정상 반영 확인
 □ 2단계 일괄확인(Bulk Confirm) UI
 □ 3단계 예외보정(Inline Edit, 차이나는 건만)
-□ 취소/환불 반영 로직(refund_status 연동, 매출 자동제외)
-□ [신규] 중간 회귀체크포인트2: 4~5단계 진행분 재확인(청소→정산 흐름 재실행)</t>
-        </is>
-      </c>
-      <c r="D44" s="150" t="inlineStr">
-        <is>
-          <t>□ 채널별 수수료 템플릿 설계(Airbnb 15.5%, Booking.com 15~18% 등)</t>
-        </is>
-      </c>
-      <c r="E44" s="148" t="inlineStr">
+□ 채널별/숙소별/월별 집계 + financial_status 뱃지 표시</t>
+        </is>
+      </c>
+      <c r="D45" s="150" t="inlineStr">
+        <is>
+          <t>□ [신규] 데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
+        </is>
+      </c>
+      <c r="E45" s="146" t="inlineStr">
         <is>
           <t>🌙 연장근무일(+3h)</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="79.5" customHeight="1" s="89">
-      <c r="A45" s="143" t="inlineStr">
-        <is>
-          <t>2026-10-06(화)</t>
-        </is>
-      </c>
-      <c r="B45" s="140" t="inlineStr">
-        <is>
-          <t>5단계</t>
-        </is>
-      </c>
-      <c r="C45" s="149" t="inlineStr">
-        <is>
-          <t>□ 채널별/숙소별/월별 집계 + financial_status 뱃지 표시
-□ 공휴일/지역축제 공공데이터 API 연동 추천가 로직
-□ 🔴🟡🟢 통합 위젯 대시보드 구현
-□ 각 이벤트 소스 연결(예약·청소·AI승인·서류만료·정산)
-□ [신규] 정산·가격 화면에 로딩/에러/빈상태 UI 적용</t>
-        </is>
-      </c>
-      <c r="D45" s="150" t="inlineStr">
-        <is>
-          <t>□ 예약임박도·잔여객실 반영(기존 iCal데이터 활용)
-□ Action Center 규칙기반 트리거 구현(최종스펙 규칙표 그대로)</t>
-        </is>
-      </c>
-      <c r="E45" s="146" t="n"/>
     </row>
     <row r="46" ht="63.75" customHeight="1" s="89">
       <c r="A46" s="147" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B46" s="140" t="inlineStr">
         <is>
-          <t>5단계,6단계</t>
+          <t>5단계</t>
         </is>
       </c>
       <c r="C46" s="144" t="inlineStr">
         <is>
-          <t>□ [신규] 공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)
+          <t>□ [신규] Mock UI '시뮬레이션' 뱃지 통일 적용(가격반영/OTA메시징)
+□ 🔴🟡🟢 통합 위젯 대시보드 구현
+□ 각 이벤트 소스 연결(예약·청소·AI승인·서류만료·정산)</t>
+        </is>
+      </c>
+      <c r="D46" s="145" t="inlineStr">
+        <is>
+          <t>□ Action Center 규칙기반 트리거 구현(최종스펙 규칙표 그대로)</t>
+        </is>
+      </c>
+      <c r="E46" s="148" t="n"/>
+    </row>
+    <row r="47" ht="79.5" customHeight="1" s="89">
+      <c r="A47" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-05(월)</t>
+        </is>
+      </c>
+      <c r="B47" s="140" t="inlineStr">
+        <is>
+          <t>5단계</t>
+        </is>
+      </c>
+      <c r="C47" s="144" t="inlineStr">
+        <is>
+          <t>□ [신규] 중간 회귀체크포인트2: 4~5단계 진행분 재확인(청소→정산 흐름 재실행)
+□ 공휴일/지역축제 공공데이터 API 연동 추천가 로직
+□ [신규] 정산·가격 화면에 로딩/에러/빈상태 UI 적용
+□ [신규] 공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)
 □ 추천가+근거 카드 UI, 승인클릭→Mock반영, 하한가 경고
 □ EVENT_BASED 변경신고 D+30 카운트다운 로직
 □ [검증] ✅ 5단계 검증: 정산 3단계 파이프라인 + 알림센터 트리거 실데이터로 재현</t>
         </is>
       </c>
-      <c r="D46" s="145" t="inlineStr">
+      <c r="D47" s="145" t="inlineStr">
+        <is>
+          <t>□ 예약임박도·잔여객실 반영(기존 iCal데이터 활용)
+□ 숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기
+□ 업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
+        </is>
+      </c>
+      <c r="E47" s="146" t="inlineStr">
+        <is>
+          <t>🌙 연장근무일(+3h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="63.75" customHeight="1" s="89">
+      <c r="A48" s="147" t="inlineStr">
+        <is>
+          <t>2026-10-06(화)</t>
+        </is>
+      </c>
+      <c r="B48" s="140" t="inlineStr">
+        <is>
+          <t>6단계</t>
+        </is>
+      </c>
+      <c r="C48" s="144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="145" t="inlineStr">
+        <is>
+          <t>□ [신규] 발표 슬라이드 초안 작성(구성·화면 캡처·AI Agent Loop 다이어그램)</t>
+        </is>
+      </c>
+      <c r="E48" s="148" t="n"/>
+    </row>
+    <row r="49" ht="48" customHeight="1" s="89">
+      <c r="A49" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-07(수)</t>
+        </is>
+      </c>
+      <c r="B49" s="140" t="inlineStr">
+        <is>
+          <t>6단계</t>
+        </is>
+      </c>
+      <c r="C49" s="149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="145" t="inlineStr">
         <is>
           <t>□ Clipchamp 10분 더미 영상 내보내기 테스트
-□ 숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기
-□ 업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)
 □ 영상 대본/콘티 초안 작성(화면 흐름·나레이션 포인트 먼저 잡기, 최종 코드 완성 전에도 가능)</t>
         </is>
       </c>
-      <c r="E46" s="148" t="inlineStr">
+      <c r="E49" s="146" t="inlineStr">
         <is>
           <t>🌙 연장근무일(+3h)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="79.5" customHeight="1" s="89">
-      <c r="A47" s="143" t="inlineStr">
+    <row r="50" ht="63.75" customHeight="1" s="89">
+      <c r="A50" s="143" t="inlineStr">
         <is>
           <t>2026-10-08(목)</t>
         </is>
       </c>
-      <c r="B47" s="140" t="inlineStr">
+      <c r="B50" s="140" t="inlineStr">
         <is>
           <t>5.5단계,6단계</t>
         </is>
       </c>
-      <c r="C47" s="144" t="inlineStr">
+      <c r="C50" s="144" t="inlineStr">
         <is>
           <t>□ [신규] 전체 기능 회귀테스트(예약→청소→AI→정산→알림 전체 플로우 1회 통관)
 □ [신규] 예외케이스 전수점검(중복예약/취소/환불/iCal실패/LLM실패/DB실패 에러UI 확인)
@@ -8764,26 +8956,26 @@
 □ GitHub 저장소 최종정리 + 프로덕션 배포 전환(스테이징→정식)+CORS 최종확인</t>
         </is>
       </c>
-      <c r="D47" s="145" t="inlineStr">
+      <c r="D50" s="145" t="inlineStr">
         <is>
           <t>□ [신규] README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)
 □ [신규] 제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
         </is>
       </c>
-      <c r="E47" s="146" t="n"/>
-    </row>
-    <row r="48" ht="63.75" customHeight="1" s="89">
-      <c r="A48" s="147" t="inlineStr">
+      <c r="E50" s="146" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>2026-10-09(금)</t>
         </is>
       </c>
-      <c r="B48" s="140" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>5.5단계,6단계</t>
         </is>
       </c>
-      <c r="C48" s="144" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>□ [신규] 1920x1080 데스크톱+Chrome 기준 화면 확인
 □ Mock/Real 표현 최종점검 + '숙소운영특화 AI Agent' 표현 일관성 점검
@@ -8791,69 +8983,75 @@
 □ 영상 대본/콘티 최종본 확정(10/7 초안 기반, 실제 화면 캡처 반영)</t>
         </is>
       </c>
-      <c r="D48" s="145" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>□ [야간] 화면 녹화 + 음성 나레이션 녹음</t>
         </is>
       </c>
-      <c r="E48" s="148" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>🌙 연장근무일(+3h)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="48" customHeight="1" s="89">
-      <c r="A49" s="143" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>2026-10-10(토)</t>
         </is>
       </c>
-      <c r="B49" s="140" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>6단계</t>
         </is>
       </c>
-      <c r="C49" s="149" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>□ 아침 검토: 전날 녹화분 확인, 재촬영 필요분 파악
 □ 최종 포맷/용량 확인 + 백업본 준비 + 최종 제출
-□ [신규] ✅ 설명문서+소스코드 GitHub 최종 제출(외부마감 10/10)</t>
-        </is>
-      </c>
-      <c r="D49" s="145" t="inlineStr">
+□ [신규] ✅ 설명문서 + 소스코드(ZIP) PBT 제출(외부마감 10/10)
+□ [신규] 소스코드 ZIP 생성(node_modules·.env·__pycache__ 제외 확인)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>□ [야간] 영상 편집(컷/자막/전환) + 렌더링</t>
         </is>
       </c>
-      <c r="E49" s="146" t="n"/>
-    </row>
-    <row r="50" ht="63.75" customHeight="1" s="89">
-      <c r="A50" s="143" t="inlineStr">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2026-10-11(일)</t>
         </is>
       </c>
-      <c r="B50" s="140" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>6.5단계</t>
         </is>
       </c>
-      <c r="C50" s="144" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>□ [신규] 데모 데이터 시드 재실행(DB 초기화+골든패스 데이터 재세팅)
 □ [신규] E2E 데모 시나리오 리허설(로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산 1회 실행)
 □ [신규] 예상 Q&amp;A 답변 준비(iCal 선택이유/DB전환이유/AI Agent vs 챗봇 차이 등)
 □ [검증] ✅ 6.5단계 검증: 배포본 재생·서버 웨이크업·발표 최종 리허설
-□ 발표영상 실제 재생 확인(음성·화면 끝까지 끊김없이 재생되는지)</t>
-        </is>
-      </c>
-      <c r="D50" s="145" t="inlineStr">
+□ 발표영상 실제 재생 확인(음성·화면 끝까지 끊김없이 재생되는지)
+□ [신규] ✅ 발표자료(PPT) PBT 제출(외부마감 10/11)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E50" s="146" t="n"/>
-    </row>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -8871,7 +9069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="88" min="1" max="1"/>
@@ -11546,12 +11744,12 @@
     <row r="54" ht="39.75" customHeight="1" s="89">
       <c r="A54" s="151" t="inlineStr">
         <is>
-          <t>2026-09-17(목)</t>
+          <t>2026-09-16(수)</t>
         </is>
       </c>
       <c r="B54" s="151" t="inlineStr">
         <is>
-          <t>3단계</t>
+          <t>2단계</t>
         </is>
       </c>
       <c r="C54" s="158" t="inlineStr">
@@ -11561,12 +11759,12 @@
       </c>
       <c r="D54" s="153" t="inlineStr">
         <is>
-          <t>고객 응대 자동화</t>
+          <t>기반 인프라</t>
         </is>
       </c>
       <c r="E54" s="153" t="inlineStr">
         <is>
-          <t>자체 통합 인박스(게스트 채팅 시뮬레이터 UI)</t>
+          <t>채널연결(iCal URL) 실패시 에러 안내 UI(잘못된 URL/파싱실패 케이스)</t>
         </is>
       </c>
       <c r="F54" s="155" t="inlineStr">
@@ -11576,86 +11774,86 @@
       </c>
       <c r="G54" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Inbox.jsx</t>
+          <t>backend/app/services/ical_sync.py</t>
         </is>
       </c>
       <c r="H54" s="153" t="inlineStr">
         <is>
-          <t>비용통제 아키텍처(1회 통합호출) 원칙을 벗어나지 않는다</t>
+          <t>로컬과 배포 환경을 최대한 동일하게 유지(dev/prod parity)</t>
         </is>
       </c>
       <c r="I54" s="154" t="inlineStr">
         <is>
-          <t>property_id 스코프 누락시 교차오답(다른 숙소 정보 노출)이라는 치명적 버그가 생김</t>
+          <t>.env 파일이 실수로 커밋되지 않았는지 매번 확인</t>
         </is>
       </c>
       <c r="J54" s="153" t="inlineStr">
         <is>
-          <t>실제 호출해보고 응답 품질과 호출 횟수(비용)를 함께 확인</t>
+          <t>로컬에서 정상 동작 확인 후에만 커밋</t>
         </is>
       </c>
     </row>
     <row r="55" ht="39.75" customHeight="1" s="89">
       <c r="A55" s="151" t="inlineStr">
         <is>
-          <t>2026-09-17(목)</t>
+          <t>2026-09-16(수)</t>
         </is>
       </c>
       <c r="B55" s="151" t="inlineStr">
         <is>
-          <t>3단계</t>
+          <t>2단계</t>
         </is>
       </c>
       <c r="C55" s="157" t="inlineStr">
         <is>
-          <t>설정확인</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D55" s="153" t="inlineStr">
         <is>
-          <t>고객 응대 자동화</t>
+          <t>기반 인프라</t>
         </is>
       </c>
       <c r="E55" s="154" t="inlineStr">
         <is>
-          <t>Claude API 초기설정: $5 선충전 + 월 Spend Limit $10 설정 + Dev/Prod API키 분리</t>
+          <t>로딩/에러/빈상태 공통 컴포넌트 적용 시작(캘린더 화면)</t>
         </is>
       </c>
       <c r="F55" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude(대화보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G55" s="153" t="inlineStr">
         <is>
-          <t>클라우드 콘솔(파일 아님) — Azure Portal / Google AI Studio</t>
+          <t>frontend/src/pages/Calendar.jsx</t>
         </is>
       </c>
       <c r="H55" s="153" t="inlineStr">
         <is>
-          <t>비용통제 아키텍처(1회 통합호출) 원칙을 벗어나지 않는다</t>
+          <t>로컬과 배포 환경을 최대한 동일하게 유지(dev/prod parity)</t>
         </is>
       </c>
       <c r="I55" s="154" t="inlineStr">
         <is>
-          <t>property_id 스코프 누락시 교차오답(다른 숙소 정보 노출)이라는 치명적 버그가 생김</t>
+          <t>.env 파일이 실수로 커밋되지 않았는지 매번 확인</t>
         </is>
       </c>
       <c r="J55" s="153" t="inlineStr">
         <is>
-          <t>실제 호출해보고 응답 품질과 호출 횟수(비용)를 함께 확인</t>
+          <t>로컬에서 정상 동작 확인 후에만 커밋</t>
         </is>
       </c>
     </row>
     <row r="56" ht="39.75" customHeight="1" s="89">
       <c r="A56" s="151" t="inlineStr">
         <is>
-          <t>2026-09-18(금)</t>
+          <t>2026-09-17(목)</t>
         </is>
       </c>
       <c r="B56" s="151" t="inlineStr">
         <is>
-          <t>2단계</t>
+          <t>3단계</t>
         </is>
       </c>
       <c r="C56" s="158" t="inlineStr">
@@ -11665,12 +11863,12 @@
       </c>
       <c r="D56" s="153" t="inlineStr">
         <is>
-          <t>기반 인프라</t>
+          <t>고객 응대 자동화</t>
         </is>
       </c>
       <c r="E56" s="153" t="inlineStr">
         <is>
-          <t>채널연결(iCal URL) 실패시 에러 안내 UI(잘못된 URL/파싱실패 케이스)</t>
+          <t>자체 통합 인박스(게스트 채팅 시뮬레이터 UI)</t>
         </is>
       </c>
       <c r="F56" s="155" t="inlineStr">
@@ -11680,81 +11878,81 @@
       </c>
       <c r="G56" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ical_sync.py</t>
+          <t>frontend/src/pages/Inbox.jsx</t>
         </is>
       </c>
       <c r="H56" s="153" t="inlineStr">
         <is>
-          <t>로컬과 배포 환경을 최대한 동일하게 유지(dev/prod parity)</t>
+          <t>비용통제 아키텍처(1회 통합호출) 원칙을 벗어나지 않는다</t>
         </is>
       </c>
       <c r="I56" s="154" t="inlineStr">
         <is>
-          <t>.env 파일이 실수로 커밋되지 않았는지 매번 확인</t>
+          <t>property_id 스코프 누락시 교차오답(다른 숙소 정보 노출)이라는 치명적 버그가 생김</t>
         </is>
       </c>
       <c r="J56" s="153" t="inlineStr">
         <is>
-          <t>로컬에서 정상 동작 확인 후에만 커밋</t>
+          <t>실제 호출해보고 응답 품질과 호출 횟수(비용)를 함께 확인</t>
         </is>
       </c>
     </row>
     <row r="57" ht="39.75" customHeight="1" s="89">
       <c r="A57" s="151" t="inlineStr">
         <is>
-          <t>2026-09-18(금)</t>
+          <t>2026-09-17(목)</t>
         </is>
       </c>
       <c r="B57" s="151" t="inlineStr">
         <is>
-          <t>2단계</t>
+          <t>3단계</t>
         </is>
       </c>
       <c r="C57" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설정확인</t>
         </is>
       </c>
       <c r="D57" s="153" t="inlineStr">
         <is>
-          <t>기반 인프라</t>
+          <t>고객 응대 자동화</t>
         </is>
       </c>
       <c r="E57" s="153" t="inlineStr">
         <is>
-          <t>로딩/에러/빈상태 공통 컴포넌트 적용 시작(캘린더 화면)</t>
+          <t>Claude API 초기설정: $5 선충전 + 월 Spend Limit $10 설정 + Dev/Prod API키 분리</t>
         </is>
       </c>
       <c r="F57" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Claude(대화보조)</t>
         </is>
       </c>
       <c r="G57" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Calendar.jsx</t>
+          <t>클라우드 콘솔(파일 아님) — Azure Portal / Google AI Studio</t>
         </is>
       </c>
       <c r="H57" s="153" t="inlineStr">
         <is>
-          <t>로컬과 배포 환경을 최대한 동일하게 유지(dev/prod parity)</t>
+          <t>비용통제 아키텍처(1회 통합호출) 원칙을 벗어나지 않는다</t>
         </is>
       </c>
       <c r="I57" s="154" t="inlineStr">
         <is>
-          <t>.env 파일이 실수로 커밋되지 않았는지 매번 확인</t>
+          <t>property_id 스코프 누락시 교차오답(다른 숙소 정보 노출)이라는 치명적 버그가 생김</t>
         </is>
       </c>
       <c r="J57" s="153" t="inlineStr">
         <is>
-          <t>로컬에서 정상 동작 확인 후에만 커밋</t>
+          <t>실제 호출해보고 응답 품질과 호출 횟수(비용)를 함께 확인</t>
         </is>
       </c>
     </row>
     <row r="58" ht="39.75" customHeight="1" s="89">
       <c r="A58" s="151" t="inlineStr">
         <is>
-          <t>2026-09-19(토)</t>
+          <t>2026-09-18(금)</t>
         </is>
       </c>
       <c r="B58" s="151" t="inlineStr">
@@ -11806,7 +12004,7 @@
     <row r="59" ht="39.75" customHeight="1" s="89">
       <c r="A59" s="151" t="inlineStr">
         <is>
-          <t>2026-09-19(토)</t>
+          <t>2026-09-18(금)</t>
         </is>
       </c>
       <c r="B59" s="151" t="inlineStr">
@@ -11858,7 +12056,7 @@
     <row r="60" ht="39.75" customHeight="1" s="89">
       <c r="A60" s="151" t="inlineStr">
         <is>
-          <t>2026-09-21(월)</t>
+          <t>2026-09-19(토)</t>
         </is>
       </c>
       <c r="B60" s="151" t="inlineStr">
@@ -11910,7 +12108,7 @@
     <row r="61" ht="39.75" customHeight="1" s="89">
       <c r="A61" s="151" t="inlineStr">
         <is>
-          <t>2026-09-21(월)</t>
+          <t>2026-09-19(토)</t>
         </is>
       </c>
       <c r="B61" s="151" t="inlineStr">
@@ -11962,7 +12160,7 @@
     <row r="62" ht="39.75" customHeight="1" s="89">
       <c r="A62" s="151" t="inlineStr">
         <is>
-          <t>2026-09-22(화)</t>
+          <t>2026-09-21(월)</t>
         </is>
       </c>
       <c r="B62" s="151" t="inlineStr">
@@ -12014,7 +12212,7 @@
     <row r="63" ht="39.75" customHeight="1" s="89">
       <c r="A63" s="151" t="inlineStr">
         <is>
-          <t>2026-09-22(화)</t>
+          <t>2026-09-21(월)</t>
         </is>
       </c>
       <c r="B63" s="151" t="inlineStr">
@@ -12066,7 +12264,7 @@
     <row r="64" ht="39.75" customHeight="1" s="89">
       <c r="A64" s="151" t="inlineStr">
         <is>
-          <t>2026-09-23(수)</t>
+          <t>2026-09-22(화)</t>
         </is>
       </c>
       <c r="B64" s="151" t="inlineStr">
@@ -12076,7 +12274,7 @@
       </c>
       <c r="C64" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D64" s="153" t="inlineStr">
@@ -12086,39 +12284,39 @@
       </c>
       <c r="E64" s="154" t="inlineStr">
         <is>
-          <t>AI/iCal 실패시 에러 Toast·Fallback 안내 처리</t>
+          <t>위험도 분류 적용(자동:와이파이/체크인시간/주차/비번 vs 승인필요:환불/변경/할인/보상/민원/고장/안전)</t>
         </is>
       </c>
       <c r="F64" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G64" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ical_sync.py</t>
+          <t>backend/app/services/ai_agent.py</t>
         </is>
       </c>
       <c r="H64" s="153" t="inlineStr">
         <is>
-          <t>비용통제 아키텍처(1회 통합호출) 원칙을 벗어나지 않는다</t>
+          <t>자동응답(와이파이/체크인시간/주차/비번)과 승인필요(환불/변경/할인/보상/민원/고장/안전)를 명확히 분리</t>
         </is>
       </c>
       <c r="I64" s="154" t="inlineStr">
         <is>
-          <t>property_id 스코프 누락시 교차오답(다른 숙소 정보 노출)이라는 치명적 버그가 생김</t>
+          <t>이 기준표가 불명확하면 고위험 문의가 실수로 자동발송될 위험</t>
         </is>
       </c>
       <c r="J64" s="153" t="inlineStr">
         <is>
-          <t>실제 호출해보고 응답 품질과 호출 횟수(비용)를 함께 확인</t>
+          <t>각 카테고리 질문을 실제로 넣어 자동/승인대기가 기준표대로 정확히 갈리는지 확인</t>
         </is>
       </c>
     </row>
     <row r="65" ht="39.75" customHeight="1" s="89">
       <c r="A65" s="151" t="inlineStr">
         <is>
-          <t>2026-09-23(수)</t>
+          <t>2026-09-22(화)</t>
         </is>
       </c>
       <c r="B65" s="151" t="inlineStr">
@@ -12138,7 +12336,7 @@
       </c>
       <c r="E65" s="154" t="inlineStr">
         <is>
-          <t>AI 답변 '근거' 표시 UI(참고 KB 나열) + 마크다운 렌더링 처리</t>
+          <t>체크인/체크아웃 안내, 리뷰요청 자동화</t>
         </is>
       </c>
       <c r="F65" s="155" t="inlineStr">
@@ -12148,7 +12346,7 @@
       </c>
       <c r="G65" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ai_agent.py</t>
+          <t>backend/app/services/notification.py</t>
         </is>
       </c>
       <c r="H65" s="153" t="inlineStr">
@@ -12190,7 +12388,7 @@
       </c>
       <c r="E66" s="153" t="inlineStr">
         <is>
-          <t>예약 상세화면→AI대화내역→Action Center 처리이력으로 이어지는 통합 딥링크/단일플로우 구현</t>
+          <t>AI/iCal 실패시 에러 Toast·Fallback 안내 처리</t>
         </is>
       </c>
       <c r="F66" s="155" t="inlineStr">
@@ -12200,22 +12398,22 @@
       </c>
       <c r="G66" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/ReservationDetail.jsx</t>
+          <t>backend/app/services/ical_sync.py</t>
         </is>
       </c>
       <c r="H66" s="154" t="inlineStr">
         <is>
-          <t>100% 규칙(시간+상태)기반 — AI가 위험을 판단하는 기능이 절대 아님</t>
+          <t>비용통제 아키텍처(1회 통합호출) 원칙을 벗어나지 않는다</t>
         </is>
       </c>
       <c r="I66" s="154" t="inlineStr">
         <is>
-          <t>check_in은 DATE라 시간정보가 없음 — checkin_time과 합산해야 'N시간 전' 계산이 실제로 가능(v1.1에서 필드 추가됨)</t>
+          <t>property_id 스코프 누락시 교차오답(다른 숙소 정보 노출)이라는 치명적 버그가 생김</t>
         </is>
       </c>
       <c r="J66" s="153" t="inlineStr">
         <is>
-          <t>규칙표(🔴🟡🟢)대로 정확히 분류되는지 실제 예약데이터로 재현해서 확인</t>
+          <t>실제 호출해보고 응답 품질과 호출 횟수(비용)를 함께 확인</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12440,7 @@
       </c>
       <c r="E67" s="153" t="inlineStr">
         <is>
-          <t>중간 회귀체크포인트1: 1~3단계 기능 통합 재확인(예약→AI응대까지 흐름 재실행)</t>
+          <t>AI 답변 '근거' 표시 UI(참고 KB 나열) + 마크다운 렌더링 처리</t>
         </is>
       </c>
       <c r="F67" s="155" t="inlineStr">
@@ -12252,7 +12450,7 @@
       </c>
       <c r="G67" s="154" t="inlineStr">
         <is>
-          <t>backend/tests/test_integration_1.py</t>
+          <t>backend/app/services/ai_agent.py</t>
         </is>
       </c>
       <c r="H67" s="153" t="inlineStr">
@@ -12274,7 +12472,7 @@
     <row r="68" ht="39.75" customHeight="1" s="89">
       <c r="A68" s="151" t="inlineStr">
         <is>
-          <t>2026-09-26(토)</t>
+          <t>2026-09-23(수)</t>
         </is>
       </c>
       <c r="B68" s="151" t="inlineStr">
@@ -12284,7 +12482,7 @@
       </c>
       <c r="C68" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D68" s="153" t="inlineStr">
@@ -12294,39 +12492,39 @@
       </c>
       <c r="E68" s="153" t="inlineStr">
         <is>
-          <t>위험도 분류 적용(자동:와이파이/체크인시간/주차/비번 vs 승인필요:환불/변경/할인/보상/민원/고장/안전)</t>
+          <t>예약 상세화면→AI대화내역→Action Center 처리이력으로 이어지는 통합 딥링크/단일플로우 구현</t>
         </is>
       </c>
       <c r="F68" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G68" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ai_agent.py</t>
+          <t>frontend/src/pages/ReservationDetail.jsx</t>
         </is>
       </c>
       <c r="H68" s="153" t="inlineStr">
         <is>
-          <t>자동응답(와이파이/체크인시간/주차/비번)과 승인필요(환불/변경/할인/보상/민원/고장/안전)를 명확히 분리</t>
+          <t>100% 규칙(시간+상태)기반 — AI가 위험을 판단하는 기능이 절대 아님</t>
         </is>
       </c>
       <c r="I68" s="153" t="inlineStr">
         <is>
-          <t>이 기준표가 불명확하면 고위험 문의가 실수로 자동발송될 위험</t>
+          <t>check_in은 DATE라 시간정보가 없음 — checkin_time과 합산해야 'N시간 전' 계산이 실제로 가능(v1.1에서 필드 추가됨)</t>
         </is>
       </c>
       <c r="J68" s="153" t="inlineStr">
         <is>
-          <t>각 카테고리 질문을 실제로 넣어 자동/승인대기가 기준표대로 정확히 갈리는지 확인</t>
+          <t>규칙표(🔴🟡🟢)대로 정확히 분류되는지 실제 예약데이터로 재현해서 확인</t>
         </is>
       </c>
     </row>
     <row r="69" ht="39.75" customHeight="1" s="89">
       <c r="A69" s="151" t="inlineStr">
         <is>
-          <t>2026-09-26(토)</t>
+          <t>2026-09-23(수)</t>
         </is>
       </c>
       <c r="B69" s="151" t="inlineStr">
@@ -12346,7 +12544,7 @@
       </c>
       <c r="E69" s="153" t="inlineStr">
         <is>
-          <t>체크인/체크아웃 안내, 리뷰요청 자동화</t>
+          <t>중간 회귀체크포인트1: 1~3단계 기능 통합 재확인(예약→AI응대까지 흐름 재실행)</t>
         </is>
       </c>
       <c r="F69" s="155" t="inlineStr">
@@ -12356,7 +12554,7 @@
       </c>
       <c r="G69" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/notification.py</t>
+          <t>backend/tests/test_integration_1.py</t>
         </is>
       </c>
       <c r="H69" s="153" t="inlineStr">
@@ -12378,7 +12576,7 @@
     <row r="70" ht="39.75" customHeight="1" s="89">
       <c r="A70" s="151" t="inlineStr">
         <is>
-          <t>2026-09-28(월)</t>
+          <t>2026-09-24(목)</t>
         </is>
       </c>
       <c r="B70" s="151" t="inlineStr">
@@ -12430,7 +12628,7 @@
     <row r="71" ht="39.75" customHeight="1" s="89">
       <c r="A71" s="151" t="inlineStr">
         <is>
-          <t>2026-09-28(월)</t>
+          <t>2026-09-24(목)</t>
         </is>
       </c>
       <c r="B71" s="151" t="inlineStr">
@@ -12440,7 +12638,7 @@
       </c>
       <c r="C71" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D71" s="153" t="inlineStr">
@@ -12450,39 +12648,39 @@
       </c>
       <c r="E71" s="154" t="inlineStr">
         <is>
-          <t>Empty State/에러처리 청소·체크인 화면 반영</t>
+          <t>청소 상태머신 구현(PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED/ISSUE)</t>
         </is>
       </c>
       <c r="F71" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G71" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Cleaning.jsx</t>
+          <t>backend/app/models/cleaning.py</t>
         </is>
       </c>
       <c r="H71" s="153" t="inlineStr">
         <is>
-          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
+          <t>PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED/ISSUE 순서 준수</t>
         </is>
       </c>
       <c r="I71" s="153" t="inlineStr">
         <is>
-          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
+          <t>COMPLETED와 VERIFIED 둘 다 '완료'로 취급하지 않으면 Action Center가 VERIFIED건까지 긴급알림으로 오탐</t>
         </is>
       </c>
       <c r="J71" s="153" t="inlineStr">
         <is>
-          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
+          <t>VERIFIED 상태의 청소건이 Action Center 긴급알림에 안 잡히는지 확인</t>
         </is>
       </c>
     </row>
     <row r="72" ht="39.75" customHeight="1" s="89">
       <c r="A72" s="151" t="inlineStr">
         <is>
-          <t>2026-09-29(화)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="B72" s="151" t="inlineStr">
@@ -12534,7 +12732,7 @@
     <row r="73" ht="39.75" customHeight="1" s="89">
       <c r="A73" s="151" t="inlineStr">
         <is>
-          <t>2026-09-29(화)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="B73" s="151" t="inlineStr">
@@ -12549,12 +12747,12 @@
       </c>
       <c r="D73" s="153" t="inlineStr">
         <is>
-          <t>비대면 체크인</t>
+          <t>청소·시설 관리</t>
         </is>
       </c>
       <c r="E73" s="153" t="inlineStr">
         <is>
-          <t>스마트락 100% Mock 확정 + '시뮬레이션' 뱃지 표시</t>
+          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
         </is>
       </c>
       <c r="F73" s="155" t="inlineStr">
@@ -12564,29 +12762,29 @@
       </c>
       <c r="G73" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/doorlock_mock.py</t>
+          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
         </is>
       </c>
       <c r="H73" s="154" t="inlineStr">
         <is>
-          <t>1개도 실연동 시도하지 않고 개발 착수부터 100% Mock으로 확정(시간 확보)</t>
+          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
         </is>
       </c>
       <c r="I73" s="153" t="inlineStr">
         <is>
-          <t>화면에 '시뮬레이션'임을 명확히 표시해야 함 — 실제 연동처럼 보이면 심사 시 오해 소지</t>
+          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J73" s="153" t="inlineStr">
         <is>
-          <t>화면에 Mock 뱃지가 육안으로 확인되는지</t>
+          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
         </is>
       </c>
     </row>
     <row r="74" ht="39.75" customHeight="1" s="89">
       <c r="A74" s="151" t="inlineStr">
         <is>
-          <t>2026-09-30(수)</t>
+          <t>2026-09-25(금)</t>
         </is>
       </c>
       <c r="B74" s="151" t="inlineStr">
@@ -12601,12 +12799,12 @@
       </c>
       <c r="D74" s="153" t="inlineStr">
         <is>
-          <t>비대면 체크인</t>
+          <t>청소·시설 관리</t>
         </is>
       </c>
       <c r="E74" s="154" t="inlineStr">
         <is>
-          <t>Mock 락 상태 대시보드(잠김/열림/배터리)</t>
+          <t>예약변경시 청소시간 자동 재계산 로직</t>
         </is>
       </c>
       <c r="F74" s="155" t="inlineStr">
@@ -12616,34 +12814,34 @@
       </c>
       <c r="G74" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.tsx</t>
+          <t>backend/app/services/cleaning.py</t>
         </is>
       </c>
       <c r="H74" s="154" t="inlineStr">
         <is>
-          <t>Mock임을 화면에서 명확히 알 수 있게 한다</t>
+          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
         </is>
       </c>
       <c r="I74" s="153" t="inlineStr">
         <is>
-          <t>실제 연동처럼 보이는 문구나 UI를 쓰지 않는다</t>
+          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J74" s="153" t="inlineStr">
         <is>
-          <t>화면에 시뮬레이션 표시가 있는지 육안 확인</t>
+          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
         </is>
       </c>
     </row>
     <row r="75" ht="39.75" customHeight="1" s="89">
       <c r="A75" s="151" t="inlineStr">
         <is>
-          <t>2026-10-01(목)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="B75" s="151" t="inlineStr">
         <is>
-          <t>6단계</t>
+          <t>4단계</t>
         </is>
       </c>
       <c r="C75" s="158" t="inlineStr">
@@ -12653,12 +12851,12 @@
       </c>
       <c r="D75" s="153" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>청소·시설 관리</t>
         </is>
       </c>
       <c r="E75" s="154" t="inlineStr">
         <is>
-          <t>Vercel+Render+Supabase 스테이징=프로덕션 서비스 생성(뼈대 프로젝트로 CORS/env 연결 테스트, 10/8에 그대로 정식승격)</t>
+          <t>Empty State/에러처리 청소·체크인 화면 반영</t>
         </is>
       </c>
       <c r="F75" s="155" t="inlineStr">
@@ -12668,34 +12866,34 @@
       </c>
       <c r="G75" s="154" t="inlineStr">
         <is>
-          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
+          <t>frontend/src/pages/Cleaning.jsx</t>
         </is>
       </c>
       <c r="H75" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
         </is>
       </c>
       <c r="I75" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J75" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
         </is>
       </c>
     </row>
     <row r="76" ht="39.75" customHeight="1" s="89">
       <c r="A76" s="151" t="inlineStr">
         <is>
-          <t>2026-10-01(목)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="B76" s="151" t="inlineStr">
         <is>
-          <t>6단계</t>
+          <t>4단계</t>
         </is>
       </c>
       <c r="C76" s="158" t="inlineStr">
@@ -12705,12 +12903,12 @@
       </c>
       <c r="D76" s="153" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>비대면 체크인</t>
         </is>
       </c>
       <c r="E76" s="154" t="inlineStr">
         <is>
-          <t>.env.production 환경변수 설정(Vercel/Render/Supabase 키 분리)</t>
+          <t>스마트락 100% Mock 확정 + '시뮬레이션' 뱃지 표시</t>
         </is>
       </c>
       <c r="F76" s="155" t="inlineStr">
@@ -12720,29 +12918,29 @@
       </c>
       <c r="G76" s="154" t="inlineStr">
         <is>
-          <t>backend/.env.production, frontend/.env.production</t>
+          <t>backend/app/services/doorlock_mock.py</t>
         </is>
       </c>
       <c r="H76" s="154" t="inlineStr">
         <is>
-          <t>JWT_SECRET_KEY를 실제 값으로 교체(기본값 change-me-in-production 방치 시 토큰 위조 가능). CORS_ORIGINS에 Vercel 배포 도메인 추가(현재 localhost:5173만 허용). SUPABASE_DATABASE_URL 설정.</t>
+          <t>1개도 실연동 시도하지 않고 개발 착수부터 100% Mock으로 확정(시간 확보)</t>
         </is>
       </c>
       <c r="I76" s="153" t="inlineStr">
         <is>
-          <t>.env.production은 커밋하지 않는다(.gitignore 확인). 실제 값은 Vercel·Render 대시보드 환경변수로 주입한다.</t>
+          <t>화면에 '시뮬레이션'임을 명확히 표시해야 함 — 실제 연동처럼 보이면 심사 시 오해 소지</t>
         </is>
       </c>
       <c r="J76" s="153" t="inlineStr">
         <is>
-          <t>배포본에서 로그인 성공 여부와 프론트→백엔드 API 호출이 CORS 오류 없이 되는지 확인</t>
+          <t>화면에 Mock 뱃지가 육안으로 확인되는지</t>
         </is>
       </c>
     </row>
     <row r="77" ht="39.75" customHeight="1" s="89">
       <c r="A77" s="151" t="inlineStr">
         <is>
-          <t>2026-10-01(목)</t>
+          <t>2026-09-26(토)</t>
         </is>
       </c>
       <c r="B77" s="151" t="inlineStr">
@@ -12757,12 +12955,12 @@
       </c>
       <c r="D77" s="153" t="inlineStr">
         <is>
-          <t>청소·시설 관리</t>
+          <t>비대면 체크인</t>
         </is>
       </c>
       <c r="E77" s="153" t="inlineStr">
         <is>
-          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
+          <t>Mock 락 상태 대시보드(잠김/열림/배터리)</t>
         </is>
       </c>
       <c r="F77" s="155" t="inlineStr">
@@ -12772,81 +12970,81 @@
       </c>
       <c r="G77" s="154" t="inlineStr">
         <is>
-          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="H77" s="153" t="inlineStr">
         <is>
-          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
+          <t>Mock임을 화면에서 명확히 알 수 있게 한다</t>
         </is>
       </c>
       <c r="I77" s="153" t="inlineStr">
         <is>
-          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
+          <t>실제 연동처럼 보이는 문구나 UI를 쓰지 않는다</t>
         </is>
       </c>
       <c r="J77" s="153" t="inlineStr">
         <is>
-          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
+          <t>화면에 시뮬레이션 표시가 있는지 육안 확인</t>
         </is>
       </c>
     </row>
     <row r="78" ht="39.75" customHeight="1" s="89">
       <c r="A78" s="151" t="inlineStr">
         <is>
-          <t>2026-10-01(목)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="B78" s="151" t="inlineStr">
         <is>
-          <t>5단계</t>
+          <t>4단계</t>
         </is>
       </c>
       <c r="C78" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D78" s="153" t="inlineStr">
         <is>
-          <t>컴플라이언스</t>
+          <t>청소·시설 관리</t>
         </is>
       </c>
       <c r="E78" s="153" t="inlineStr">
         <is>
-          <t>개인정보 최소수집 원칙 점검(게스트데이터-RAG데이터 분리 확인)</t>
+          <t>문자API(알리고 등) 청소업체 알림 자동발송</t>
         </is>
       </c>
       <c r="F78" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G78" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/rag.py</t>
+          <t>backend/app/services/sms.py</t>
         </is>
       </c>
       <c r="H78" s="154" t="inlineStr">
         <is>
-          <t>RAG검색(로컬벡터, 비용0) → Claude 1회 통합호출로 분류+위험도+다국어+근거 동시반환</t>
+          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
         </is>
       </c>
       <c r="I78" s="153" t="inlineStr">
         <is>
-          <t>멀티스텝으로 쪼개면 같은 컨텍스트를 반복 전송해 비용 급증. property_id 스코프 격리 누락시 교차오답(치명적 버그) 발생. 임베딩 모델 확정 시 EMBEDDING_DIM(현재 384, all-MiniLM-L6-v2 가정값)이 실제 선택 모델과 일치하는지 재확인 — 다르면 컬럼 마이그레이션 1회 필요</t>
+          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J78" s="153" t="inlineStr">
         <is>
-          <t>숙소A/B에 동일 질문을 던져서 서로 다른 정답이 나오는지, 로그상 문의 1건당 Claude 호출이 1~2회인지 확인</t>
+          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
         </is>
       </c>
     </row>
     <row r="79" ht="39.75" customHeight="1" s="89">
       <c r="A79" s="151" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="B79" s="151" t="inlineStr">
@@ -12856,7 +13054,7 @@
       </c>
       <c r="C79" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D79" s="153" t="inlineStr">
@@ -12866,39 +13064,39 @@
       </c>
       <c r="E79" s="153" t="inlineStr">
         <is>
-          <t>청소 상태머신 구현(PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED/ISSUE)</t>
+          <t>체크리스트+사진업로드 완료확인(VERIFIED 단계)</t>
         </is>
       </c>
       <c r="F79" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G79" s="154" t="inlineStr">
         <is>
-          <t>backend/app/models/cleaning.py</t>
+          <t>frontend/src/pages/Cleaning.jsx</t>
         </is>
       </c>
       <c r="H79" s="154" t="inlineStr">
         <is>
-          <t>PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED/ISSUE 순서 준수</t>
+          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
         </is>
       </c>
       <c r="I79" s="154" t="inlineStr">
         <is>
-          <t>COMPLETED와 VERIFIED 둘 다 '완료'로 취급하지 않으면 Action Center가 VERIFIED건까지 긴급알림으로 오탐</t>
+          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J79" s="154" t="inlineStr">
         <is>
-          <t>VERIFIED 상태의 청소건이 Action Center 긴급알림에 안 잡히는지 확인</t>
+          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
         </is>
       </c>
     </row>
     <row r="80" ht="39.75" customHeight="1" s="89">
       <c r="A80" s="151" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-28(월)</t>
         </is>
       </c>
       <c r="B80" s="151" t="inlineStr">
@@ -12908,7 +13106,7 @@
       </c>
       <c r="C80" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D80" s="153" t="inlineStr">
@@ -12918,17 +13116,17 @@
       </c>
       <c r="E80" s="153" t="inlineStr">
         <is>
-          <t>예약변경시 청소시간 자동 재계산 로직</t>
+          <t>호스텔 객실(Room)단위 정비 체크리스트 + 비품부족 체크박스</t>
         </is>
       </c>
       <c r="F80" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G80" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/cleaning.py</t>
+          <t>frontend/src/pages/Cleaning.jsx</t>
         </is>
       </c>
       <c r="H80" s="153" t="inlineStr">
@@ -12950,59 +13148,59 @@
     <row r="81" ht="39.75" customHeight="1" s="89">
       <c r="A81" s="151" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-29(화)</t>
         </is>
       </c>
       <c r="B81" s="151" t="inlineStr">
         <is>
-          <t>5단계</t>
+          <t>4단계</t>
         </is>
       </c>
       <c r="C81" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>신규작성</t>
         </is>
       </c>
       <c r="D81" s="153" t="inlineStr">
         <is>
-          <t>정산 리포트</t>
+          <t>청소·시설 관리</t>
         </is>
       </c>
       <c r="E81" s="153" t="inlineStr">
         <is>
-          <t>데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
+          <t>✅ 4단계 검증: 체크아웃→청소생성→상태전이 전체 흐름 1회 시뮬레이션</t>
         </is>
       </c>
       <c r="F81" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude(대화보조)</t>
         </is>
       </c>
       <c r="G81" s="154" t="inlineStr">
         <is>
-          <t>backend/scripts/seed_demo.py</t>
+          <t>docs/3rd_host_ai_db_spec_v1.md (상태전이 섹션 추가)</t>
         </is>
       </c>
       <c r="H81" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
         </is>
       </c>
       <c r="I81" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J81" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
         </is>
       </c>
     </row>
     <row r="82" ht="39.75" customHeight="1" s="89">
       <c r="A82" s="151" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-09-29(화)</t>
         </is>
       </c>
       <c r="B82" s="151" t="inlineStr">
@@ -13012,7 +13210,7 @@
       </c>
       <c r="C82" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D82" s="153" t="inlineStr">
@@ -13022,17 +13220,17 @@
       </c>
       <c r="E82" s="153" t="inlineStr">
         <is>
-          <t>시드 스크립트 실행 및 데이터 정상 반영 확인</t>
+          <t>채널별 수수료 템플릿 설계(Airbnb 15.5%, Booking.com 15~18% 등)</t>
         </is>
       </c>
       <c r="F82" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G82" s="154" t="inlineStr">
         <is>
-          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
+          <t>backend/app/services/settlement.py</t>
         </is>
       </c>
       <c r="H82" s="153" t="inlineStr">
@@ -13054,12 +13252,12 @@
     <row r="83" ht="39.75" customHeight="1" s="89">
       <c r="A83" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-30(수)</t>
         </is>
       </c>
       <c r="B83" s="151" t="inlineStr">
         <is>
-          <t>4단계</t>
+          <t>5단계</t>
         </is>
       </c>
       <c r="C83" s="158" t="inlineStr">
@@ -13069,12 +13267,12 @@
       </c>
       <c r="D83" s="153" t="inlineStr">
         <is>
-          <t>청소·시설 관리</t>
+          <t>정산 리포트</t>
         </is>
       </c>
       <c r="E83" s="153" t="inlineStr">
         <is>
-          <t>문자API(알리고 등) 청소업체 알림 자동발송</t>
+          <t>1단계 자동추정 로직(Room 기본단가×박수-수수료)</t>
         </is>
       </c>
       <c r="F83" s="155" t="inlineStr">
@@ -13084,34 +13282,34 @@
       </c>
       <c r="G83" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/sms.py</t>
+          <t>backend/app/services/settlement.py</t>
         </is>
       </c>
       <c r="H83" s="153" t="inlineStr">
         <is>
-          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
+          <t>모든 금액이 추정치임을 UI에서 명확히 구분 표시한다</t>
         </is>
       </c>
       <c r="I83" s="153" t="inlineStr">
         <is>
-          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
+          <t>실제 결제 확정 금액으로 착각되지 않게 financial_status를 반드시 노출</t>
         </is>
       </c>
       <c r="J83" s="153" t="inlineStr">
         <is>
-          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
+          <t>예상/확정/수동수정 뱃지가 실제로 다르게 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="84" ht="39.75" customHeight="1" s="89">
       <c r="A84" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-09-30(수)</t>
         </is>
       </c>
       <c r="B84" s="151" t="inlineStr">
         <is>
-          <t>4단계</t>
+          <t>5단계</t>
         </is>
       </c>
       <c r="C84" s="158" t="inlineStr">
@@ -13121,12 +13319,12 @@
       </c>
       <c r="D84" s="153" t="inlineStr">
         <is>
-          <t>청소·시설 관리</t>
+          <t>정산 리포트</t>
         </is>
       </c>
       <c r="E84" s="153" t="inlineStr">
         <is>
-          <t>체크리스트+사진업로드 완료확인(VERIFIED 단계)</t>
+          <t>취소/환불 반영 로직(refund_status 연동, 매출 자동제외)</t>
         </is>
       </c>
       <c r="F84" s="155" t="inlineStr">
@@ -13136,133 +13334,133 @@
       </c>
       <c r="G84" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Cleaning.jsx</t>
+          <t>backend/app/services/settlement.py</t>
         </is>
       </c>
       <c r="H84" s="153" t="inlineStr">
         <is>
-          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
+          <t>모든 금액이 추정치임을 UI에서 명확히 구분 표시한다</t>
         </is>
       </c>
       <c r="I84" s="153" t="inlineStr">
         <is>
-          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
+          <t>실제 결제 확정 금액으로 착각되지 않게 financial_status를 반드시 노출</t>
         </is>
       </c>
       <c r="J84" s="153" t="inlineStr">
         <is>
-          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
+          <t>예상/확정/수동수정 뱃지가 실제로 다르게 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="85" ht="39.75" customHeight="1" s="89">
       <c r="A85" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-10-01(목)</t>
         </is>
       </c>
       <c r="B85" s="151" t="inlineStr">
         <is>
-          <t>4단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C85" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D85" s="153" t="inlineStr">
         <is>
-          <t>청소·시설 관리</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E85" s="153" t="inlineStr">
         <is>
-          <t>호스텔 객실(Room)단위 정비 체크리스트 + 비품부족 체크박스</t>
+          <t>Vercel+Render+Supabase 스테이징=프로덕션 서비스 생성(뼈대 프로젝트로 CORS/env 연결 테스트, 10/8에 그대로 정식승격)</t>
         </is>
       </c>
       <c r="F85" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G85" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Cleaning.jsx</t>
+          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
         </is>
       </c>
       <c r="H85" s="153" t="inlineStr">
         <is>
-          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I85" s="153" t="inlineStr">
         <is>
-          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J85" s="153" t="inlineStr">
         <is>
-          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
     <row r="86" ht="39.75" customHeight="1" s="89">
       <c r="A86" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-10-01(목)</t>
         </is>
       </c>
       <c r="B86" s="151" t="inlineStr">
         <is>
-          <t>4단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C86" s="156" t="inlineStr">
         <is>
-          <t>신규작성</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D86" s="153" t="inlineStr">
         <is>
-          <t>청소·시설 관리</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E86" s="154" t="inlineStr">
         <is>
-          <t>✅ 4단계 검증: 체크아웃→청소생성→상태전이 전체 흐름 1회 시뮬레이션</t>
+          <t>.env.production 환경변수 설정(Vercel/Render/Supabase 키 분리)</t>
         </is>
       </c>
       <c r="F86" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude(대화보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G86" s="154" t="inlineStr">
         <is>
-          <t>docs/3rd_host_ai_db_spec_v1.md (상태전이 섹션 추가)</t>
+          <t>backend/.env.production, frontend/.env.production</t>
         </is>
       </c>
       <c r="H86" s="153" t="inlineStr">
         <is>
-          <t>상태머신 순서(PENDING~VERIFIED/ISSUE)를 정확히 지킨다</t>
+          <t>JWT_SECRET_KEY를 실제 값으로 교체(기본값 change-me-in-production 방치 시 토큰 위조 가능). CORS_ORIGINS에 Vercel 배포 도메인 추가(현재 localhost:5173만 허용). SUPABASE_DATABASE_URL 설정.</t>
         </is>
       </c>
       <c r="I86" s="153" t="inlineStr">
         <is>
-          <t>체크아웃 이벤트당 청소작업이 중복 생성되지 않게 한다</t>
+          <t>.env.production은 커밋하지 않는다(.gitignore 확인). 실제 값은 Vercel·Render 대시보드 환경변수로 주입한다.</t>
         </is>
       </c>
       <c r="J86" s="153" t="inlineStr">
         <is>
-          <t>상태 전이를 하나씩 실제로 눌러보며 순서대로 넘어가는지 확인</t>
+          <t>배포본에서 로그인 성공 여부와 프론트→백엔드 API 호출이 CORS 오류 없이 되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="87" ht="39.75" customHeight="1" s="89">
       <c r="A87" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-01(목)</t>
         </is>
       </c>
       <c r="B87" s="151" t="inlineStr">
@@ -13272,49 +13470,49 @@
       </c>
       <c r="C87" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D87" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>컴플라이언스</t>
         </is>
       </c>
       <c r="E87" s="154" t="inlineStr">
         <is>
-          <t>Mock UI '시뮬레이션' 뱃지 통일 적용(가격반영/OTA메시징)</t>
+          <t>개인정보 최소수집 원칙 점검(게스트데이터-RAG데이터 분리 확인)</t>
         </is>
       </c>
       <c r="F87" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G87" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/components/MockBadge.jsx</t>
+          <t>backend/app/services/rag.py</t>
         </is>
       </c>
       <c r="H87" s="154" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>RAG검색(로컬벡터, 비용0) → Claude 1회 통합호출로 분류+위험도+다국어+근거 동시반환</t>
         </is>
       </c>
       <c r="I87" s="153" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>멀티스텝으로 쪼개면 같은 컨텍스트를 반복 전송해 비용 급증. property_id 스코프 격리 누락시 교차오답(치명적 버그) 발생. 임베딩 모델 확정 시 EMBEDDING_DIM(현재 384, all-MiniLM-L6-v2 가정값)이 실제 선택 모델과 일치하는지 재확인 — 다르면 컬럼 마이그레이션 1회 필요</t>
         </is>
       </c>
       <c r="J87" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>숙소A/B에 동일 질문을 던져서 서로 다른 정답이 나오는지, 로그상 문의 1건당 Claude 호출이 1~2회인지 확인</t>
         </is>
       </c>
     </row>
     <row r="88" ht="39.75" customHeight="1" s="89">
       <c r="A88" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B88" s="151" t="inlineStr">
@@ -13334,7 +13532,7 @@
       </c>
       <c r="E88" s="153" t="inlineStr">
         <is>
-          <t>채널별 수수료 템플릿 설계(Airbnb 15.5%, Booking.com 15~18% 등)</t>
+          <t>데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
         </is>
       </c>
       <c r="F88" s="155" t="inlineStr">
@@ -13344,29 +13542,29 @@
       </c>
       <c r="G88" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/settlement.py</t>
+          <t>backend/scripts/seed_demo.py</t>
         </is>
       </c>
       <c r="H88" s="153" t="inlineStr">
         <is>
-          <t>모든 금액이 추정치임을 UI에서 명확히 구분 표시한다</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I88" s="153" t="inlineStr">
         <is>
-          <t>실제 결제 확정 금액으로 착각되지 않게 financial_status를 반드시 노출</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J88" s="153" t="inlineStr">
         <is>
-          <t>예상/확정/수동수정 뱃지가 실제로 다르게 표시되는지 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
     <row r="89" ht="39.75" customHeight="1" s="89">
       <c r="A89" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B89" s="151" t="inlineStr">
@@ -13386,7 +13584,7 @@
       </c>
       <c r="E89" s="154" t="inlineStr">
         <is>
-          <t>1단계 자동추정 로직(Room 기본단가×박수-수수료)</t>
+          <t>시드 스크립트 실행 및 데이터 정상 반영 확인</t>
         </is>
       </c>
       <c r="F89" s="155" t="inlineStr">
@@ -13396,7 +13594,7 @@
       </c>
       <c r="G89" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/settlement.py</t>
+          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
         </is>
       </c>
       <c r="H89" s="153" t="inlineStr">
@@ -13418,7 +13616,7 @@
     <row r="90" ht="39.75" customHeight="1" s="89">
       <c r="A90" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B90" s="151" t="inlineStr">
@@ -13470,7 +13668,7 @@
     <row r="91" ht="39.75" customHeight="1" s="89">
       <c r="A91" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B91" s="151" t="inlineStr">
@@ -13522,7 +13720,7 @@
     <row r="92" ht="39.75" customHeight="1" s="89">
       <c r="A92" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B92" s="151" t="inlineStr">
@@ -13542,7 +13740,7 @@
       </c>
       <c r="E92" s="153" t="inlineStr">
         <is>
-          <t>취소/환불 반영 로직(refund_status 연동, 매출 자동제외)</t>
+          <t>채널별/숙소별/월별 집계 + financial_status 뱃지 표시</t>
         </is>
       </c>
       <c r="F92" s="155" t="inlineStr">
@@ -13574,7 +13772,7 @@
     <row r="93" ht="39.75" customHeight="1" s="89">
       <c r="A93" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B93" s="151" t="inlineStr">
@@ -13589,12 +13787,12 @@
       </c>
       <c r="D93" s="153" t="inlineStr">
         <is>
-          <t>정산 리포트</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E93" s="153" t="inlineStr">
         <is>
-          <t>중간 회귀체크포인트2: 4~5단계 진행분 재확인(청소→정산 흐름 재실행)</t>
+          <t>Mock UI '시뮬레이션' 뱃지 통일 적용(가격반영/OTA메시징)</t>
         </is>
       </c>
       <c r="F93" s="155" t="inlineStr">
@@ -13604,29 +13802,29 @@
       </c>
       <c r="G93" s="154" t="inlineStr">
         <is>
-          <t>backend/tests/test_integration_2.py</t>
+          <t>frontend/src/components/MockBadge.jsx</t>
         </is>
       </c>
       <c r="H93" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I93" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J93" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="94" ht="39.75" customHeight="1" s="89">
       <c r="A94" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B94" s="151" t="inlineStr">
@@ -13636,49 +13834,49 @@
       </c>
       <c r="C94" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D94" s="153" t="inlineStr">
         <is>
-          <t>정산 리포트</t>
+          <t>알림·액션센터</t>
         </is>
       </c>
       <c r="E94" s="153" t="inlineStr">
         <is>
-          <t>채널별/숙소별/월별 집계 + financial_status 뱃지 표시</t>
+          <t>Action Center 규칙기반 트리거 구현(최종스펙 규칙표 그대로)</t>
         </is>
       </c>
       <c r="F94" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G94" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/settlement.py</t>
+          <t>backend/app/services/action_center.py</t>
         </is>
       </c>
       <c r="H94" s="153" t="inlineStr">
         <is>
-          <t>모든 금액이 추정치임을 UI에서 명확히 구분 표시한다</t>
+          <t>100% 규칙(시간+상태)기반 — AI가 위험을 판단하는 기능이 절대 아님</t>
         </is>
       </c>
       <c r="I94" s="153" t="inlineStr">
         <is>
-          <t>실제 결제 확정 금액으로 착각되지 않게 financial_status를 반드시 노출</t>
+          <t>check_in은 DATE라 시간정보가 없음 — checkin_time과 합산해야 'N시간 전' 계산이 실제로 가능(v1.1에서 필드 추가됨)</t>
         </is>
       </c>
       <c r="J94" s="153" t="inlineStr">
         <is>
-          <t>예상/확정/수동수정 뱃지가 실제로 다르게 표시되는지 확인</t>
+          <t>규칙표(🔴🟡🟢)대로 정확히 분류되는지 실제 예약데이터로 재현해서 확인</t>
         </is>
       </c>
     </row>
     <row r="95" ht="39.75" customHeight="1" s="89">
       <c r="A95" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B95" s="151" t="inlineStr">
@@ -13693,12 +13891,12 @@
       </c>
       <c r="D95" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>알림·액션센터</t>
         </is>
       </c>
       <c r="E95" s="153" t="inlineStr">
         <is>
-          <t>공휴일/지역축제 공공데이터 API 연동 추천가 로직</t>
+          <t>🔴🟡🟢 통합 위젯 대시보드 구현</t>
         </is>
       </c>
       <c r="F95" s="155" t="inlineStr">
@@ -13708,29 +13906,29 @@
       </c>
       <c r="G95" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/pricing.py</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="H95" s="154" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>100% 규칙기반, AI 판단이 절대 개입하지 않는다</t>
         </is>
       </c>
       <c r="I95" s="153" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>같은 이벤트가 반복돼도 알림이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J95" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>규칙표대로 🔴🟡🟢이 정확히 분류되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="96" ht="39.75" customHeight="1" s="89">
       <c r="A96" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B96" s="151" t="inlineStr">
@@ -13740,49 +13938,49 @@
       </c>
       <c r="C96" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D96" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>알림·액션센터</t>
         </is>
       </c>
       <c r="E96" s="153" t="inlineStr">
         <is>
-          <t>예약임박도·잔여객실 반영(기존 iCal데이터 활용)</t>
+          <t>각 이벤트 소스 연결(예약·청소·AI승인·서류만료·정산)</t>
         </is>
       </c>
       <c r="F96" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G96" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ical_sync.py</t>
+          <t>backend/app/services/action_center.py</t>
         </is>
       </c>
       <c r="H96" s="154" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I96" s="153" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J96" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
     <row r="97" ht="39.75" customHeight="1" s="89">
       <c r="A97" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B97" s="151" t="inlineStr">
@@ -13792,49 +13990,49 @@
       </c>
       <c r="C97" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D97" s="153" t="inlineStr">
         <is>
-          <t>알림·액션센터</t>
+          <t>정산 리포트</t>
         </is>
       </c>
       <c r="E97" s="154" t="inlineStr">
         <is>
-          <t>Action Center 규칙기반 트리거 구현(최종스펙 규칙표 그대로)</t>
+          <t>중간 회귀체크포인트2: 4~5단계 진행분 재확인(청소→정산 흐름 재실행)</t>
         </is>
       </c>
       <c r="F97" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G97" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/action_center.py</t>
+          <t>backend/tests/test_integration_2.py</t>
         </is>
       </c>
       <c r="H97" s="154" t="inlineStr">
         <is>
-          <t>100% 규칙(시간+상태)기반 — AI가 위험을 판단하는 기능이 절대 아님</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I97" s="154" t="inlineStr">
         <is>
-          <t>check_in은 DATE라 시간정보가 없음 — checkin_time과 합산해야 'N시간 전' 계산이 실제로 가능(v1.1에서 필드 추가됨)</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J97" s="153" t="inlineStr">
         <is>
-          <t>규칙표(🔴🟡🟢)대로 정확히 분류되는지 실제 예약데이터로 재현해서 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
     <row r="98" ht="39.75" customHeight="1" s="89">
       <c r="A98" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B98" s="151" t="inlineStr">
@@ -13849,12 +14047,12 @@
       </c>
       <c r="D98" s="153" t="inlineStr">
         <is>
-          <t>알림·액션센터</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E98" s="153" t="inlineStr">
         <is>
-          <t>🔴🟡🟢 통합 위젯 대시보드 구현</t>
+          <t>공휴일/지역축제 공공데이터 API 연동 추천가 로직</t>
         </is>
       </c>
       <c r="F98" s="155" t="inlineStr">
@@ -13864,29 +14062,29 @@
       </c>
       <c r="G98" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.tsx</t>
+          <t>backend/app/services/pricing.py</t>
         </is>
       </c>
       <c r="H98" s="154" t="inlineStr">
         <is>
-          <t>100% 규칙기반, AI 판단이 절대 개입하지 않는다</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I98" s="153" t="inlineStr">
         <is>
-          <t>같은 이벤트가 반복돼도 알림이 중복 생성되지 않게 한다</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J98" s="153" t="inlineStr">
         <is>
-          <t>규칙표대로 🔴🟡🟢이 정확히 분류되는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="99" ht="39.75" customHeight="1" s="89">
       <c r="A99" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B99" s="151" t="inlineStr">
@@ -13896,49 +14094,49 @@
       </c>
       <c r="C99" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D99" s="153" t="inlineStr">
         <is>
-          <t>알림·액션센터</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E99" s="153" t="inlineStr">
         <is>
-          <t>각 이벤트 소스 연결(예약·청소·AI승인·서류만료·정산)</t>
+          <t>예약임박도·잔여객실 반영(기존 iCal데이터 활용)</t>
         </is>
       </c>
       <c r="F99" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G99" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/action_center.py</t>
+          <t>backend/app/services/ical_sync.py</t>
         </is>
       </c>
       <c r="H99" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I99" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J99" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="100" ht="39.75" customHeight="1" s="89">
       <c r="A100" s="151" t="inlineStr">
         <is>
-          <t>2026-10-06(화)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B100" s="151" t="inlineStr">
@@ -13990,59 +14188,59 @@
     <row r="101" ht="39.75" customHeight="1" s="89">
       <c r="A101" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B101" s="151" t="inlineStr">
         <is>
-          <t>6단계</t>
+          <t>5단계</t>
         </is>
       </c>
       <c r="C101" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D101" s="153" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E101" s="154" t="inlineStr">
         <is>
-          <t>Clipchamp 10분 더미 영상 내보내기 테스트</t>
+          <t>공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)</t>
         </is>
       </c>
       <c r="F101" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G101" s="153" t="inlineStr">
         <is>
-          <t>외부(Clipchamp)</t>
+          <t>backend/app/services/pricing.py</t>
         </is>
       </c>
       <c r="H101" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>실제 운영 페인포인트(3박이상만 받아 화~금이 비는 문제)를 규칙화 — 평일할인/주말·연휴인상 양방향</t>
         </is>
       </c>
       <c r="I101" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>연휴·공휴일은 시스템이 임의로 계속 인상하면 안 됨 — 방치감지 후 반드시 호스트 승인 거쳐야 함(100% 자동 금지)</t>
         </is>
       </c>
       <c r="J101" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>평일 미예약건은 할인추천, 주말 미예약건은 인상추천이 반대로 나오는지 실데이터로 확인 + 연휴 3일 방치 시 알림만 뜨고 자동조정 안 되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="102" ht="39.75" customHeight="1" s="89">
       <c r="A102" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B102" s="151" t="inlineStr">
@@ -14062,7 +14260,7 @@
       </c>
       <c r="E102" s="153" t="inlineStr">
         <is>
-          <t>공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)</t>
+          <t>추천가+근거 카드 UI, 승인클릭→Mock반영, 하한가 경고</t>
         </is>
       </c>
       <c r="F102" s="155" t="inlineStr">
@@ -14072,29 +14270,29 @@
       </c>
       <c r="G102" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/pricing.py</t>
+          <t>backend/app/services/ai_agent.py</t>
         </is>
       </c>
       <c r="H102" s="153" t="inlineStr">
         <is>
-          <t>실제 운영 페인포인트(3박이상만 받아 화~금이 비는 문제)를 규칙화 — 평일할인/주말·연휴인상 양방향</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I102" s="153" t="inlineStr">
         <is>
-          <t>연휴·공휴일은 시스템이 임의로 계속 인상하면 안 됨 — 방치감지 후 반드시 호스트 승인 거쳐야 함(100% 자동 금지)</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J102" s="153" t="inlineStr">
         <is>
-          <t>평일 미예약건은 할인추천, 주말 미예약건은 인상추천이 반대로 나오는지 실데이터로 확인 + 연휴 3일 방치 시 알림만 뜨고 자동조정 안 되는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="103" ht="39.75" customHeight="1" s="89">
       <c r="A103" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B103" s="151" t="inlineStr">
@@ -14104,49 +14302,49 @@
       </c>
       <c r="C103" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D103" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>컴플라이언스</t>
         </is>
       </c>
       <c r="E103" s="153" t="inlineStr">
         <is>
-          <t>추천가+근거 카드 UI, 승인클릭→Mock반영, 하한가 경고</t>
+          <t>숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기</t>
         </is>
       </c>
       <c r="F103" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G103" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ai_agent.py</t>
+          <t>backend/app/data/checklist_templates.json</t>
         </is>
       </c>
       <c r="H103" s="154" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
         </is>
       </c>
       <c r="I103" s="153" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
         </is>
       </c>
       <c r="J103" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="104" ht="39.75" customHeight="1" s="89">
       <c r="A104" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B104" s="151" t="inlineStr">
@@ -14166,7 +14364,7 @@
       </c>
       <c r="E104" s="153" t="inlineStr">
         <is>
-          <t>숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기</t>
+          <t>업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
         </is>
       </c>
       <c r="F104" s="155" t="inlineStr">
@@ -14198,7 +14396,7 @@
     <row r="105" ht="39.75" customHeight="1" s="89">
       <c r="A105" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B105" s="151" t="inlineStr">
@@ -14208,7 +14406,7 @@
       </c>
       <c r="C105" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D105" s="153" t="inlineStr">
@@ -14218,17 +14416,17 @@
       </c>
       <c r="E105" s="153" t="inlineStr">
         <is>
-          <t>업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
+          <t>EVENT_BASED 변경신고 D+30 카운트다운 로직</t>
         </is>
       </c>
       <c r="F105" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G105" s="154" t="inlineStr">
         <is>
-          <t>backend/app/data/checklist_templates.json</t>
+          <t>backend/app/services/checklist.py</t>
         </is>
       </c>
       <c r="H105" s="153" t="inlineStr">
@@ -14250,7 +14448,7 @@
     <row r="106" ht="39.75" customHeight="1" s="89">
       <c r="A106" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-05(월)</t>
         </is>
       </c>
       <c r="B106" s="151" t="inlineStr">
@@ -14270,7 +14468,7 @@
       </c>
       <c r="E106" s="154" t="inlineStr">
         <is>
-          <t>EVENT_BASED 변경신고 D+30 카운트다운 로직</t>
+          <t>✅ 5단계 검증: 정산 3단계 파이프라인 + 알림센터 트리거 실데이터로 재현</t>
         </is>
       </c>
       <c r="F106" s="155" t="inlineStr">
@@ -14280,76 +14478,64 @@
       </c>
       <c r="G106" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/checklist.py</t>
+          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
         </is>
       </c>
       <c r="H106" s="153" t="inlineStr">
         <is>
-          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I106" s="153" t="inlineStr">
         <is>
-          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J106" s="154" t="inlineStr">
         <is>
-          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
     <row r="107" ht="39.75" customHeight="1" s="89">
       <c r="A107" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-06(화)</t>
         </is>
       </c>
       <c r="B107" s="151" t="inlineStr">
         <is>
-          <t>5단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C107" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>신규작성</t>
         </is>
       </c>
       <c r="D107" s="153" t="inlineStr">
         <is>
-          <t>컴플라이언스</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E107" s="154" t="inlineStr">
         <is>
-          <t>✅ 5단계 검증: 정산 3단계 파이프라인 + 알림센터 트리거 실데이터로 재현</t>
+          <t>발표 슬라이드 초안 작성(구성·화면 캡처·AI Agent Loop 다이어그램)</t>
         </is>
       </c>
       <c r="F107" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G107" s="154" t="inlineStr">
         <is>
-          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
-        </is>
-      </c>
-      <c r="H107" s="153" t="inlineStr">
-        <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
-        </is>
-      </c>
-      <c r="I107" s="154" t="inlineStr">
-        <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
-        </is>
-      </c>
-      <c r="J107" s="153" t="inlineStr">
-        <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
-        </is>
-      </c>
+          <t>발표자료(PPTX)</t>
+        </is>
+      </c>
+      <c r="H107" s="153" t="n"/>
+      <c r="I107" s="154" t="n"/>
+      <c r="J107" s="153" t="n"/>
     </row>
     <row r="108" ht="39.75" customHeight="1" s="89">
       <c r="A108" s="151" t="inlineStr">
@@ -14374,7 +14560,7 @@
       </c>
       <c r="E108" s="153" t="inlineStr">
         <is>
-          <t>영상 대본/콘티 초안 작성(화면 흐름·나레이션 포인트 먼저 잡기, 최종 코드 완성 전에도 가능)</t>
+          <t>Clipchamp 10분 더미 영상 내보내기 테스트</t>
         </is>
       </c>
       <c r="F108" s="155" t="inlineStr">
@@ -14384,7 +14570,7 @@
       </c>
       <c r="G108" s="154" t="inlineStr">
         <is>
-          <t>docs/video_script.md</t>
+          <t>외부(Clipchamp)</t>
         </is>
       </c>
       <c r="H108" s="154" t="inlineStr">
@@ -14406,52 +14592,52 @@
     <row r="109" ht="39.75" customHeight="1" s="89">
       <c r="A109" s="151" t="inlineStr">
         <is>
-          <t>2026-10-08(목)</t>
+          <t>2026-10-07(수)</t>
         </is>
       </c>
       <c r="B109" s="151" t="inlineStr">
         <is>
-          <t>5.5단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C109" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D109" s="153" t="inlineStr">
         <is>
-          <t>통합QA·보안</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E109" s="153" t="inlineStr">
         <is>
-          <t>전체 기능 회귀테스트(예약→청소→AI→정산→알림 전체 플로우 1회 통관)</t>
+          <t>영상 대본/콘티 초안 작성(화면 흐름·나레이션 포인트 먼저 잡기, 최종 코드 완성 전에도 가능)</t>
         </is>
       </c>
       <c r="F109" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G109" s="154" t="inlineStr">
         <is>
-          <t>backend/tests/test_full_flow.py</t>
+          <t>docs/video_script.md</t>
         </is>
       </c>
       <c r="H109" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I109" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J109" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14664,7 @@
       </c>
       <c r="E110" s="153" t="inlineStr">
         <is>
-          <t>예외케이스 전수점검(중복예약/취소/환불/iCal실패/LLM실패/DB실패 에러UI 확인)</t>
+          <t>전체 기능 회귀테스트(예약→청소→AI→정산→알림 전체 플로우 1회 통관)</t>
         </is>
       </c>
       <c r="F110" s="155" t="inlineStr">
@@ -14488,22 +14674,22 @@
       </c>
       <c r="G110" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ical_sync.py</t>
+          <t>backend/tests/test_full_flow.py</t>
         </is>
       </c>
       <c r="H110" s="153" t="inlineStr">
         <is>
-          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I110" s="153" t="inlineStr">
         <is>
-          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J110" s="153" t="inlineStr">
         <is>
-          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14716,7 @@
       </c>
       <c r="E111" s="153" t="inlineStr">
         <is>
-          <t>보안점검: 비밀번호 해시 확인, .env/GitHub secret 노출여부 검색</t>
+          <t>예외케이스 전수점검(중복예약/취소/환불/iCal실패/LLM실패/DB실패 에러UI 확인)</t>
         </is>
       </c>
       <c r="F111" s="155" t="inlineStr">
@@ -14540,7 +14726,7 @@
       </c>
       <c r="G111" s="154" t="inlineStr">
         <is>
-          <t>backend/app/core/security.py</t>
+          <t>backend/app/services/ical_sync.py</t>
         </is>
       </c>
       <c r="H111" s="153" t="inlineStr">
@@ -14582,7 +14768,7 @@
       </c>
       <c r="E112" s="154" t="inlineStr">
         <is>
-          <t>Real/Mock UI 라벨 전수 확인(스마트락/가격반영/OTA메시징 '시뮬레이션' 표시)</t>
+          <t>보안점검: 비밀번호 해시 확인, .env/GitHub secret 노출여부 검색</t>
         </is>
       </c>
       <c r="F112" s="155" t="inlineStr">
@@ -14592,22 +14778,22 @@
       </c>
       <c r="G112" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/doorlock_mock.py</t>
+          <t>backend/app/core/security.py</t>
         </is>
       </c>
       <c r="H112" s="154" t="inlineStr">
         <is>
-          <t>1개도 실연동 시도하지 않고 개발 착수부터 100% Mock으로 확정(시간 확보)</t>
+          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
         </is>
       </c>
       <c r="I112" s="153" t="inlineStr">
         <is>
-          <t>화면에 '시뮬레이션'임을 명확히 표시해야 함 — 실제 연동처럼 보이면 심사 시 오해 소지</t>
+          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
         </is>
       </c>
       <c r="J112" s="153" t="inlineStr">
         <is>
-          <t>화면에 Mock 뱃지가 육안으로 확인되는지</t>
+          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14810,7 @@
       </c>
       <c r="C113" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D113" s="153" t="inlineStr">
@@ -14634,32 +14820,32 @@
       </c>
       <c r="E113" s="154" t="inlineStr">
         <is>
-          <t>README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)</t>
+          <t>Real/Mock UI 라벨 전수 확인(스마트락/가격반영/OTA메시징 '시뮬레이션' 표시)</t>
         </is>
       </c>
       <c r="F113" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G113" s="154" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>backend/app/services/doorlock_mock.py</t>
         </is>
       </c>
       <c r="H113" s="153" t="inlineStr">
         <is>
-          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
+          <t>1개도 실연동 시도하지 않고 개발 착수부터 100% Mock으로 확정(시간 확보)</t>
         </is>
       </c>
       <c r="I113" s="153" t="inlineStr">
         <is>
-          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
+          <t>화면에 '시뮬레이션'임을 명확히 표시해야 함 — 실제 연동처럼 보이면 심사 시 오해 소지</t>
         </is>
       </c>
       <c r="J113" s="153" t="inlineStr">
         <is>
-          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
+          <t>화면에 Mock 뱃지가 육안으로 확인되는지</t>
         </is>
       </c>
     </row>
@@ -14671,47 +14857,47 @@
       </c>
       <c r="B114" s="151" t="inlineStr">
         <is>
-          <t>6단계</t>
+          <t>5.5단계</t>
         </is>
       </c>
       <c r="C114" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D114" s="153" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>통합QA·보안</t>
         </is>
       </c>
       <c r="E114" s="154" t="inlineStr">
         <is>
-          <t>GitHub 저장소 최종정리 + 프로덕션 배포 전환(스테이징→정식)+CORS 최종확인</t>
+          <t>README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)</t>
         </is>
       </c>
       <c r="F114" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G114" s="153" t="inlineStr">
         <is>
-          <t>전체 저장소</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="H114" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
         </is>
       </c>
       <c r="I114" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
         </is>
       </c>
       <c r="J114" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14914,7 @@
       </c>
       <c r="C115" s="156" t="inlineStr">
         <is>
-          <t>신규작성</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D115" s="153" t="inlineStr">
@@ -14738,17 +14924,17 @@
       </c>
       <c r="E115" s="153" t="inlineStr">
         <is>
-          <t>제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
+          <t>GitHub 저장소 최종정리 + 프로덕션 배포 전환(스테이징→정식)+CORS 최종확인</t>
         </is>
       </c>
       <c r="F115" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G115" s="154" t="inlineStr">
         <is>
-          <t>docs/project_plan_draft.md (신규생성)</t>
+          <t>전체 저장소</t>
         </is>
       </c>
       <c r="H115" s="154" t="inlineStr">
@@ -14770,52 +14956,52 @@
     <row r="116" ht="39.75" customHeight="1" s="89">
       <c r="A116" s="151" t="inlineStr">
         <is>
-          <t>2026-10-09(금)</t>
+          <t>2026-10-08(목)</t>
         </is>
       </c>
       <c r="B116" s="151" t="inlineStr">
         <is>
-          <t>5.5단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C116" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>신규작성</t>
         </is>
       </c>
       <c r="D116" s="153" t="inlineStr">
         <is>
-          <t>통합QA·보안</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E116" s="154" t="inlineStr">
         <is>
-          <t>1920x1080 데스크톱+Chrome 기준 화면 확인</t>
+          <t>제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
         </is>
       </c>
       <c r="F116" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G116" s="154" t="inlineStr">
         <is>
-          <t>frontend/ (브라우저 확인, 파일아님)</t>
+          <t>docs/project_plan_draft.md (신규생성)</t>
         </is>
       </c>
       <c r="H116" s="153" t="inlineStr">
         <is>
-          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I116" s="153" t="inlineStr">
         <is>
-          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J116" s="153" t="inlineStr">
         <is>
-          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
@@ -14827,7 +15013,7 @@
       </c>
       <c r="B117" s="151" t="inlineStr">
         <is>
-          <t>6단계</t>
+          <t>5.5단계</t>
         </is>
       </c>
       <c r="C117" s="158" t="inlineStr">
@@ -14837,12 +15023,12 @@
       </c>
       <c r="D117" s="153" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>통합QA·보안</t>
         </is>
       </c>
       <c r="E117" s="154" t="inlineStr">
         <is>
-          <t>Mock/Real 표현 최종점검 + '숙소운영특화 AI Agent' 표현 일관성 점검</t>
+          <t>1920x1080 데스크톱+Chrome 기준 화면 확인</t>
         </is>
       </c>
       <c r="F117" s="155" t="inlineStr">
@@ -14852,22 +15038,22 @@
       </c>
       <c r="G117" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/ (전체 텍스트 검수)</t>
+          <t>frontend/ (브라우저 확인, 파일아님)</t>
         </is>
       </c>
       <c r="H117" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
         </is>
       </c>
       <c r="I117" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
         </is>
       </c>
       <c r="J117" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
         </is>
       </c>
     </row>
@@ -14894,17 +15080,17 @@
       </c>
       <c r="E118" s="153" t="inlineStr">
         <is>
-          <t>발표 슬라이드 최종본 확정(AI Agent Loop 다이어그램 포함)</t>
+          <t>Mock/Real 표현 최종점검 + '숙소운영특화 AI Agent' 표현 일관성 점검</t>
         </is>
       </c>
       <c r="F118" s="155" t="inlineStr">
         <is>
-          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G118" s="154" t="inlineStr">
         <is>
-          <t>docs/presentation.pptx (외부)</t>
+          <t>frontend/src/ (전체 텍스트 검수)</t>
         </is>
       </c>
       <c r="H118" s="154" t="inlineStr">
@@ -14936,7 +15122,7 @@
       </c>
       <c r="C119" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>문서확인</t>
         </is>
       </c>
       <c r="D119" s="153" t="inlineStr">
@@ -14946,7 +15132,7 @@
       </c>
       <c r="E119" s="153" t="inlineStr">
         <is>
-          <t>영상 대본/콘티 최종본 확정(10/7 초안 기반, 실제 화면 캡처 반영)</t>
+          <t>발표 슬라이드 최종본 확정(AI Agent Loop 다이어그램 포함)</t>
         </is>
       </c>
       <c r="F119" s="155" t="inlineStr">
@@ -14956,7 +15142,7 @@
       </c>
       <c r="G119" s="154" t="inlineStr">
         <is>
-          <t>docs/video_script.md</t>
+          <t>docs/presentation.pptx (외부)</t>
         </is>
       </c>
       <c r="H119" s="154" t="inlineStr">
@@ -14988,7 +15174,7 @@
       </c>
       <c r="C120" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>문서확인</t>
         </is>
       </c>
       <c r="D120" s="153" t="inlineStr">
@@ -14998,17 +15184,17 @@
       </c>
       <c r="E120" s="154" t="inlineStr">
         <is>
-          <t>[야간] 화면 녹화 + 음성 나레이션 녹음</t>
+          <t>영상 대본/콘티 최종본 확정(10/7 초안 기반, 실제 화면 캡처 반영)</t>
         </is>
       </c>
       <c r="F120" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="G120" s="153" t="inlineStr">
         <is>
-          <t>외부(녹화 소프트웨어)</t>
+          <t>docs/video_script.md</t>
         </is>
       </c>
       <c r="H120" s="154" t="inlineStr">
@@ -15030,7 +15216,7 @@
     <row r="121" ht="39.75" customHeight="1" s="89">
       <c r="A121" s="151" t="inlineStr">
         <is>
-          <t>2026-10-10(토)</t>
+          <t>2026-10-09(금)</t>
         </is>
       </c>
       <c r="B121" s="151" t="inlineStr">
@@ -15040,7 +15226,7 @@
       </c>
       <c r="C121" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D121" s="153" t="inlineStr">
@@ -15050,17 +15236,17 @@
       </c>
       <c r="E121" s="153" t="inlineStr">
         <is>
-          <t>아침 검토: 전날 녹화분 확인, 재촬영 필요분 파악</t>
+          <t>[야간] 화면 녹화 + 음성 나레이션 녹음</t>
         </is>
       </c>
       <c r="F121" s="155" t="inlineStr">
         <is>
-          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G121" s="153" t="inlineStr">
         <is>
-          <t>외부(전날 녹화된 영상 파일 직접 재생·확인)</t>
+          <t>외부(녹화 소프트웨어)</t>
         </is>
       </c>
       <c r="H121" s="154" t="inlineStr">
@@ -15092,7 +15278,7 @@
       </c>
       <c r="C122" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>문서확인</t>
         </is>
       </c>
       <c r="D122" s="153" t="inlineStr">
@@ -15102,32 +15288,32 @@
       </c>
       <c r="E122" s="154" t="inlineStr">
         <is>
-          <t>[야간] 영상 편집(컷/자막/전환) + 렌더링</t>
+          <t>아침 검토: 전날 녹화분 확인, 재촬영 필요분 파악</t>
         </is>
       </c>
       <c r="F122" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
         </is>
       </c>
       <c r="G122" s="153" t="inlineStr">
         <is>
-          <t>외부(편집 소프트웨어)</t>
+          <t>외부(전날 녹화된 영상 파일 직접 재생·확인)</t>
         </is>
       </c>
       <c r="H122" s="153" t="inlineStr">
         <is>
-          <t>녹화 시점의 코드를 버전 태그로 고정해서 '보여준 화면=제출 코드' 일치를 보장</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I122" s="153" t="inlineStr">
         <is>
-          <t>녹화 후에 코드를 더 고치고 싶은 충동을 참을 것(버전 불일치 위험)</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J122" s="153" t="inlineStr">
         <is>
-          <t>최종 mp4를 다른 플레이어·다른 브라우저에서도 정상 재생되는지 확인</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
@@ -15144,7 +15330,7 @@
       </c>
       <c r="C123" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D123" s="153" t="inlineStr">
@@ -15154,32 +15340,32 @@
       </c>
       <c r="E123" s="153" t="inlineStr">
         <is>
-          <t>최종 포맷/용량 확인 + 백업본 준비 + 최종 제출</t>
+          <t>[야간] 영상 편집(컷/자막/전환) + 렌더링</t>
         </is>
       </c>
       <c r="F123" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G123" s="153" t="inlineStr">
         <is>
-          <t>제출플랫폼(외부)</t>
+          <t>외부(편집 소프트웨어)</t>
         </is>
       </c>
       <c r="H123" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>녹화 시점의 코드를 버전 태그로 고정해서 '보여준 화면=제출 코드' 일치를 보장</t>
         </is>
       </c>
       <c r="I123" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>녹화 후에 코드를 더 고치고 싶은 충동을 참을 것(버전 불일치 위험)</t>
         </is>
       </c>
       <c r="J123" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>최종 mp4를 다른 플레이어·다른 브라우저에서도 정상 재생되는지 확인</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15392,7 @@
       </c>
       <c r="E124" s="153" t="inlineStr">
         <is>
-          <t>✅ 설명문서+소스코드 GitHub 최종 제출(외부마감 10/10)</t>
+          <t>최종 포맷/용량 확인 + 백업본 준비 + 최종 제출</t>
         </is>
       </c>
       <c r="F124" s="155" t="inlineStr">
@@ -15238,12 +15424,12 @@
     <row r="125" ht="39.75" customHeight="1" s="89">
       <c r="A125" s="151" t="inlineStr">
         <is>
-          <t>2026-10-11(일)</t>
+          <t>2026-10-10(토)</t>
         </is>
       </c>
       <c r="B125" s="151" t="inlineStr">
         <is>
-          <t>6.5단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C125" s="158" t="inlineStr">
@@ -15253,12 +15439,12 @@
       </c>
       <c r="D125" s="153" t="inlineStr">
         <is>
-          <t>최종 데모검증</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E125" s="153" t="inlineStr">
         <is>
-          <t>데모 데이터 시드 재실행(DB 초기화+골든패스 데이터 재세팅)</t>
+          <t>✅ 설명문서+소스코드 GitHub 최종 제출(외부마감 10/10)</t>
         </is>
       </c>
       <c r="F125" s="155" t="inlineStr">
@@ -15268,34 +15454,34 @@
       </c>
       <c r="G125" s="154" t="inlineStr">
         <is>
-          <t>backend/scripts/seed_demo.py</t>
+          <t>제출플랫폼(외부)</t>
         </is>
       </c>
       <c r="H125" s="153" t="inlineStr">
         <is>
-          <t>발표 당일 사고 예방이 유일한 목적</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I125" s="153" t="inlineStr">
         <is>
-          <t>시연 직전 반드시 실제 환경에서 리허설한다(로컬 테스트만으로 안심 금지)</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J125" s="153" t="inlineStr">
         <is>
-          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
     <row r="126" ht="39.75" customHeight="1" s="89">
       <c r="A126" s="151" t="inlineStr">
         <is>
-          <t>2026-10-11(일)</t>
+          <t>2026-10-10(토)</t>
         </is>
       </c>
       <c r="B126" s="151" t="inlineStr">
         <is>
-          <t>6.5단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C126" s="158" t="inlineStr">
@@ -15305,12 +15491,12 @@
       </c>
       <c r="D126" s="153" t="inlineStr">
         <is>
-          <t>최종 데모검증</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E126" s="154" t="inlineStr">
         <is>
-          <t>E2E 데모 시나리오 리허설(로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산 1회 실행)</t>
+          <t>소스코드 ZIP 생성(node_modules·.env·__pycache__ 제외 확인)</t>
         </is>
       </c>
       <c r="F126" s="155" t="inlineStr">
@@ -15320,22 +15506,22 @@
       </c>
       <c r="G126" s="154" t="inlineStr">
         <is>
-          <t>docs/demo_scenario.md</t>
+          <t>전체 저장소</t>
         </is>
       </c>
       <c r="H126" s="153" t="inlineStr">
         <is>
-          <t>발표 전 마지막 통관 테스트 — 로그인부터 정산까지 실제로 끊기는 지점이 있는지 확인하는 것이 유일한 목적</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I126" s="154" t="inlineStr">
         <is>
-          <t>로컬 개발환경이 아니라 실제 배포된(Supabase 연결) 환경에서 리허설해야 의미가 있다 — 로컬에서만 통과하고 배포환경에서 다르게 동작할 위험을 놓치면 발표 당일 사고로 이어진다</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J126" s="153" t="inlineStr">
         <is>
-          <t>로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산까지 끊김없이 1회 실행, 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지)</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
@@ -15362,17 +15548,17 @@
       </c>
       <c r="E127" s="153" t="inlineStr">
         <is>
-          <t>예상 Q&amp;A 답변 준비(iCal 선택이유/DB전환이유/AI Agent vs 챗봇 차이 등)</t>
+          <t>데모 데이터 시드 재실행(DB 초기화+골든패스 데이터 재세팅)</t>
         </is>
       </c>
       <c r="F127" s="155" t="inlineStr">
         <is>
-          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G127" s="154" t="inlineStr">
         <is>
-          <t>docs/qna_prep.md</t>
+          <t>backend/scripts/seed_demo.py</t>
         </is>
       </c>
       <c r="H127" s="153" t="inlineStr">
@@ -15414,7 +15600,7 @@
       </c>
       <c r="E128" s="154" t="inlineStr">
         <is>
-          <t>✅ 6.5단계 검증: 배포본 재생·서버 웨이크업·발표 최종 리허설</t>
+          <t>E2E 데모 시나리오 리허설(로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산 1회 실행)</t>
         </is>
       </c>
       <c r="F128" s="155" t="inlineStr">
@@ -15424,87 +15610,248 @@
       </c>
       <c r="G128" s="154" t="inlineStr">
         <is>
-          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
+          <t>docs/demo_scenario.md</t>
         </is>
       </c>
       <c r="H128" s="153" t="inlineStr">
         <is>
+          <t>발표 전 마지막 통관 테스트 — 로그인부터 정산까지 실제로 끊기는 지점이 있는지 확인하는 것이 유일한 목적</t>
+        </is>
+      </c>
+      <c r="I128" s="153" t="inlineStr">
+        <is>
+          <t>로컬 개발환경이 아니라 실제 배포된(Supabase 연결) 환경에서 리허설해야 의미가 있다 — 로컬에서만 통과하고 배포환경에서 다르게 동작할 위험을 놓치면 발표 당일 사고로 이어진다</t>
+        </is>
+      </c>
+      <c r="J128" s="153" t="inlineStr">
+        <is>
+          <t>로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산까지 끊김없이 1회 실행, 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="88" t="inlineStr">
+        <is>
+          <t>2026-10-11(일)</t>
+        </is>
+      </c>
+      <c r="B129" s="88" t="inlineStr">
+        <is>
+          <t>6.5단계</t>
+        </is>
+      </c>
+      <c r="C129" s="88" t="inlineStr">
+        <is>
+          <t>신규작성</t>
+        </is>
+      </c>
+      <c r="D129" s="88" t="inlineStr">
+        <is>
+          <t>최종 데모검증</t>
+        </is>
+      </c>
+      <c r="E129" s="88" t="inlineStr">
+        <is>
+          <t>예상 Q&amp;A 답변 준비(iCal 선택이유/DB전환이유/AI Agent vs 챗봇 차이 등)</t>
+        </is>
+      </c>
+      <c r="F129" s="88" t="inlineStr">
+        <is>
+          <t>본인 직접(콘텐츠 확인/검토, 코드작업 아님)</t>
+        </is>
+      </c>
+      <c r="G129" s="88" t="inlineStr">
+        <is>
+          <t>docs/qna_prep.md</t>
+        </is>
+      </c>
+      <c r="H129" s="88" t="inlineStr">
+        <is>
           <t>발표 당일 사고 예방이 유일한 목적</t>
         </is>
       </c>
-      <c r="I128" s="153" t="inlineStr">
+      <c r="I129" s="88" t="inlineStr">
         <is>
           <t>시연 직전 반드시 실제 환경에서 리허설한다(로컬 테스트만으로 안심 금지)</t>
         </is>
       </c>
-      <c r="J128" s="153" t="inlineStr">
-        <is>
-          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인. 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지, 10/11 리허설 때 반드시 함께 확인)</t>
+      <c r="J129" s="88" t="inlineStr">
+        <is>
+          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="89">
       <c r="A130" s="160" t="inlineStr">
         <is>
-          <t>※ 구분 범례</t>
+          <t>2026-10-11(일)</t>
+        </is>
+      </c>
+      <c r="B130" s="88" t="inlineStr">
+        <is>
+          <t>6.5단계</t>
+        </is>
+      </c>
+      <c r="C130" s="88" t="inlineStr">
+        <is>
+          <t>코드구현</t>
+        </is>
+      </c>
+      <c r="D130" s="88" t="inlineStr">
+        <is>
+          <t>최종 데모검증</t>
+        </is>
+      </c>
+      <c r="E130" s="88" t="inlineStr">
+        <is>
+          <t>✅ 6.5단계 검증: 배포본 재생·서버 웨이크업·발표 최종 리허설</t>
+        </is>
+      </c>
+      <c r="F130" s="88" t="inlineStr">
+        <is>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+        </is>
+      </c>
+      <c r="G130" s="88" t="inlineStr">
+        <is>
+          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
+        </is>
+      </c>
+      <c r="H130" s="88" t="inlineStr">
+        <is>
+          <t>발표 당일 사고 예방이 유일한 목적</t>
+        </is>
+      </c>
+      <c r="I130" s="88" t="inlineStr">
+        <is>
+          <t>시연 직전 반드시 실제 환경에서 리허설한다(로컬 테스트만으로 안심 금지)</t>
+        </is>
+      </c>
+      <c r="J130" s="88" t="inlineStr">
+        <is>
+          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인. 발표영상 실제 재생 확인 포함(음성·화면 끝까지 끊김없이 재생되는지, 10/11 리허설 때 반드시 함께 확인)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="89">
       <c r="A131" s="161" t="inlineStr">
         <is>
-          <t>문서확인</t>
+          <t>2026-10-11(일)</t>
         </is>
       </c>
       <c r="B131" s="162" t="inlineStr">
         <is>
-          <t>이미 DB명세서 등에 작성된 내용을 재확인·체크만</t>
+          <t>6.5단계</t>
+        </is>
+      </c>
+      <c r="C131" s="88" t="inlineStr">
+        <is>
+          <t>코드구현</t>
+        </is>
+      </c>
+      <c r="D131" s="88" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="E131" s="88" t="inlineStr">
+        <is>
+          <t>✅ 발표자료(PPT) PBT 제출(외부마감 10/11)</t>
+        </is>
+      </c>
+      <c r="F131" s="88" t="inlineStr">
+        <is>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+        </is>
+      </c>
+      <c r="G131" s="88" t="inlineStr">
+        <is>
+          <t>제출플랫폼(외부)</t>
+        </is>
+      </c>
+      <c r="H131" s="88" t="inlineStr">
+        <is>
+          <t>발표 당일 사고 예방이 유일한 목적</t>
+        </is>
+      </c>
+      <c r="I131" s="88" t="inlineStr">
+        <is>
+          <t>시연 직전 반드시 실제 환경에서 리허설한다(로컬 테스트만으로 안심 금지)</t>
+        </is>
+      </c>
+      <c r="J131" s="88" t="inlineStr">
+        <is>
+          <t>처음부터 끝까지 실제로 클릭해보며 끊기는 지점이 없는지 확인</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="89">
-      <c r="A132" s="163" t="inlineStr">
-        <is>
-          <t>신규작성</t>
-        </is>
-      </c>
-      <c r="B132" s="162" t="inlineStr">
-        <is>
-          <t>아직 없는 문서를 새로 작성</t>
-        </is>
-      </c>
+      <c r="A132" s="163" t="n"/>
+      <c r="B132" s="162" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1" s="89">
       <c r="A133" s="164" t="inlineStr">
         <is>
-          <t>설정확인</t>
-        </is>
-      </c>
-      <c r="B133" s="162" t="inlineStr">
-        <is>
-          <t>파일이 아닌 클라우드 콘솔 등 외부 설정 확인</t>
-        </is>
-      </c>
+          <t>※ 구분 범례</t>
+        </is>
+      </c>
+      <c r="B133" s="162" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" s="89">
       <c r="A134" s="165" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>문서확인</t>
         </is>
       </c>
       <c r="B134" s="162" t="inlineStr">
         <is>
-          <t>실제 backend/frontend 코드 작성(9/5 이후만 해당)</t>
+          <t>이미 DB명세서 등에 작성된 내용을 재확인·체크만</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="89">
       <c r="A135" s="166" t="inlineStr">
         <is>
+          <t>신규작성</t>
+        </is>
+      </c>
+      <c r="B135" s="162" t="inlineStr">
+        <is>
+          <t>아직 없는 문서를 새로 작성</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="88" t="inlineStr">
+        <is>
+          <t>설정확인</t>
+        </is>
+      </c>
+      <c r="B136" s="88" t="inlineStr">
+        <is>
+          <t>파일이 아닌 클라우드 콘솔 등 외부 설정 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="88" t="inlineStr">
+        <is>
+          <t>코드구현</t>
+        </is>
+      </c>
+      <c r="B137" s="88" t="inlineStr">
+        <is>
+          <t>실제 backend/frontend 코드 작성(9/5 이후만 해당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="88" t="inlineStr">
+        <is>
           <t>설계/콘텐츠</t>
         </is>
       </c>
-      <c r="B135" s="162" t="inlineStr">
+      <c r="B138" s="88" t="inlineStr">
         <is>
           <t>야간 시간대 문서·콘텐츠 초안 작업</t>
         </is>
@@ -15513,11 +15860,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B132:E132"/>
     <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B138:E138"/>
     <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B133:E133"/>
-    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B136:E136"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2427,9 +2427,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="G103" s="135" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-01(목)</t>
         </is>
       </c>
       <c r="H103" s="136" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G104" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="H104" s="126" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="G105" s="125" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="H105" s="126" t="n"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="G119" s="121" t="inlineStr">
         <is>
-          <t>2026-10-08(목)</t>
+          <t>2026-10-06(화)</t>
         </is>
       </c>
       <c r="H119" s="122" t="inlineStr">
@@ -8790,7 +8790,8 @@
       </c>
       <c r="D44" s="150" t="inlineStr">
         <is>
-          <t>□ [신규] 개인정보 최소수집 원칙 점검(게스트데이터-RAG데이터 분리 확인)</t>
+          <t>□ [신규] 개인정보 최소수집 원칙 점검(게스트데이터-RAG데이터 분리 확인)
+□ 숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기</t>
         </is>
       </c>
       <c r="E44" s="148" t="n"/>
@@ -8811,12 +8812,14 @@
           <t>□ [신규] 시드 스크립트 실행 및 데이터 정상 반영 확인
 □ 2단계 일괄확인(Bulk Confirm) UI
 □ 3단계 예외보정(Inline Edit, 차이나는 건만)
-□ 채널별/숙소별/월별 집계 + financial_status 뱃지 표시</t>
+□ 채널별/숙소별/월별 집계 + financial_status 뱃지 표시
+□ EVENT_BASED 변경신고 D+30 카운트다운 로직</t>
         </is>
       </c>
       <c r="D45" s="150" t="inlineStr">
         <is>
-          <t>□ [신규] 데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
+          <t>□ [신규] 데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)
+□ 업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
         </is>
       </c>
       <c r="E45" s="146" t="inlineStr">
@@ -8868,15 +8871,12 @@
 □ [신규] 정산·가격 화면에 로딩/에러/빈상태 UI 적용
 □ [신규] 공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)
 □ 추천가+근거 카드 UI, 승인클릭→Mock반영, 하한가 경고
-□ EVENT_BASED 변경신고 D+30 카운트다운 로직
 □ [검증] ✅ 5단계 검증: 정산 3단계 파이프라인 + 알림센터 트리거 실데이터로 재현</t>
         </is>
       </c>
       <c r="D47" s="145" t="inlineStr">
         <is>
-          <t>□ 예약임박도·잔여객실 반영(기존 iCal데이터 활용)
-□ 숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기
-□ 업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
+          <t>□ 예약임박도·잔여객실 반영(기존 iCal데이터 활용)</t>
         </is>
       </c>
       <c r="E47" s="146" t="inlineStr">
@@ -8903,7 +8903,8 @@
       </c>
       <c r="D48" s="145" t="inlineStr">
         <is>
-          <t>□ [신규] 발표 슬라이드 초안 작성(구성·화면 캡처·AI Agent Loop 다이어그램)</t>
+          <t>□ [신규] 발표 슬라이드 초안 작성(구성·화면 캡처·AI Agent Loop 다이어그램)
+□ [신규] 제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
         </is>
       </c>
       <c r="E48" s="148" t="n"/>
@@ -8958,24 +8959,23 @@
       </c>
       <c r="D50" s="145" t="inlineStr">
         <is>
-          <t>□ [신규] README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)
-□ [신규] 제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
+          <t>□ [신규] README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)</t>
         </is>
       </c>
       <c r="E50" s="146" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="88" t="inlineStr">
         <is>
           <t>2026-10-09(금)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="88" t="inlineStr">
         <is>
           <t>5.5단계,6단계</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="88" t="inlineStr">
         <is>
           <t>□ [신규] 1920x1080 데스크톱+Chrome 기준 화면 확인
 □ Mock/Real 표현 최종점검 + '숙소운영특화 AI Agent' 표현 일관성 점검
@@ -8983,29 +8983,29 @@
 □ 영상 대본/콘티 최종본 확정(10/7 초안 기반, 실제 화면 캡처 반영)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="88" t="inlineStr">
         <is>
           <t>□ [야간] 화면 녹화 + 음성 나레이션 녹음</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="88" t="inlineStr">
         <is>
           <t>🌙 연장근무일(+3h)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="88" t="inlineStr">
         <is>
           <t>2026-10-10(토)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="88" t="inlineStr">
         <is>
           <t>6단계</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="88" t="inlineStr">
         <is>
           <t>□ 아침 검토: 전날 녹화분 확인, 재촬영 필요분 파악
 □ 최종 포맷/용량 확인 + 백업본 준비 + 최종 제출
@@ -9013,24 +9013,24 @@
 □ [신규] 소스코드 ZIP 생성(node_modules·.env·__pycache__ 제외 확인)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="88" t="inlineStr">
         <is>
           <t>□ [야간] 영상 편집(컷/자막/전환) + 렌더링</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="88" t="inlineStr">
         <is>
           <t>2026-10-11(일)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="88" t="inlineStr">
         <is>
           <t>6.5단계</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="88" t="inlineStr">
         <is>
           <t>□ [신규] 데모 데이터 시드 재실행(DB 초기화+골든패스 데이터 재세팅)
 □ [신규] E2E 데모 시나리오 리허설(로그인→대시보드→액션센터→예약확인→AI문의→승인→청소→정산 1회 실행)
@@ -9040,7 +9040,7 @@
 □ [신규] ✅ 발표자료(PPT) PBT 제출(외부마감 10/11)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13512,7 +13512,7 @@
     <row r="88" ht="39.75" customHeight="1" s="89">
       <c r="A88" s="151" t="inlineStr">
         <is>
-          <t>2026-10-02(금)</t>
+          <t>2026-10-01(목)</t>
         </is>
       </c>
       <c r="B88" s="151" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="D88" s="153" t="inlineStr">
         <is>
-          <t>정산 리포트</t>
+          <t>컴플라이언스</t>
         </is>
       </c>
       <c r="E88" s="153" t="inlineStr">
         <is>
-          <t>데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
+          <t>숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기</t>
         </is>
       </c>
       <c r="F88" s="155" t="inlineStr">
@@ -13542,22 +13542,22 @@
       </c>
       <c r="G88" s="154" t="inlineStr">
         <is>
-          <t>backend/scripts/seed_demo.py</t>
+          <t>backend/app/data/checklist_templates.json</t>
         </is>
       </c>
       <c r="H88" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
         </is>
       </c>
       <c r="I88" s="153" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
         </is>
       </c>
       <c r="J88" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C89" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D89" s="153" t="inlineStr">
@@ -13584,32 +13584,32 @@
       </c>
       <c r="E89" s="154" t="inlineStr">
         <is>
-          <t>시드 스크립트 실행 및 데이터 정상 반영 확인</t>
+          <t>데모 시드 데이터 스크립트 작성(호스트1+숙소3+예약15~20건+문의+청소+정산+긴급알림 시나리오, 발표 시점 기준 상대시간(체크인 D-1.5시간 등) 자동계산 로직 포함)</t>
         </is>
       </c>
       <c r="F89" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G89" s="154" t="inlineStr">
         <is>
-          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
+          <t>backend/scripts/seed_demo.py</t>
         </is>
       </c>
       <c r="H89" s="153" t="inlineStr">
         <is>
-          <t>모든 금액이 추정치임을 UI에서 명확히 구분 표시한다</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I89" s="153" t="inlineStr">
         <is>
-          <t>실제 결제 확정 금액으로 착각되지 않게 financial_status를 반드시 노출</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J89" s="153" t="inlineStr">
         <is>
-          <t>예상/확정/수동수정 뱃지가 실제로 다르게 표시되는지 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="E90" s="154" t="inlineStr">
         <is>
-          <t>2단계 일괄확인(Bulk Confirm) UI</t>
+          <t>시드 스크립트 실행 및 데이터 정상 반영 확인</t>
         </is>
       </c>
       <c r="F90" s="155" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G90" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Settlement.jsx</t>
+          <t>backend/ 또는 frontend/ (세부 위치는 해당일 착수시 확정)</t>
         </is>
       </c>
       <c r="H90" s="153" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="E91" s="154" t="inlineStr">
         <is>
-          <t>3단계 예외보정(Inline Edit, 차이나는 건만)</t>
+          <t>2단계 일괄확인(Bulk Confirm) UI</t>
         </is>
       </c>
       <c r="F91" s="155" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="E92" s="153" t="inlineStr">
         <is>
-          <t>채널별/숙소별/월별 집계 + financial_status 뱃지 표시</t>
+          <t>3단계 예외보정(Inline Edit, 차이나는 건만)</t>
         </is>
       </c>
       <c r="F92" s="155" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="G92" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/settlement.py</t>
+          <t>frontend/src/pages/Settlement.jsx</t>
         </is>
       </c>
       <c r="H92" s="153" t="inlineStr">
@@ -13772,7 +13772,7 @@
     <row r="93" ht="39.75" customHeight="1" s="89">
       <c r="A93" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B93" s="151" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="D93" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>정산 리포트</t>
         </is>
       </c>
       <c r="E93" s="153" t="inlineStr">
         <is>
-          <t>Mock UI '시뮬레이션' 뱃지 통일 적용(가격반영/OTA메시징)</t>
+          <t>채널별/숙소별/월별 집계 + financial_status 뱃지 표시</t>
         </is>
       </c>
       <c r="F93" s="155" t="inlineStr">
@@ -13802,29 +13802,29 @@
       </c>
       <c r="G93" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/components/MockBadge.jsx</t>
+          <t>backend/app/services/settlement.py</t>
         </is>
       </c>
       <c r="H93" s="153" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>모든 금액이 추정치임을 UI에서 명확히 구분 표시한다</t>
         </is>
       </c>
       <c r="I93" s="154" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>실제 결제 확정 금액으로 착각되지 않게 financial_status를 반드시 노출</t>
         </is>
       </c>
       <c r="J93" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>예상/확정/수동수정 뱃지가 실제로 다르게 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="94" ht="39.75" customHeight="1" s="89">
       <c r="A94" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B94" s="151" t="inlineStr">
@@ -13839,12 +13839,12 @@
       </c>
       <c r="D94" s="153" t="inlineStr">
         <is>
-          <t>알림·액션센터</t>
+          <t>컴플라이언스</t>
         </is>
       </c>
       <c r="E94" s="153" t="inlineStr">
         <is>
-          <t>Action Center 규칙기반 트리거 구현(최종스펙 규칙표 그대로)</t>
+          <t>업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
         </is>
       </c>
       <c r="F94" s="155" t="inlineStr">
@@ -13854,29 +13854,29 @@
       </c>
       <c r="G94" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/action_center.py</t>
+          <t>backend/app/data/checklist_templates.json</t>
         </is>
       </c>
       <c r="H94" s="153" t="inlineStr">
         <is>
-          <t>100% 규칙(시간+상태)기반 — AI가 위험을 판단하는 기능이 절대 아님</t>
+          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
         </is>
       </c>
       <c r="I94" s="153" t="inlineStr">
         <is>
-          <t>check_in은 DATE라 시간정보가 없음 — checkin_time과 합산해야 'N시간 전' 계산이 실제로 가능(v1.1에서 필드 추가됨)</t>
+          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
         </is>
       </c>
       <c r="J94" s="153" t="inlineStr">
         <is>
-          <t>규칙표(🔴🟡🟢)대로 정확히 분류되는지 실제 예약데이터로 재현해서 확인</t>
+          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="95" ht="39.75" customHeight="1" s="89">
       <c r="A95" s="151" t="inlineStr">
         <is>
-          <t>2026-10-03(토)</t>
+          <t>2026-10-02(금)</t>
         </is>
       </c>
       <c r="B95" s="151" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="D95" s="153" t="inlineStr">
         <is>
-          <t>알림·액션센터</t>
+          <t>컴플라이언스</t>
         </is>
       </c>
       <c r="E95" s="153" t="inlineStr">
         <is>
-          <t>🔴🟡🟢 통합 위젯 대시보드 구현</t>
+          <t>EVENT_BASED 변경신고 D+30 카운트다운 로직</t>
         </is>
       </c>
       <c r="F95" s="155" t="inlineStr">
@@ -13906,22 +13906,22 @@
       </c>
       <c r="G95" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Dashboard.tsx</t>
+          <t>backend/app/services/checklist.py</t>
         </is>
       </c>
       <c r="H95" s="154" t="inlineStr">
         <is>
-          <t>100% 규칙기반, AI 판단이 절대 개입하지 않는다</t>
+          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
         </is>
       </c>
       <c r="I95" s="153" t="inlineStr">
         <is>
-          <t>같은 이벤트가 반복돼도 알림이 중복 생성되지 않게 한다</t>
+          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
         </is>
       </c>
       <c r="J95" s="153" t="inlineStr">
         <is>
-          <t>규칙표대로 🔴🟡🟢이 정확히 분류되는지 확인</t>
+          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
         </is>
       </c>
     </row>
@@ -13943,12 +13943,12 @@
       </c>
       <c r="D96" s="153" t="inlineStr">
         <is>
-          <t>알림·액션센터</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E96" s="153" t="inlineStr">
         <is>
-          <t>각 이벤트 소스 연결(예약·청소·AI승인·서류만료·정산)</t>
+          <t>Mock UI '시뮬레이션' 뱃지 통일 적용(가격반영/OTA메시징)</t>
         </is>
       </c>
       <c r="F96" s="155" t="inlineStr">
@@ -13958,29 +13958,29 @@
       </c>
       <c r="G96" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/action_center.py</t>
+          <t>frontend/src/components/MockBadge.jsx</t>
         </is>
       </c>
       <c r="H96" s="154" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I96" s="153" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J96" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="97" ht="39.75" customHeight="1" s="89">
       <c r="A97" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B97" s="151" t="inlineStr">
@@ -13990,49 +13990,49 @@
       </c>
       <c r="C97" s="159" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D97" s="153" t="inlineStr">
         <is>
-          <t>정산 리포트</t>
+          <t>알림·액션센터</t>
         </is>
       </c>
       <c r="E97" s="154" t="inlineStr">
         <is>
-          <t>중간 회귀체크포인트2: 4~5단계 진행분 재확인(청소→정산 흐름 재실행)</t>
+          <t>Action Center 규칙기반 트리거 구현(최종스펙 규칙표 그대로)</t>
         </is>
       </c>
       <c r="F97" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G97" s="154" t="inlineStr">
         <is>
-          <t>backend/tests/test_integration_2.py</t>
+          <t>backend/app/services/action_center.py</t>
         </is>
       </c>
       <c r="H97" s="154" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>100% 규칙(시간+상태)기반 — AI가 위험을 판단하는 기능이 절대 아님</t>
         </is>
       </c>
       <c r="I97" s="154" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>check_in은 DATE라 시간정보가 없음 — checkin_time과 합산해야 'N시간 전' 계산이 실제로 가능(v1.1에서 필드 추가됨)</t>
         </is>
       </c>
       <c r="J97" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>규칙표(🔴🟡🟢)대로 정확히 분류되는지 실제 예약데이터로 재현해서 확인</t>
         </is>
       </c>
     </row>
     <row r="98" ht="39.75" customHeight="1" s="89">
       <c r="A98" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B98" s="151" t="inlineStr">
@@ -14047,12 +14047,12 @@
       </c>
       <c r="D98" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>알림·액션센터</t>
         </is>
       </c>
       <c r="E98" s="153" t="inlineStr">
         <is>
-          <t>공휴일/지역축제 공공데이터 API 연동 추천가 로직</t>
+          <t>🔴🟡🟢 통합 위젯 대시보드 구현</t>
         </is>
       </c>
       <c r="F98" s="155" t="inlineStr">
@@ -14062,29 +14062,29 @@
       </c>
       <c r="G98" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/pricing.py</t>
+          <t>frontend/src/pages/Dashboard.tsx</t>
         </is>
       </c>
       <c r="H98" s="154" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>100% 규칙기반, AI 판단이 절대 개입하지 않는다</t>
         </is>
       </c>
       <c r="I98" s="153" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>같은 이벤트가 반복돼도 알림이 중복 생성되지 않게 한다</t>
         </is>
       </c>
       <c r="J98" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>규칙표대로 🔴🟡🟢이 정확히 분류되는지 확인</t>
         </is>
       </c>
     </row>
     <row r="99" ht="39.75" customHeight="1" s="89">
       <c r="A99" s="151" t="inlineStr">
         <is>
-          <t>2026-10-05(월)</t>
+          <t>2026-10-03(토)</t>
         </is>
       </c>
       <c r="B99" s="151" t="inlineStr">
@@ -14094,42 +14094,42 @@
       </c>
       <c r="C99" s="158" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D99" s="153" t="inlineStr">
         <is>
-          <t>동적 가격 책정</t>
+          <t>알림·액션센터</t>
         </is>
       </c>
       <c r="E99" s="153" t="inlineStr">
         <is>
-          <t>예약임박도·잔여객실 반영(기존 iCal데이터 활용)</t>
+          <t>각 이벤트 소스 연결(예약·청소·AI승인·서류만료·정산)</t>
         </is>
       </c>
       <c r="F99" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G99" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ical_sync.py</t>
+          <t>backend/app/services/action_center.py</t>
         </is>
       </c>
       <c r="H99" s="153" t="inlineStr">
         <is>
-          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I99" s="154" t="inlineStr">
         <is>
-          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J99" s="153" t="inlineStr">
         <is>
-          <t>추천가와 근거가 함께 표시되는지 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14156,7 @@
       </c>
       <c r="E100" s="153" t="inlineStr">
         <is>
-          <t>정산·가격 화면에 로딩/에러/빈상태 UI 적용</t>
+          <t>중간 회귀체크포인트2: 4~5단계 진행분 재확인(청소→정산 흐름 재실행)</t>
         </is>
       </c>
       <c r="F100" s="155" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="G100" s="154" t="inlineStr">
         <is>
-          <t>frontend/src/components/StateHandler.jsx</t>
+          <t>backend/tests/test_integration_2.py</t>
         </is>
       </c>
       <c r="H100" s="153" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="E101" s="154" t="inlineStr">
         <is>
-          <t>공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)</t>
+          <t>공휴일/지역축제 공공데이터 API 연동 추천가 로직</t>
         </is>
       </c>
       <c r="F101" s="155" t="inlineStr">
@@ -14223,17 +14223,17 @@
       </c>
       <c r="H101" s="154" t="inlineStr">
         <is>
-          <t>실제 운영 페인포인트(3박이상만 받아 화~금이 비는 문제)를 규칙화 — 평일할인/주말·연휴인상 양방향</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I101" s="153" t="inlineStr">
         <is>
-          <t>연휴·공휴일은 시스템이 임의로 계속 인상하면 안 됨 — 방치감지 후 반드시 호스트 승인 거쳐야 함(100% 자동 금지)</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J101" s="153" t="inlineStr">
         <is>
-          <t>평일 미예약건은 할인추천, 주말 미예약건은 인상추천이 반대로 나오는지 실데이터로 확인 + 연휴 3일 방치 시 알림만 뜨고 자동조정 안 되는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="C102" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D102" s="153" t="inlineStr">
@@ -14260,17 +14260,17 @@
       </c>
       <c r="E102" s="153" t="inlineStr">
         <is>
-          <t>추천가+근거 카드 UI, 승인클릭→Mock반영, 하한가 경고</t>
+          <t>예약임박도·잔여객실 반영(기존 iCal데이터 활용)</t>
         </is>
       </c>
       <c r="F102" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G102" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ai_agent.py</t>
+          <t>backend/app/services/ical_sync.py</t>
         </is>
       </c>
       <c r="H102" s="153" t="inlineStr">
@@ -14302,42 +14302,42 @@
       </c>
       <c r="C103" s="158" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D103" s="153" t="inlineStr">
         <is>
-          <t>컴플라이언스</t>
+          <t>정산 리포트</t>
         </is>
       </c>
       <c r="E103" s="153" t="inlineStr">
         <is>
-          <t>숙박업 유형별 체크리스트 정적 JSON 템플릿, 법정명칭 정확표기</t>
+          <t>정산·가격 화면에 로딩/에러/빈상태 UI 적용</t>
         </is>
       </c>
       <c r="F103" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G103" s="154" t="inlineStr">
         <is>
-          <t>backend/app/data/checklist_templates.json</t>
+          <t>frontend/src/components/StateHandler.jsx</t>
         </is>
       </c>
       <c r="H103" s="154" t="inlineStr">
         <is>
-          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I103" s="153" t="inlineStr">
         <is>
-          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J103" s="153" t="inlineStr">
         <is>
-          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
@@ -14354,42 +14354,42 @@
       </c>
       <c r="C104" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D104" s="153" t="inlineStr">
         <is>
-          <t>컴플라이언스</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E104" s="153" t="inlineStr">
         <is>
-          <t>업종별 킬러요건 1~2개 노출(여권보관/수질검사/소방안전관리자 등)</t>
+          <t>공백일 미세조정+성수기 방치감지 배치로직(평일할인/주말·연휴인상, DB명세서 6절)</t>
         </is>
       </c>
       <c r="F104" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G104" s="154" t="inlineStr">
         <is>
-          <t>backend/app/data/checklist_templates.json</t>
+          <t>backend/app/services/pricing.py</t>
         </is>
       </c>
       <c r="H104" s="153" t="inlineStr">
         <is>
-          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
+          <t>실제 운영 페인포인트(3박이상만 받아 화~금이 비는 문제)를 규칙화 — 평일할인/주말·연휴인상 양방향</t>
         </is>
       </c>
       <c r="I104" s="153" t="inlineStr">
         <is>
-          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
+          <t>연휴·공휴일은 시스템이 임의로 계속 인상하면 안 됨 — 방치감지 후 반드시 호스트 승인 거쳐야 함(100% 자동 금지)</t>
         </is>
       </c>
       <c r="J104" s="154" t="inlineStr">
         <is>
-          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
+          <t>평일 미예약건은 할인추천, 주말 미예약건은 인상추천이 반대로 나오는지 실데이터로 확인 + 연휴 3일 방치 시 알림만 뜨고 자동조정 안 되는지 확인</t>
         </is>
       </c>
     </row>
@@ -14411,12 +14411,12 @@
       </c>
       <c r="D105" s="153" t="inlineStr">
         <is>
-          <t>컴플라이언스</t>
+          <t>동적 가격 책정</t>
         </is>
       </c>
       <c r="E105" s="153" t="inlineStr">
         <is>
-          <t>EVENT_BASED 변경신고 D+30 카운트다운 로직</t>
+          <t>추천가+근거 카드 UI, 승인클릭→Mock반영, 하한가 경고</t>
         </is>
       </c>
       <c r="F105" s="155" t="inlineStr">
@@ -14426,22 +14426,22 @@
       </c>
       <c r="G105" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/checklist.py</t>
+          <t>backend/app/services/ai_agent.py</t>
         </is>
       </c>
       <c r="H105" s="153" t="inlineStr">
         <is>
-          <t>법률판단이 아니라 참고용 체크리스트임을 UI에 명시</t>
+          <t>AI가 아니라 규칙기반 추천임을 명확히 한다(과대포장 금지)</t>
         </is>
       </c>
       <c r="I105" s="153" t="inlineStr">
         <is>
-          <t>숙박업 유형별 정교한 법률 로직을 만들지 않는다(범위 초과)</t>
+          <t>가격 실제 반영은 Mock — UI에서 실제 반영된 것처럼 보이지 않게</t>
         </is>
       </c>
       <c r="J105" s="154" t="inlineStr">
         <is>
-          <t>'참고용, 관할 지자체 확인 필요' 문구가 화면에 표시되는지 확인</t>
+          <t>추천가와 근거가 함께 표시되는지 확인</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
     <row r="108" ht="39.75" customHeight="1" s="89">
       <c r="A108" s="151" t="inlineStr">
         <is>
-          <t>2026-10-07(수)</t>
+          <t>2026-10-06(화)</t>
         </is>
       </c>
       <c r="B108" s="151" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="C108" s="159" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>신규작성</t>
         </is>
       </c>
       <c r="D108" s="153" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="E108" s="153" t="inlineStr">
         <is>
-          <t>Clipchamp 10분 더미 영상 내보내기 테스트</t>
+          <t>제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
         </is>
       </c>
       <c r="F108" s="155" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="G108" s="154" t="inlineStr">
         <is>
-          <t>외부(Clipchamp)</t>
+          <t>docs/project_plan_draft.md (신규생성)</t>
         </is>
       </c>
       <c r="H108" s="154" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="E109" s="153" t="inlineStr">
         <is>
-          <t>영상 대본/콘티 초안 작성(화면 흐름·나레이션 포인트 먼저 잡기, 최종 코드 완성 전에도 가능)</t>
+          <t>Clipchamp 10분 더미 영상 내보내기 테스트</t>
         </is>
       </c>
       <c r="F109" s="155" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="G109" s="154" t="inlineStr">
         <is>
-          <t>docs/video_script.md</t>
+          <t>외부(Clipchamp)</t>
         </is>
       </c>
       <c r="H109" s="153" t="inlineStr">
@@ -14644,52 +14644,52 @@
     <row r="110" ht="39.75" customHeight="1" s="89">
       <c r="A110" s="151" t="inlineStr">
         <is>
-          <t>2026-10-08(목)</t>
+          <t>2026-10-07(수)</t>
         </is>
       </c>
       <c r="B110" s="151" t="inlineStr">
         <is>
-          <t>5.5단계</t>
+          <t>6단계</t>
         </is>
       </c>
       <c r="C110" s="158" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D110" s="153" t="inlineStr">
         <is>
-          <t>통합QA·보안</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="E110" s="153" t="inlineStr">
         <is>
-          <t>전체 기능 회귀테스트(예약→청소→AI→정산→알림 전체 플로우 1회 통관)</t>
+          <t>영상 대본/콘티 초안 작성(화면 흐름·나레이션 포인트 먼저 잡기, 최종 코드 완성 전에도 가능)</t>
         </is>
       </c>
       <c r="F110" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G110" s="154" t="inlineStr">
         <is>
-          <t>backend/tests/test_full_flow.py</t>
+          <t>docs/video_script.md</t>
         </is>
       </c>
       <c r="H110" s="153" t="inlineStr">
         <is>
-          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
+          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
         </is>
       </c>
       <c r="I110" s="153" t="inlineStr">
         <is>
-          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
+          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
         </is>
       </c>
       <c r="J110" s="153" t="inlineStr">
         <is>
-          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
+          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="E111" s="153" t="inlineStr">
         <is>
-          <t>예외케이스 전수점검(중복예약/취소/환불/iCal실패/LLM실패/DB실패 에러UI 확인)</t>
+          <t>전체 기능 회귀테스트(예약→청소→AI→정산→알림 전체 플로우 1회 통관)</t>
         </is>
       </c>
       <c r="F111" s="155" t="inlineStr">
@@ -14726,22 +14726,22 @@
       </c>
       <c r="G111" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/ical_sync.py</t>
+          <t>backend/tests/test_full_flow.py</t>
         </is>
       </c>
       <c r="H111" s="153" t="inlineStr">
         <is>
-          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
+          <t>자동추정→일괄확인→예외보정 3단계로 수작업을 최소화(엑셀 수기정산과 다르게 만드는 것이 목표)</t>
         </is>
       </c>
       <c r="I111" s="153" t="inlineStr">
         <is>
-          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
+          <t>iCal에는 결제정보가 없어 모든 금액이 추정치 — financial_status(ESTIMATED/CONFIRMED/MANUALLY_ADJUSTED)로 신뢰도를 반드시 구분표시</t>
         </is>
       </c>
       <c r="J111" s="153" t="inlineStr">
         <is>
-          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
+          <t>전체 예약 중 예외건(할인적용 등)만 수동수정하고 나머지는 1클릭으로 끝나는지 확인</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="E112" s="154" t="inlineStr">
         <is>
-          <t>보안점검: 비밀번호 해시 확인, .env/GitHub secret 노출여부 검색</t>
+          <t>예외케이스 전수점검(중복예약/취소/환불/iCal실패/LLM실패/DB실패 에러UI 확인)</t>
         </is>
       </c>
       <c r="F112" s="155" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="G112" s="154" t="inlineStr">
         <is>
-          <t>backend/app/core/security.py</t>
+          <t>backend/app/services/ical_sync.py</t>
         </is>
       </c>
       <c r="H112" s="154" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="E113" s="154" t="inlineStr">
         <is>
-          <t>Real/Mock UI 라벨 전수 확인(스마트락/가격반영/OTA메시징 '시뮬레이션' 표시)</t>
+          <t>보안점검: 비밀번호 해시 확인, .env/GitHub secret 노출여부 검색</t>
         </is>
       </c>
       <c r="F113" s="155" t="inlineStr">
@@ -14830,22 +14830,22 @@
       </c>
       <c r="G113" s="154" t="inlineStr">
         <is>
-          <t>backend/app/services/doorlock_mock.py</t>
+          <t>backend/app/core/security.py</t>
         </is>
       </c>
       <c r="H113" s="153" t="inlineStr">
         <is>
-          <t>1개도 실연동 시도하지 않고 개발 착수부터 100% Mock으로 확정(시간 확보)</t>
+          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
         </is>
       </c>
       <c r="I113" s="153" t="inlineStr">
         <is>
-          <t>화면에 '시뮬레이션'임을 명확히 표시해야 함 — 실제 연동처럼 보이면 심사 시 오해 소지</t>
+          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
         </is>
       </c>
       <c r="J113" s="153" t="inlineStr">
         <is>
-          <t>화면에 Mock 뱃지가 육안으로 확인되는지</t>
+          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="C114" s="158" t="inlineStr">
         <is>
-          <t>설계/콘텐츠</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D114" s="153" t="inlineStr">
@@ -14872,32 +14872,32 @@
       </c>
       <c r="E114" s="154" t="inlineStr">
         <is>
-          <t>README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)</t>
+          <t>Real/Mock UI 라벨 전수 확인(스마트락/가격반영/OTA메시징 '시뮬레이션' 표시)</t>
         </is>
       </c>
       <c r="F114" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G114" s="153" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>backend/app/services/doorlock_mock.py</t>
         </is>
       </c>
       <c r="H114" s="154" t="inlineStr">
         <is>
-          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
+          <t>1개도 실연동 시도하지 않고 개발 착수부터 100% Mock으로 확정(시간 확보)</t>
         </is>
       </c>
       <c r="I114" s="153" t="inlineStr">
         <is>
-          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
+          <t>화면에 '시뮬레이션'임을 명확히 표시해야 함 — 실제 연동처럼 보이면 심사 시 오해 소지</t>
         </is>
       </c>
       <c r="J114" s="153" t="inlineStr">
         <is>
-          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
+          <t>화면에 Mock 뱃지가 육안으로 확인되는지</t>
         </is>
       </c>
     </row>
@@ -14909,47 +14909,47 @@
       </c>
       <c r="B115" s="151" t="inlineStr">
         <is>
-          <t>6단계</t>
+          <t>5.5단계</t>
         </is>
       </c>
       <c r="C115" s="156" t="inlineStr">
         <is>
-          <t>코드구현</t>
+          <t>설계/콘텐츠</t>
         </is>
       </c>
       <c r="D115" s="153" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>통합QA·보안</t>
         </is>
       </c>
       <c r="E115" s="153" t="inlineStr">
         <is>
-          <t>GitHub 저장소 최종정리 + 프로덕션 배포 전환(스테이징→정식)+CORS 최종확인</t>
+          <t>README.md 작성(소개/아키텍처/스택/설치법/환경변수/Demo계정/Real·Mock범위)</t>
         </is>
       </c>
       <c r="F115" s="155" t="inlineStr">
         <is>
-          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
+          <t>본인 — Gemini(검토·콘텐츠보조)</t>
         </is>
       </c>
       <c r="G115" s="154" t="inlineStr">
         <is>
-          <t>전체 저장소</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="H115" s="154" t="inlineStr">
         <is>
-          <t>Feature Freeze 이후에는 로직 변경 없이 텍스트·설정만 수정</t>
+          <t>배포 전 마지막 방어선 — 여기서 놓치면 발표 중 사고로 직결</t>
         </is>
       </c>
       <c r="I115" s="153" t="inlineStr">
         <is>
-          <t>제출 직전 급하게 뭔가 더 고치려는 유혹을 참는다</t>
+          <t>체크리스트 일부만 하지 말고 전체 시나리오를 빠짐없이 재현</t>
         </is>
       </c>
       <c r="J115" s="153" t="inlineStr">
         <is>
-          <t>최종 산출물(배포본/영상/문서)을 처음부터 끝까지 직접 재생·재확인</t>
+          <t>각 항목을 실제로 테스트해보고 결과를 기록</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="C116" s="158" t="inlineStr">
         <is>
-          <t>신규작성</t>
+          <t>코드구현</t>
         </is>
       </c>
       <c r="D116" s="153" t="inlineStr">
@@ -14976,17 +14976,17 @@
       </c>
       <c r="E116" s="154" t="inlineStr">
         <is>
-          <t>제출용 설명문서 최종본 정리(9/3 기획서 확장판: 배경/주제/기술스택/아키텍처/사용법)</t>
+          <t>GitHub 저장소 최종정리 + 프로덕션 배포 전환(스테이징→정식)+CORS 최종확인</t>
         </is>
       </c>
       <c r="F116" s="155" t="inlineStr">
         <is>
-          <t>본인 — Gemini(검토·콘텐츠보조)</t>
+          <t>본인 — Claude Code(터미널 직접실행 권장)</t>
         </is>
       </c>
       <c r="G116" s="154" t="inlineStr">
         <is>
-          <t>docs/project_plan_draft.md (신규생성)</t>
+          <t>전체 저장소</t>
         </is>
       </c>
       <c r="H116" s="153" t="inlineStr">
@@ -23515,9 +23515,9 @@
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="C216:G216"/>
     <mergeCell ref="C186:F186"/>
+    <mergeCell ref="A230:G230"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="C217:F217"/>
-    <mergeCell ref="A230:G230"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C136:F136"/>
     <mergeCell ref="C210:F210"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7949,7 +7949,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -8147,8 +8146,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="17.35" customHeight="1" s="89">
       <c r="A15" s="142" t="inlineStr">
         <is>
@@ -9193,7 +9190,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="89">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -19228,7 +19224,13 @@
         </is>
       </c>
       <c r="B143" s="184" t="n"/>
-      <c r="C143" s="183" t="n"/>
+      <c r="C143" s="183" t="inlineStr">
+        <is>
+          <t>[상황] 호스트가 채널연결시 iCal URL을 잘못 입력하는 경우가 실제로 자주 발생함
+[동작] ① 잘못된 URL·파싱실패 케이스 감지 ② 명확한 에러 메시지로 안내(재입력 유도)
+[원칙 없었다면] 에러 처리 없이 조용히 실패하면 호스트가 캘린더가 왜 안 뜨는지 원인을 못 찾음</t>
+        </is>
+      </c>
       <c r="D143" s="185" t="n"/>
       <c r="E143" s="185" t="n"/>
       <c r="F143" s="185" t="n"/>
@@ -19552,9 +19554,9 @@
       <c r="B159" s="184" t="n"/>
       <c r="C159" s="183" t="inlineStr">
         <is>
-          <t>[상황] 호스트가 채널연결시 iCal URL을 잘못 입력하는 경우가 실제로 자주 발생함
-[동작] ① 잘못된 URL·파싱실패 케이스 감지 ② 명확한 에러 메시지로 안내(재입력 유도)
-[원칙 없었다면] 에러 처리 없이 조용히 실패하면 호스트가 캘린더가 왜 안 뜨는지 원인을 못 찾음</t>
+          <t>[상황] 새벽에 게스트가 와이파이 비번을 물어봐도 호스트가 매번 직접 답할 순 없음
+[동작] ① 숙소별 RAG 지식베이스 구축(로컬 벡터검색) ② property_id로 숙소간 지식 완전 격리
+[원칙 없었다면] 격리가 없으면 강남 정보가 홍대 게스트에게 잘못 전달되는 교차오답 사고 발생</t>
         </is>
       </c>
       <c r="D159" s="185" t="n"/>
@@ -19716,9 +19718,9 @@
       <c r="B167" s="184" t="n"/>
       <c r="C167" s="183" t="inlineStr">
         <is>
-          <t>[상황] 새벽에 게스트가 와이파이 비번을 물어봐도 호스트가 매번 직접 답할 순 없음
-[동작] ① 숙소별 RAG 지식베이스 구축(로컬 벡터검색) ② property_id로 숙소간 지식 완전 격리
-[원칙 없었다면] 격리가 없으면 강남 정보가 홍대 게스트에게 잘못 전달되는 교차오답 사고 발생</t>
+          <t>[상황] AI 호출이 무한정 반복되면 비용이 통제 불가능하게 폭주할 위험
+[동작] ① 재시도는 개별호출 2회로 제한(1문의당 최대 3회) ② MAX_STEPS로 무한루프 원천 차단
+[원칙 없었다면] 제한이 없으면 API 장애시 재시도가 끝없이 반복되어 순식간에 비용 폭탄</t>
         </is>
       </c>
       <c r="D167" s="185" t="n"/>
@@ -19880,9 +19882,9 @@
       <c r="B175" s="184" t="n"/>
       <c r="C175" s="183" t="inlineStr">
         <is>
-          <t>[상황] AI 호출이 무한정 반복되면 비용이 통제 불가능하게 폭주할 위험
-[동작] ① 재시도는 개별호출 2회로 제한(1문의당 최대 3회) ② MAX_STEPS로 무한루프 원천 차단
-[원칙 없었다면] 제한이 없으면 API 장애시 재시도가 끝없이 반복되어 순식간에 비용 폭탄</t>
+          <t>[상황] 외국인 게스트(영/중/일)가 각자 자기 언어로 문의를 보냄
+[동작] ① 문의 언어 자동감지 ② 감지된 언어로 자동 응답 생성
+[원칙 없었다면] 한국어로만 응답하면 외국인 게스트 응대라는 핵심 가치 자체가 성립 안 함</t>
         </is>
       </c>
       <c r="D175" s="185" t="n"/>
@@ -20044,9 +20046,9 @@
       <c r="B183" s="184" t="n"/>
       <c r="C183" s="183" t="inlineStr">
         <is>
-          <t>[상황] 외국인 게스트(영/중/일)가 각자 자기 언어로 문의를 보냄
-[동작] ① 문의 언어 자동감지 ② 감지된 언어로 자동 응답 생성
-[원칙 없었다면] 한국어로만 응답하면 외국인 게스트 응대라는 핵심 가치 자체가 성립 안 함</t>
+          <t>[상황] 게스트가 '환불해주세요'처럼 금전이 걸린 문의를 보내는 경우
+[동작] ① 위험도를 자동(와이파이 등) vs 승인필요(환불·변경 등)로 분류 ② 승인필요 건은 Action Center에서 호스트 확인 후에만 발송
+[원칙 없었다면] 구분 없이 전부 자동응답하면 AI가 호스트도 모르게 환불을 약속하는 사고 위험</t>
         </is>
       </c>
       <c r="D183" s="185" t="n"/>
@@ -20442,7 +20444,13 @@
         </is>
       </c>
       <c r="B201" s="184" t="n"/>
-      <c r="C201" s="183" t="n"/>
+      <c r="C201" s="183" t="inlineStr">
+        <is>
+          <t>[상황] 3단계(고객응대자동화) 마무리 시점, AI가 실제로 안전하게 동작하는지 확인 필요
+[동작] ① 교차오답 테스트(다른 숙소 정보 유출 여부) ② 의도적으로 API 실패 유발 후 에러UI 확인
+[원칙 없었다면] 검증 없이 넘어가면 실제 게스트 응대 중 교차오답이나 먹통 화면을 처음 마주하게 됨</t>
+        </is>
+      </c>
       <c r="D201" s="185" t="n"/>
       <c r="E201" s="185" t="n"/>
       <c r="F201" s="185" t="n"/>
@@ -20636,7 +20644,13 @@
         </is>
       </c>
       <c r="B210" s="184" t="n"/>
-      <c r="C210" s="183" t="n"/>
+      <c r="C210" s="183" t="inlineStr">
+        <is>
+          <t>[상황] 체크인 시각이 된 게스트에게 출입 방법을 안전하게 안내해야 함
+[동작] ① 예약확정시 임시 비밀번호 자동생성 ② 체크아웃 시각에 자동 만료 처리(Mock)
+[원칙 없었다면] 수동 발급이면 깜빡하고 비밀번호를 안 보내 게스트가 문 앞에서 못 들어가는 사고</t>
+        </is>
+      </c>
       <c r="D210" s="185" t="n"/>
       <c r="E210" s="185" t="n"/>
       <c r="F210" s="185" t="n"/>
@@ -20832,9 +20846,9 @@
       <c r="B219" s="184" t="n"/>
       <c r="C219" s="183" t="inlineStr">
         <is>
-          <t>[상황] 게스트가 '환불해주세요'처럼 금전이 걸린 문의를 보내는 경우
-[동작] ① 위험도를 자동(와이파이 등) vs 승인필요(환불·변경 등)로 분류 ② 승인필요 건은 Action Center에서 호스트 확인 후에만 발송
-[원칙 없었다면] 구분 없이 전부 자동응답하면 AI가 호스트도 모르게 환불을 약속하는 사고 위험</t>
+          <t>[상황] 실제 스마트락 하드웨어 없이도 잠김/열림 상태를 관리해야 함
+[동작] ① Mock 락 상태 대시보드 구현(잠김/열림/배터리 표시) ② 실제 연동은 2차 과제로 명확히 구분
+[원칙 없었다면] 실제 하드웨어 연동을 무리하게 시도했다면 부트캠프 기간 내 완성 자체가 불가능</t>
         </is>
       </c>
       <c r="D219" s="185" t="n"/>
@@ -21032,9 +21046,9 @@
       <c r="B228" s="184" t="n"/>
       <c r="C228" s="183" t="inlineStr">
         <is>
-          <t>[상황] 3단계(고객응대자동화) 마무리 시점, AI가 실제로 안전하게 동작하는지 확인 필요
-[동작] ① 교차오답 테스트(다른 숙소 정보 유출 여부) ② 의도적으로 API 실패 유발 후 에러UI 확인
-[원칙 없었다면] 검증 없이 넘어가면 실제 게스트 응대 중 교차오답이나 먹통 화면을 처음 마주하게 됨</t>
+          <t>[상황] 청소 작업이 시스템에 만들어져도 청소업체에 전달되지 않으면 화면 안에서만 도는 데이터
+[동작] ① 청소업체에 문자로 자동 발송해 사람에게 실제로 닿게 함 ② 체크리스트와 사진으로 완료를 증빙받아 VERIFIED로 닫음 ③ 호스텔은 객실 단위로 정비 항목과 비품부족을 따로 체크
+[원칙 없었다면] 호스트가 매번 전화로 청소를 부르고 끝났는지 눈으로 확인하러 가야 하며, 비품이 떨어진 걸 다음 게스트가 먼저 발견하게 됨</t>
         </is>
       </c>
       <c r="D228" s="185" t="n"/>
@@ -21196,9 +21210,9 @@
       <c r="B236" s="184" t="n"/>
       <c r="C236" s="183" t="inlineStr">
         <is>
-          <t>[상황] 체크인 시각이 된 게스트에게 출입 방법을 안전하게 안내해야 함
-[동작] ① 예약확정시 임시 비밀번호 자동생성 ② 체크아웃 시각에 자동 만료 처리(Mock)
-[원칙 없었다면] 수동 발급이면 깜빡하고 비밀번호를 안 보내 게스트가 문 앞에서 못 들어가는 사고</t>
+          <t>[상황] 4단계(청소·체크인) 마무리 시점, 예약부터 청소까지 전체 흐름 확인 필요
+[동작] ① 체크아웃→청소생성→상태전이 전체 흐름을 1회 시뮬레이션으로 재현 ② 끊기는 지점 없는지 확인
+[원칙 없었다면] 검증 없이 넘어가면 실제 게스트 체크아웃 후 청소가 자동 생성 안 되는 걸 뒤늦게 발견</t>
         </is>
       </c>
       <c r="D236" s="185" t="n"/>
@@ -21360,9 +21374,9 @@
       <c r="B244" s="184" t="n"/>
       <c r="C244" s="183" t="inlineStr">
         <is>
-          <t>[상황] 실제 스마트락 하드웨어 없이도 잠김/열림 상태를 관리해야 함
-[동작] ① Mock 락 상태 대시보드 구현(잠김/열림/배터리 표시) ② 실제 연동은 2차 과제로 명확히 구분
-[원칙 없었다면] 실제 하드웨어 연동을 무리하게 시도했다면 부트캠프 기간 내 완성 자체가 불가능</t>
+          <t>[상황] 현재 연동하는 iCal 데이터에는 결제·정산 금액이 포함되지 않아, 정산 금액을 시스템이 스스로 계산해내야 함
+[동작] ① 전날 정한 채널별 수수료를 적용해 기본단가×박수-수수료로 1차 금액을 자동 추정 ② 취소·환불된 예약은 refund_status를 보고 매출에서 자동 제외
+[원칙 없었다면] 매달 예약을 하나씩 엑셀에 옮겨 적어야 하고, 환불된 건을 빼먹으면 매출이 실제보다 부풀려짐</t>
         </is>
       </c>
       <c r="D244" s="185" t="n"/>
@@ -21940,9 +21954,9 @@
       <c r="B267" s="184" t="n"/>
       <c r="C267" s="183" t="inlineStr">
         <is>
-          <t>[상황] 청소 상태가 실제로 어디까지 진행됐는지 추적이 안 되면 다음 게스트 체크인에 지장
-[동작] ① PENDING→ASSIGNED→IN_PROGRESS→COMPLETED→VERIFIED 상태머신 구현 ② ISSUE 상태에서 복귀경로도 확보
-[원칙 없었다면] 상태 구분이 없으면 청소가 끝났는지 안 끝났는지 매번 직접 확인해야 함</t>
+          <t>[상황] 자동추정만으로는 정산이 끝나지 않는다 — 할인처럼 시스템이 모르는 예외가 늘 섞여 있고, 인허가 기한도 호스트가 놓치기 쉬움
+[동작] ① 추정된 금액을 한 번에 확인 처리하는 일괄확인 UI ② 차이나는 건만 골라 고치는 예외보정 ③ 채널·숙소·월별로 집계하고 금액이 추정치인지 확정인지 뱃지로 구분 ④ 변경신고 D+30 카운트다운을 붙여 액션센터가 서류 기한을 잡아내게 함 ⑤ 발표용 시드 데이터를 작성하고 ⑥ 화면과 집계에 실제 반영되는지 확인
+[원칙 없었다면] 전부 수기로 고치면 엑셀 정산과 다를 게 없고, 기한이 지난 신고는 아무도 알려주지 않아 그대로 넘어감</t>
         </is>
       </c>
       <c r="D267" s="185" t="n"/>
@@ -22176,9 +22190,9 @@
       <c r="B277" s="184" t="n"/>
       <c r="C277" s="183" t="inlineStr">
         <is>
-          <t>[상황] 4단계(청소·체크인) 마무리 시점, 예약부터 청소까지 전체 흐름 확인 필요
-[동작] ① 체크아웃→청소생성→상태전이 전체 흐름을 1회 시뮬레이션으로 재현 ② 끊기는 지점 없는지 확인
-[원칙 없었다면] 검증 없이 넘어가면 실제 게스트 체크아웃 후 청소가 자동 생성 안 되는 걸 뒤늦게 발견</t>
+          <t>[상황] 청소지연·중복예약·정산검토 등 여러 이벤트가 흩어져 있으면 호스트가 놓치기 쉬움
+[동작] ① Action Center 규칙기반 트리거 구현 ② 이벤트 발생시 자동으로 🔴🟡🟢 큐에 분류
+[원칙 없었다면] 통합 큐가 없으면 각 화면을 매번 따로 확인해야 하고 급한 건을 놓치는 사고</t>
         </is>
       </c>
       <c r="D277" s="185" t="n"/>
@@ -22520,9 +22534,9 @@
       <c r="B290" s="184" t="n"/>
       <c r="C290" s="183" t="inlineStr">
         <is>
-          <t>[상황] 2026년 5월부터 에어비앤비 국내 수수료가 단일요율(15.5%)로 바뀌어 기존 가정이 틀렸었음
-[동작] ① 채널별 수수료 템플릿 설계(Airbnb 15.5%, Booking.com 15~18%) ② 정산 로직에 정확히 반영
-[원칙 없었다면] 옛날 요율(3.3%)을 그대로 썼다면 실제 정산 금액이 크게 어긋나는 사고</t>
+          <t>[상황] 기능 구현의 마지막 날. 빈 날짜를 그대로 두면 매출이 새지만, 호스트가 매일 달력을 보며 가격을 조정할 수는 없음
+[동작] ① 공휴일·지역축제와 예약임박도·잔여객실을 근거로 추천가를 계산 ② 평일할인·주말인상을 배치로 미세조정하고 연휴 방치를 감지 ③ 추천가를 근거와 함께 카드로 보여주고 승인은 호스트가 하되 하한가 아래는 경고 ④ 정산·가격 화면에 로딩·에러·빈상태를 붙여 마무리 ⑤ 5단계 검증으로 정산 3단계 파이프라인과 알림센터 트리거를 실데이터로 재현하고, 회귀체크로 청소→정산 흐름까지 다시 확인
+[원칙 없었다면] AI가 호스트 동의 없이 가격을 내려버리거나, 반대로 아무도 손대지 않아 연휴가 빈 채로 지나감. 여기서 닫지 못하면 내일부터 시작할 발표 준비가 밀림</t>
         </is>
       </c>
       <c r="D290" s="185" t="n"/>
@@ -22680,9 +22694,9 @@
       <c r="B298" s="184" t="n"/>
       <c r="C298" s="183" t="inlineStr">
         <is>
-          <t>[상황] 청소지연·중복예약·정산검토 등 여러 이벤트가 흩어져 있으면 호스트가 놓치기 쉬움
-[동작] ① Action Center 규칙기반 트리거 구현 ② 이벤트 발생시 자동으로 🔴🟡🟢 큐에 분류
-[원칙 없었다면] 통합 큐가 없으면 각 화면을 매번 따로 확인해야 하고 급한 건을 놓치는 사고</t>
+          <t>[상황] 어제로 기능 구현이 끝났다. 오늘부터는 만드는 일이 아니라 만든 것을 설명하는 일로 성격이 바뀜
+[동작] ① 발표 슬라이드 초안을 잡고 실제 화면을 캡처해 AI Agent Loop 다이어그램까지 넣음 ② 9/3 기획서를 확장해 배경·기술스택·아키텍처·사용법이 담긴 제출용 설명문서를 정리
+[원칙 없었다면] 슬라이드와 설명문서는 기획안·구조·주요 기능이 겹치는데 따로 만들면 같은 내용을 두 번 쓰고 서로 다른 말을 하게 됨. 같은 날 함께 잡아야 한 번에 정리됨</t>
         </is>
       </c>
       <c r="D298" s="185" t="n"/>
@@ -22844,9 +22858,9 @@
       <c r="B306" s="184" t="n"/>
       <c r="C306" s="183" t="inlineStr">
         <is>
-          <t>[상황] 5단계(정산·가격·컴플라이언스) 마무리 시점, 정산 파이프라인이 실제로 맞물려 돌아가는지 확인 필요
-[동작] ① 정산 3단계 파이프라인 재현 ② 알림센터 트리거가 실데이터로 정상 작동하는지 확인
-[원칙 없었다면] 검증 없이 넘어가면 실제 정산 시점에 계산이 틀어지는 걸 뒤늦게 발견</t>
+          <t>[상황] 편집 도구가 10분짜리를 감당하지 못하는 걸 10/10 밤에 알게 되면 손쓸 방법이 없음
+[동작] ① 더미 영상으로 10분 내보내기를 미리 돌려보고, 실패하면 Shotcut으로 전환할지 오늘 결정 ② 화면 흐름과 나레이션 포인트를 대본·콘티로 먼저 잡아둠
+[원칙 없었다면] 도구를 검증하지 않으면 녹화를 다 마친 뒤 내보내기에서 막히고, 대본 없이 녹화하면 말이 꼬여 같은 구간을 몇 번씩 다시 찍게 됨</t>
         </is>
       </c>
       <c r="D306" s="185" t="n"/>
@@ -23696,9 +23710,9 @@
       <c r="B340" s="184" t="n"/>
       <c r="C340" s="183" t="inlineStr">
         <is>
-          <t>[상황] 어젯밤(10/9) 녹화한 영상 중 일부는 재촬영이 필요할 수 있음
-[동작] ① 아침에 전날 녹화분부터 다시 확인 ② 재촬영 필요분만 골라서 다시 찍기 ③ 이후 편집+최종 제출
-[원칙 없었다면] 확인 없이 바로 편집 들어가면 편집 다 끝난 뒤에야 빠진 장면을 발견하는 최악의 상황</t>
+          <t>[상황] 어젯밤 녹화분에 재촬영이 필요할 수 있고, 오늘은 설명문서와 소스코드를 제출해야 하는 날이기도 하다
+[동작] ① 아침에 전날 녹화분부터 다시 확인 ② 재촬영 필요분만 골라서 다시 찍기 ③ 편집·렌더링 후 소스코드를 ZIP으로 압축(node_modules·.env·__pycache__ 제외 확인) ④ 설명문서와 함께 PBT에 최종 제출
+[원칙 없었다면] 확인 없이 바로 편집 들어가면 편집 다 끝난 뒤에야 빠진 장면을 발견하는 최악의 상황. 압축 전에 걸러내지 않으면 API 키나 개인정보가 그대로 담긴 채 제출됨</t>
         </is>
       </c>
       <c r="D340" s="185" t="n"/>
@@ -23969,7 +23983,7 @@
       <c r="C351" s="183" t="inlineStr">
         <is>
           <t>[상황] 발표 전날, 실제 발표에 쓸 데이터가 지금까지 테스트하며 어질러진 상태일 수 있음
-[동작] ① DB 초기화 후 골든패스 데이터로 재세팅 ② 로그인→예약→AI응대→정산까지 리허설 1회 실행
+[동작] ① DB 초기화 후 골든패스 데이터로 재세팅 ② 로그인→예약→AI응대→정산까지 리허설 1회 실행 ③ 발표자료(PPT)를 PBT에 제출 — 오늘이 외부마감이다
 [원칙 없었다면] 어질러진 데이터로 발표하면 화면에 이상한 값이 노출되거나 시나리오가 꼬이는 사고</t>
         </is>
       </c>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E37" s="124" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F37" s="122" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="C25" s="144" t="inlineStr">
         <is>
-          <t>□ [신규] 회원가입/로그인 화면+API 설계(JWT)
+          <t>☑ [신규] 회원가입/로그인 화면+API 설계(JWT)
 □ [검증] ✅ 1.5단계 검증: 와이어프레임 실제 흐름대로 클릭 시뮬레이션 리뷰</t>
         </is>
       </c>
@@ -16005,7 +16005,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="89">
       <c r="A4" s="178" t="inlineStr">
         <is>
@@ -16205,7 +16204,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="89">
       <c r="A13" s="178" t="inlineStr">
         <is>
@@ -16621,7 +16619,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1" s="89">
       <c r="A28" s="178" t="inlineStr">
         <is>
@@ -17145,7 +17142,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46" ht="24" customHeight="1" s="89">
       <c r="A46" s="178" t="inlineStr">
         <is>
@@ -17381,7 +17377,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56" ht="24" customHeight="1" s="89">
       <c r="A56" s="178" t="inlineStr">
         <is>
@@ -17509,7 +17504,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63" ht="24" customHeight="1" s="89">
       <c r="A63" s="178" t="inlineStr">
         <is>
@@ -17781,7 +17775,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74" ht="24" customHeight="1" s="89">
       <c r="A74" s="178" t="inlineStr">
         <is>
@@ -17981,7 +17974,6 @@
         </is>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="89">
       <c r="A83" s="178" t="inlineStr">
         <is>
@@ -18109,7 +18101,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90" ht="24" customHeight="1" s="89">
       <c r="A90" s="178" t="inlineStr">
         <is>
@@ -18229,7 +18220,7 @@
       </c>
       <c r="G94" s="181" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18300,6 @@
         </is>
       </c>
     </row>
-    <row r="98"/>
     <row r="99" ht="24" customHeight="1" s="89">
       <c r="A99" s="178" t="inlineStr">
         <is>
@@ -18437,7 +18427,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106" ht="24" customHeight="1" s="89">
       <c r="A106" s="178" t="inlineStr">
         <is>
@@ -18565,7 +18554,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113" ht="24" customHeight="1" s="89">
       <c r="A113" s="178" t="inlineStr">
         <is>
@@ -18729,7 +18717,6 @@
         </is>
       </c>
     </row>
-    <row r="120"/>
     <row r="121" ht="24" customHeight="1" s="89">
       <c r="A121" s="178" t="inlineStr">
         <is>
@@ -18929,7 +18916,6 @@
         </is>
       </c>
     </row>
-    <row r="129"/>
     <row r="130" ht="24" customHeight="1" s="89">
       <c r="A130" s="178" t="inlineStr">
         <is>
@@ -19093,7 +19079,6 @@
         </is>
       </c>
     </row>
-    <row r="137"/>
     <row r="138" ht="24" customHeight="1" s="89">
       <c r="A138" s="178" t="inlineStr">
         <is>
@@ -19257,7 +19242,6 @@
         </is>
       </c>
     </row>
-    <row r="145"/>
     <row r="146" ht="24" customHeight="1" s="89">
       <c r="A146" s="178" t="inlineStr">
         <is>
@@ -19421,7 +19405,6 @@
         </is>
       </c>
     </row>
-    <row r="153"/>
     <row r="154" ht="24" customHeight="1" s="89">
       <c r="A154" s="178" t="inlineStr">
         <is>
@@ -19585,7 +19568,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162" ht="24" customHeight="1" s="89">
       <c r="A162" s="178" t="inlineStr">
         <is>
@@ -19749,7 +19731,6 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
     <row r="170" ht="24" customHeight="1" s="89">
       <c r="A170" s="178" t="inlineStr">
         <is>
@@ -19913,7 +19894,6 @@
         </is>
       </c>
     </row>
-    <row r="177"/>
     <row r="178" ht="24" customHeight="1" s="89">
       <c r="A178" s="178" t="inlineStr">
         <is>
@@ -20077,7 +20057,6 @@
         </is>
       </c>
     </row>
-    <row r="185"/>
     <row r="186" ht="24" customHeight="1" s="89">
       <c r="A186" s="178" t="inlineStr">
         <is>
@@ -20313,7 +20292,6 @@
         </is>
       </c>
     </row>
-    <row r="195"/>
     <row r="196" ht="24" customHeight="1" s="89">
       <c r="A196" s="178" t="inlineStr">
         <is>
@@ -20477,7 +20455,6 @@
         </is>
       </c>
     </row>
-    <row r="203"/>
     <row r="204" ht="24" customHeight="1" s="89">
       <c r="A204" s="178" t="inlineStr">
         <is>
@@ -20677,7 +20654,6 @@
         </is>
       </c>
     </row>
-    <row r="212"/>
     <row r="213" ht="24" customHeight="1" s="89">
       <c r="A213" s="178" t="inlineStr">
         <is>
@@ -20877,7 +20853,6 @@
         </is>
       </c>
     </row>
-    <row r="221"/>
     <row r="222" ht="24" customHeight="1" s="89">
       <c r="A222" s="178" t="inlineStr">
         <is>
@@ -21077,7 +21052,6 @@
         </is>
       </c>
     </row>
-    <row r="230"/>
     <row r="231" ht="24" customHeight="1" s="89">
       <c r="A231" s="178" t="inlineStr">
         <is>
@@ -21241,7 +21215,6 @@
         </is>
       </c>
     </row>
-    <row r="238"/>
     <row r="239" ht="24" customHeight="1" s="89">
       <c r="A239" s="178" t="inlineStr">
         <is>
@@ -21405,7 +21378,6 @@
         </is>
       </c>
     </row>
-    <row r="246"/>
     <row r="247" ht="24" customHeight="1" s="89">
       <c r="A247" s="178" t="inlineStr">
         <is>
@@ -21641,7 +21613,6 @@
         </is>
       </c>
     </row>
-    <row r="256"/>
     <row r="257" ht="24" customHeight="1" s="89">
       <c r="A257" s="178" t="inlineStr">
         <is>
@@ -21985,7 +21956,6 @@
         </is>
       </c>
     </row>
-    <row r="269"/>
     <row r="270" ht="24" customHeight="1" s="89">
       <c r="A270" s="178" t="inlineStr">
         <is>
@@ -22221,7 +22191,6 @@
         </is>
       </c>
     </row>
-    <row r="279"/>
     <row r="280" ht="24" customHeight="1" s="89">
       <c r="A280" s="178" t="inlineStr">
         <is>
@@ -22565,7 +22534,6 @@
         </is>
       </c>
     </row>
-    <row r="292"/>
     <row r="293" ht="24" customHeight="1" s="89">
       <c r="A293" s="178" t="inlineStr">
         <is>
@@ -22725,7 +22693,6 @@
         </is>
       </c>
     </row>
-    <row r="300"/>
     <row r="301" ht="24" customHeight="1" s="89">
       <c r="A301" s="178" t="inlineStr">
         <is>
@@ -22889,7 +22856,6 @@
         </is>
       </c>
     </row>
-    <row r="308"/>
     <row r="309" ht="24" customHeight="1" s="89">
       <c r="A309" s="178" t="inlineStr">
         <is>
@@ -23197,7 +23163,6 @@
         </is>
       </c>
     </row>
-    <row r="320"/>
     <row r="321" ht="24" customHeight="1" s="89">
       <c r="A321" s="178" t="inlineStr">
         <is>
@@ -23469,7 +23434,6 @@
         </is>
       </c>
     </row>
-    <row r="331"/>
     <row r="332" ht="24" customHeight="1" s="89">
       <c r="A332" s="178" t="inlineStr">
         <is>
@@ -23741,7 +23705,6 @@
         </is>
       </c>
     </row>
-    <row r="342"/>
     <row r="343" ht="24" customHeight="1" s="89">
       <c r="A343" s="178" t="inlineStr">
         <is>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,8 +2534,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="E34" s="124" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F34" s="130" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E38" s="134" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F38" s="132" t="inlineStr">
@@ -7965,6 +7965,11 @@
           <t>결과 확인 리스트(Definition of Done)</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>판정 근거(9/9 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" s="89">
       <c r="A4" s="139" t="inlineStr">
@@ -7998,10 +8003,18 @@
       </c>
       <c r="C5" s="140" t="inlineStr">
         <is>
-          <t>□ 11개 화면 목록에 빠진 화면이 없는가
-□ 와이어프레임이 실제 사용흐름과 맞는가(클릭 시뮬레이션)
-□ 공통 컴포넌트(Loading/Empty/Error/Toast)가 정의됐는가
-□ 회원가입/로그인 플로우가 설계에 포함됐는가</t>
+          <t>☑ 11개 화면 목록에 빠진 화면이 없는가
+☑ 설계 문서(ui_design 6·7절)와 구현 계획이 실제 사용흐름과 맞는가
+☑ 공통 컴포넌트(Loading/Empty/Error/Toast)가 정의됐는가
+☑ 회원가입/로그인 플로우가 설계에 포함됐는가</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>① ui_design 7-7 커버리지 표로 11개 라우트 전수 확인
+② 후보 25건 추출, 3회 독립 크로스체크로 판정 — 완료 9 / 종결·흡수 4 / 부분 3 / 미완 9. 미완은 전부 착수일 지정하여 이월
+③ ui_design 5-9절. 9/9에 폼 화면용 어휘(입력대기/제출중/실패/성공)를 추가로 분리
+④ api_contract v2.3, ui_design 4-1·4-2·7-2, 401 정책 1-6</t>
         </is>
       </c>
     </row>
@@ -8407,17 +8420,18 @@
       <c r="C25" s="144" t="inlineStr">
         <is>
           <t>☑ [신규] 회원가입/로그인 화면+API 설계(JWT)
-□ [검증] ✅ 1.5단계 검증: 와이어프레임 실제 흐름대로 클릭 시뮬레이션 리뷰</t>
+☑ [검증] ✅ 1.5단계 검증: 와이어프레임 실제 흐름대로 클릭 시뮬레이션 리뷰</t>
         </is>
       </c>
       <c r="D25" s="145" t="inlineStr">
         <is>
-          <t>□ [신규] User Flow 다이어그램 작성(화면간 이동 구조)</t>
+          <t>☑ [신규] User Flow 다이어그램 작성(화면간 이동 구조)</t>
         </is>
       </c>
       <c r="E25" s="148" t="inlineStr">
         <is>
-          <t>🌙 연장근무일(+3h)</t>
+          <t>🌙 연장근무일(+3h)
+※ User Flow는 D열(야간·Gemini)에 있으나 실제로는 Claude Code가 주간에 작성. 열은 옮기지 않았다(9/9).</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18198,7 @@
       </c>
       <c r="G93" s="181" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18270,7 @@
       </c>
       <c r="G95" s="181" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7965,7 +7965,7 @@
           <t>결과 확인 리스트(Definition of Done)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="88" t="inlineStr">
         <is>
           <t>판정 근거(9/9 추가)</t>
         </is>
@@ -8009,7 +8009,7 @@
 ☑ 회원가입/로그인 플로우가 설계에 포함됐는가</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="88" t="inlineStr">
         <is>
           <t>① ui_design 7-7 커버리지 표로 11개 라우트 전수 확인
 ② 후보 25건 추출, 3회 독립 크로스체크로 판정 — 완료 9 / 종결·흡수 4 / 부분 3 / 미완 9. 미완은 전부 착수일 지정하여 이월
@@ -16206,7 +16206,7 @@
       <c r="B11" s="184" t="n"/>
       <c r="C11" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D11" s="185" t="n"/>
@@ -16621,7 +16621,7 @@
       <c r="B26" s="184" t="n"/>
       <c r="C26" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D26" s="185" t="n"/>
@@ -17144,7 +17144,7 @@
       <c r="B44" s="184" t="n"/>
       <c r="C44" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D44" s="185" t="n"/>
@@ -17379,7 +17379,7 @@
       <c r="B54" s="184" t="n"/>
       <c r="C54" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D54" s="185" t="n"/>
@@ -17506,7 +17506,7 @@
       <c r="B61" s="184" t="n"/>
       <c r="C61" s="187" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)  ☐ 검증 체크 완료  ☐ 🔍 오늘은 검증일! DoD 결과 '9단계 검증 체크리스트' 시트에 기록</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)  ☑ 검증 체크 완료  ☑ 🔍 오늘은 검증일! DoD 결과 '9단계 검증 체크리스트' 시트에 기록</t>
         </is>
       </c>
       <c r="D61" s="185" t="n"/>
@@ -17777,7 +17777,7 @@
       <c r="B72" s="184" t="n"/>
       <c r="C72" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D72" s="185" t="n"/>
@@ -18302,7 +18302,7 @@
       <c r="B97" s="184" t="n"/>
       <c r="C97" s="187" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)  ☐ 검증 체크 완료  ☐ 🔍 오늘은 검증일! DoD 결과 '9단계 검증 체크리스트' 시트에 기록</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)  ☐ 검증 체크 완료  ☐ 🔍 오늘은 검증일! DoD 결과 '9단계 검증 체크리스트' 시트에 기록</t>
         </is>
       </c>
       <c r="D97" s="185" t="n"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -18302,7 +18302,7 @@
       <c r="B97" s="184" t="n"/>
       <c r="C97" s="187" t="inlineStr">
         <is>
-          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)  ☐ 검증 체크 완료  ☐ 🔍 오늘은 검증일! DoD 결과 '9단계 검증 체크리스트' 시트에 기록</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)  ☑ 검증 체크 완료  ☑ 🔍 오늘은 검증일! DoD 결과 '9단계 검증 체크리스트' 시트에 기록</t>
         </is>
       </c>
       <c r="D97" s="185" t="n"/>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,8 +2534,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C77" s="122" t="inlineStr">
         <is>
-          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
+          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_at=체크아웃 시각, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
         </is>
       </c>
       <c r="D77" s="124" t="inlineStr">
@@ -8777,7 +8777,7 @@
       <c r="C39" s="149" t="inlineStr">
         <is>
           <t>□ 예약확정시 임시 비밀번호 자동생성/만료 로직
-□ [신규] 예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)
+□ [신규] 예약확정 시점 청소작업 선제생성 로직(scheduled_at=체크아웃 시각, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)
 □ 예약변경시 청소시간 자동 재계산 로직</t>
         </is>
       </c>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="E73" s="153" t="inlineStr">
         <is>
-          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
+          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_at=체크아웃 시각, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
         </is>
       </c>
       <c r="F73" s="155" t="inlineStr">
@@ -20479,7 +20479,7 @@
     <row r="205" ht="18" customHeight="1" s="89">
       <c r="A205" s="179" t="inlineStr">
         <is>
-          <t>🎯 오늘의 타이틀: 예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
+          <t>🎯 오늘의 타이틀: 예약확정 시점 청소작업 선제생성 로직(scheduled_at=체크아웃 시각, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="B208" s="182" t="inlineStr">
         <is>
-          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_date=체크아웃일, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
+          <t>예약확정 시점 청소작업 선제생성 로직(scheduled_at=체크아웃 시각, 9/3 크로스체크로 시점 정정 — 전날알림 기능 성립을 위해 필요)</t>
         </is>
       </c>
       <c r="C208" s="182" t="inlineStr">

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="H128" s="132" t="inlineStr">
         <is>
-          <t>검증, 10/12는 발표당일 작업없음</t>
+          <t>검증, 10/12는 발표당일 작업없음. 발표 당일 아침 UptimeRobot 가동 상태 확인, 발표 30분 전 /health 수동 호출로 웜업. 전날 웨이크업은 15분 뒤 무효</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
         <is>
           <t>□ 시드데이터 재실행 후 데모 데이터가 깨끗한가
 □ E2E 시나리오(로그인→...→정산)가 끊김없이 진행되는가
-□ 발표 전 서버 웨이크업을 확인했는가
+□ 발표 당일(10/12) 웜업 절차를 확인했는가 — 전날 웨이크업은 15분 뒤 무효
 □ 예상 Q&amp;A 답변이 준비됐는가
 □ 발표영상 실제 재생 확인(음성·화면 끝까지 끊김없이 재생되는지)</t>
         </is>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E46" s="128" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F46" s="126" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C26" s="144" t="inlineStr">
         <is>
-          <t>□ iCal 연동 + ChannelConnection 구현(sync_status/last_synced_at 표시)</t>
+          <t>☑ iCal 연동 + ChannelConnection 구현(sync_status/last_synced_at 표시)</t>
         </is>
       </c>
       <c r="D26" s="145" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="G102" s="181" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,8 +2534,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E47" s="124" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F47" s="122" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="C27" s="144" t="inlineStr">
         <is>
-          <t>□ [신규] 회원가입/로그인 화면+API 구현(JWT, 비밀번호는 bcrypt 해시로 저장)</t>
+          <t>☑ [신규] 회원가입/로그인 화면+API 구현(JWT, 비밀번호는 bcrypt 해시로 저장)</t>
         </is>
       </c>
       <c r="D27" s="145" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="G46" s="154" t="inlineStr">
         <is>
-          <t>backend/app/api/auth.py, frontend/src/pages/Login.jsx</t>
+          <t>backend/app/api/v1/endpoints/auth.py, frontend/src/pages/Login.tsx</t>
         </is>
       </c>
       <c r="H46" s="153" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="J46" s="153" t="inlineStr">
         <is>
-          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 403으로 차단되는지 확인</t>
+          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 404으로 차단되는지 확인</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="D109" s="182" t="inlineStr">
         <is>
-          <t>backend/app/api/auth.py, frontend/src/pages/Login.jsx</t>
+          <t>backend/app/api/v1/endpoints/auth.py, frontend/src/pages/Login.tsx</t>
         </is>
       </c>
       <c r="E109" s="182" t="inlineStr">
@@ -18519,12 +18519,12 @@
       </c>
       <c r="F109" s="182" t="inlineStr">
         <is>
-          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 403으로 차단되는지 확인</t>
+          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 404으로 차단되는지 확인</t>
         </is>
       </c>
       <c r="G109" s="181" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
     </row>

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="J46" s="153" t="inlineStr">
         <is>
-          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 404으로 차단되는지 확인</t>
+          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 404로 차단되는지 확인</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,8 @@
       </c>
       <c r="J53" s="153" t="inlineStr">
         <is>
-          <t>로컬에서 정상 동작 확인 후에만 커밋</t>
+          <t>로컬에서 정상 동작 확인 후에만 커밋
+Mock 해제 상태에서 가입 → /onboarding 숙소·객실 등록 → 대시보드 진입 확인(숙소 API 8개, api_contract 2절)</t>
         </is>
       </c>
     </row>
@@ -18519,7 +18520,7 @@
       </c>
       <c r="F109" s="182" t="inlineStr">
         <is>
-          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 404으로 차단되는지 확인</t>
+          <t>호스트A의 토큰으로 호스트B 소유의 property_id를 조회 시도 → 404로 차단되는지 확인</t>
         </is>
       </c>
       <c r="G109" s="181" t="inlineStr">
@@ -19044,7 +19045,8 @@
       </c>
       <c r="F134" s="182" t="inlineStr">
         <is>
-          <t>로컬에서 정상 동작 확인 후에만 커밋</t>
+          <t>로컬에서 정상 동작 확인 후에만 커밋
+Mock 해제 상태에서 가입 → /onboarding 숙소·객실 등록 → 대시보드 진입 확인(숙소 API 8개, api_contract 2절)</t>
         </is>
       </c>
       <c r="G134" s="181" t="inlineStr">

--- a/3rd_host_ai_체크리스트.xlsx
+++ b/3rd_host_ai_체크리스트.xlsx
@@ -2534,9 +2534,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -18430,7 +18430,7 @@
       <c r="B104" s="184" t="n"/>
       <c r="C104" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D104" s="185" t="n"/>
@@ -18557,7 +18557,7 @@
       <c r="B111" s="184" t="n"/>
       <c r="C111" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D111" s="185" t="n"/>
@@ -18720,7 +18720,7 @@
       <c r="B119" s="184" t="n"/>
       <c r="C119" s="186" t="inlineStr">
         <is>
-          <t>☐ 전날 순서대로 실행됨  ☐ 위 작업 전부 완료  ☐ git commit 완료  ☐ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
+          <t>☑ 전날 순서대로 실행됨  ☑ 위 작업 전부 완료  ☑ git commit 완료  ☑ 전날 백업 실행(backup_push.ps1/.bat 더블클릭 → git push+Desktop 미러백업)</t>
         </is>
       </c>
       <c r="D119" s="185" t="n"/>
